--- a/research/traditional_assets/database/data/colombia/colombia_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_oil_gas_production_and_exploration.xlsx
@@ -647,10 +647,10 @@
         <v>0.681702668360864</v>
       </c>
       <c r="X2">
-        <v>0.1594513046214187</v>
+        <v>0.1594256544784785</v>
       </c>
       <c r="Y2">
-        <v>0.5222513637394454</v>
+        <v>0.5222770138823856</v>
       </c>
       <c r="Z2">
         <v>1.242287694974003</v>
@@ -659,10 +659,10 @@
         <v>0.2415077989601386</v>
       </c>
       <c r="AB2">
-        <v>0.1066892577322327</v>
+        <v>0.1066770793030216</v>
       </c>
       <c r="AC2">
-        <v>0.1348185412279059</v>
+        <v>0.134830719657117</v>
       </c>
       <c r="AD2">
         <v>525</v>
@@ -781,10 +781,10 @@
         <v>0.681702668360864</v>
       </c>
       <c r="X3">
-        <v>0.1594513046214187</v>
+        <v>0.1594256544784785</v>
       </c>
       <c r="Y3">
-        <v>0.5222513637394454</v>
+        <v>0.5222770138823856</v>
       </c>
       <c r="Z3">
         <v>1.242287694974003</v>
@@ -793,10 +793,10 @@
         <v>0.2415077989601386</v>
       </c>
       <c r="AB3">
-        <v>0.1066892577322327</v>
+        <v>0.1066770793030216</v>
       </c>
       <c r="AC3">
-        <v>0.1348185412279059</v>
+        <v>0.134830719657117</v>
       </c>
       <c r="AD3">
         <v>525</v>
@@ -1133,49 +1133,49 @@
         <v>8.770967741935481</v>
       </c>
       <c r="F2">
-        <v>4.54326012172902</v>
+        <v>4.03223377469243</v>
       </c>
       <c r="G2">
         <v>1.19726339794755</v>
       </c>
       <c r="H2">
-        <v>1.77807981755986</v>
+        <v>2.00603876852908</v>
       </c>
       <c r="I2">
         <v>0.525210084033613</v>
       </c>
       <c r="J2">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
       <c r="K2">
         <v>474.6</v>
       </c>
       <c r="L2">
-        <v>305.639968975381</v>
+        <v>225.221627000829</v>
       </c>
       <c r="M2">
         <v>876.2</v>
       </c>
       <c r="N2">
-        <v>961.927968975381</v>
+        <v>981.469627000829</v>
       </c>
       <c r="O2">
         <v>525</v>
       </c>
       <c r="P2">
-        <v>779.688</v>
+        <v>879.648</v>
       </c>
       <c r="Q2">
-        <v>0.106689257732233</v>
+        <v>0.106677079303022</v>
       </c>
       <c r="R2">
-        <v>0.09705674833535261</v>
+        <v>0.0950844779997545</v>
       </c>
       <c r="S2">
         <v>0.0589923673444086</v>
       </c>
       <c r="T2">
-        <v>0.0498923673444086</v>
+        <v>0.0498273673444086</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1184,20 +1184,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="W2">
-        <v>0.159451304621419</v>
+        <v>0.159425654478479</v>
       </c>
       <c r="X2">
-        <v>0.264275917303245</v>
+        <v>0.426969956138958</v>
       </c>
       <c r="Y2">
         <v>1.65339172131106</v>
       </c>
       <c r="Z2">
-        <v>3.17837330753305</v>
+        <v>5.54648730328785</v>
       </c>
       <c r="AA2">
         <v>525</v>
@@ -1230,7 +1230,7 @@
         <v>474.6</v>
       </c>
       <c r="AK2">
-        <v>0.06873828092673559</v>
+        <v>0.06872276727524601</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1119137576433478</v>
+        <v>0.1118988363246747</v>
       </c>
       <c r="C2">
-        <v>959.1994437346691</v>
+        <v>959.2192528477892</v>
       </c>
       <c r="D2">
-        <v>835.7994437346691</v>
+        <v>835.8192528477892</v>
       </c>
       <c r="E2">
         <v>-525</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1119137576433478</v>
+        <v>0.1118988363246747</v>
       </c>
       <c r="T2">
         <v>0.9618186075065634</v>
       </c>
       <c r="U2">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V2">
         <v>0.35</v>
       </c>
       <c r="W2">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1116829831650402</v>
+        <v>0.1116590140709825</v>
       </c>
       <c r="C3">
-        <v>950.9091908882534</v>
+        <v>950.9961212736974</v>
       </c>
       <c r="D3">
-        <v>837.5051908882534</v>
+        <v>837.5921212736974</v>
       </c>
       <c r="E3">
         <v>-515.004</v>
@@ -1533,37 +1533,37 @@
         <v>271.9</v>
       </c>
       <c r="M3">
-        <v>0.7052926522687826</v>
+        <v>0.6912982522687826</v>
       </c>
       <c r="N3">
-        <v>271.1947073477312</v>
+        <v>271.2087017477312</v>
       </c>
       <c r="O3">
-        <v>94.91814757170592</v>
+        <v>94.92304561170592</v>
       </c>
       <c r="P3">
-        <v>176.2765597760253</v>
+        <v>176.2856561360253</v>
       </c>
       <c r="Q3">
-        <v>342.8765597760253</v>
+        <v>342.8856561360253</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1123478378702991</v>
+        <v>0.1123328185833721</v>
       </c>
       <c r="T3">
         <v>0.9681335781619097</v>
       </c>
       <c r="U3">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V3">
         <v>0.35</v>
       </c>
       <c r="W3">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>385.5137284152233</v>
+        <v>393.3179334789971</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1114522086867325</v>
+        <v>0.1114191918172902</v>
       </c>
       <c r="C4">
-        <v>942.6259146521729</v>
+        <v>942.7805266004647</v>
       </c>
       <c r="D4">
-        <v>839.2179146521729</v>
+        <v>839.3725266004647</v>
       </c>
       <c r="E4">
         <v>-505.008</v>
@@ -1615,37 +1615,37 @@
         <v>271.9</v>
       </c>
       <c r="M4">
-        <v>1.410585304537565</v>
+        <v>1.382596504537565</v>
       </c>
       <c r="N4">
-        <v>270.4894146954624</v>
+        <v>270.5174034954624</v>
       </c>
       <c r="O4">
-        <v>94.67129514341184</v>
+        <v>94.68109122341184</v>
       </c>
       <c r="P4">
-        <v>175.8181195520506</v>
+        <v>175.8363122720506</v>
       </c>
       <c r="Q4">
-        <v>342.4181195520506</v>
+        <v>342.4363122720506</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1127907768773922</v>
+        <v>0.1127756576228592</v>
       </c>
       <c r="T4">
         <v>0.9745774257694056</v>
       </c>
       <c r="U4">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V4">
         <v>0.35</v>
       </c>
       <c r="W4">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>192.7568642076117</v>
+        <v>196.6589667394985</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1112214342084249</v>
+        <v>0.1111793695635979</v>
       </c>
       <c r="C5">
-        <v>934.3496579162836</v>
+        <v>934.5725169923062</v>
       </c>
       <c r="D5">
-        <v>840.9376579162837</v>
+        <v>841.1605169923062</v>
       </c>
       <c r="E5">
         <v>-495.012</v>
@@ -1697,37 +1697,37 @@
         <v>271.9</v>
       </c>
       <c r="M5">
-        <v>2.115877956806348</v>
+        <v>2.073894756806347</v>
       </c>
       <c r="N5">
-        <v>269.7841220431936</v>
+        <v>269.8261052431936</v>
       </c>
       <c r="O5">
-        <v>94.42444271511776</v>
+        <v>94.43913683511776</v>
       </c>
       <c r="P5">
-        <v>175.3596793280759</v>
+        <v>175.3869684080759</v>
       </c>
       <c r="Q5">
-        <v>341.9596793280758</v>
+        <v>341.9869684080759</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1132428486475182</v>
+        <v>0.1132276273641914</v>
       </c>
       <c r="T5">
         <v>0.9811541362141696</v>
       </c>
       <c r="U5">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V5">
         <v>0.35</v>
       </c>
       <c r="W5">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>128.5045761384078</v>
+        <v>131.1059778263324</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1109906597301173</v>
+        <v>0.1109395473099056</v>
       </c>
       <c r="C6">
-        <v>926.0804639227274</v>
+        <v>926.3721410247009</v>
       </c>
       <c r="D6">
-        <v>842.6644639227275</v>
+        <v>842.956141024701</v>
       </c>
       <c r="E6">
         <v>-485.016</v>
@@ -1779,37 +1779,37 @@
         <v>271.9</v>
       </c>
       <c r="M6">
-        <v>2.82117060907513</v>
+        <v>2.76519300907513</v>
       </c>
       <c r="N6">
-        <v>269.0788293909249</v>
+        <v>269.1348069909249</v>
       </c>
       <c r="O6">
-        <v>94.17759028682369</v>
+        <v>94.19718244682369</v>
       </c>
       <c r="P6">
-        <v>174.9012391041012</v>
+        <v>174.9376245441012</v>
       </c>
       <c r="Q6">
-        <v>341.5012391041012</v>
+        <v>341.5376245441012</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1137043385795218</v>
+        <v>0.1136890131418014</v>
       </c>
       <c r="T6">
         <v>0.9878678614598663</v>
       </c>
       <c r="U6">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V6">
         <v>0.35</v>
       </c>
       <c r="W6">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>96.37843210380584</v>
+        <v>98.32948336974927</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1107598852518096</v>
+        <v>0.1106997250562134</v>
       </c>
       <c r="C7">
-        <v>917.8183762695556</v>
+        <v>918.1794476887922</v>
       </c>
       <c r="D7">
-        <v>844.3983762695557</v>
+        <v>844.7594476887922</v>
       </c>
       <c r="E7">
         <v>-475.02</v>
@@ -1861,37 +1861,37 @@
         <v>271.9</v>
       </c>
       <c r="M7">
-        <v>3.526463261343913</v>
+        <v>3.456491261343913</v>
       </c>
       <c r="N7">
-        <v>268.3735367386561</v>
+        <v>268.4435087386561</v>
       </c>
       <c r="O7">
-        <v>93.93073785852962</v>
+        <v>93.95522805852963</v>
       </c>
       <c r="P7">
-        <v>174.4427988801264</v>
+        <v>174.4882806801265</v>
       </c>
       <c r="Q7">
-        <v>341.0427988801264</v>
+        <v>341.0882806801264</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1141755440890413</v>
+        <v>0.1141601123042031</v>
       </c>
       <c r="T7">
         <v>0.9947229282896827</v>
       </c>
       <c r="U7">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V7">
         <v>0.35</v>
       </c>
       <c r="W7">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>77.10274568304466</v>
+        <v>78.66358669579942</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.110529110773502</v>
+        <v>0.1104599028025211</v>
       </c>
       <c r="C8">
-        <v>909.5634389143978</v>
+        <v>909.9944863958412</v>
       </c>
       <c r="D8">
-        <v>846.1394389143978</v>
+        <v>846.5704863958413</v>
       </c>
       <c r="E8">
         <v>-465.024</v>
@@ -1943,37 +1943,37 @@
         <v>271.9</v>
       </c>
       <c r="M8">
-        <v>4.231755913612695</v>
+        <v>4.147789513612695</v>
       </c>
       <c r="N8">
-        <v>267.6682440863873</v>
+        <v>267.7522104863873</v>
       </c>
       <c r="O8">
-        <v>93.68388543023555</v>
+        <v>93.71327367023555</v>
       </c>
       <c r="P8">
-        <v>173.9843586561518</v>
+        <v>174.0389368161518</v>
       </c>
       <c r="Q8">
-        <v>340.5843586561517</v>
+        <v>340.6389368161517</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1146567752476995</v>
+        <v>0.1146412348530389</v>
       </c>
       <c r="T8">
         <v>1.00172384760524</v>
       </c>
       <c r="U8">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V8">
         <v>0.35</v>
       </c>
       <c r="W8">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>64.25228806920389</v>
+        <v>65.55298891316619</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1102983362951944</v>
+        <v>0.1102200805488288</v>
       </c>
       <c r="C9">
-        <v>901.3156961781779</v>
+        <v>901.8173069817421</v>
       </c>
       <c r="D9">
-        <v>847.8876961781779</v>
+        <v>848.3893069817422</v>
       </c>
       <c r="E9">
         <v>-455.028</v>
@@ -2025,37 +2025,37 @@
         <v>271.9</v>
       </c>
       <c r="M9">
-        <v>4.937048565881478</v>
+        <v>4.839087765881478</v>
       </c>
       <c r="N9">
-        <v>266.9629514341185</v>
+        <v>267.0609122341185</v>
       </c>
       <c r="O9">
-        <v>93.43703300194147</v>
+        <v>93.47131928194148</v>
       </c>
       <c r="P9">
-        <v>173.525918432177</v>
+        <v>173.589592952177</v>
       </c>
       <c r="Q9">
-        <v>340.1259184321771</v>
+        <v>340.189592952177</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1151483554635331</v>
+        <v>0.1151327041233551</v>
       </c>
       <c r="T9">
         <v>1.008875324325433</v>
       </c>
       <c r="U9">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V9">
         <v>0.35</v>
       </c>
       <c r="W9">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>55.07338977360332</v>
+        <v>56.1882762112853</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1100675618168868</v>
+        <v>0.1099802582951366</v>
       </c>
       <c r="C10">
-        <v>893.0751927488728</v>
+        <v>893.6479597115915</v>
       </c>
       <c r="D10">
-        <v>849.6431927488728</v>
+        <v>850.2159597115915</v>
       </c>
       <c r="E10">
         <v>-445.032</v>
@@ -2107,37 +2107,37 @@
         <v>271.9</v>
       </c>
       <c r="M10">
-        <v>5.642341218150261</v>
+        <v>5.530386018150261</v>
       </c>
       <c r="N10">
-        <v>266.2576587818497</v>
+        <v>266.3696139818497</v>
       </c>
       <c r="O10">
-        <v>93.1901805736474</v>
+        <v>93.2293648936474</v>
       </c>
       <c r="P10">
-        <v>173.0674782082023</v>
+        <v>173.1402490882023</v>
       </c>
       <c r="Q10">
-        <v>339.6674782082023</v>
+        <v>339.7402490882023</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1156506222057979</v>
+        <v>0.1156348575082433</v>
       </c>
       <c r="T10">
         <v>1.016182267930847</v>
       </c>
       <c r="U10">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V10">
         <v>0.35</v>
       </c>
       <c r="W10">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>48.18921605190292</v>
+        <v>49.16474168487464</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1098367873385791</v>
+        <v>0.1097404360414443</v>
       </c>
       <c r="C11">
-        <v>884.8419736853236</v>
+        <v>885.4864952843202</v>
       </c>
       <c r="D11">
-        <v>851.4059736853237</v>
+        <v>852.0504952843202</v>
       </c>
       <c r="E11">
         <v>-435.036</v>
@@ -2189,37 +2189,37 @@
         <v>271.9</v>
       </c>
       <c r="M11">
-        <v>6.347633870419043</v>
+        <v>6.221684270419042</v>
       </c>
       <c r="N11">
-        <v>265.5523661295809</v>
+        <v>265.678315729581</v>
       </c>
       <c r="O11">
-        <v>92.94332814535332</v>
+        <v>92.98741050535332</v>
       </c>
       <c r="P11">
-        <v>172.6090379842276</v>
+        <v>172.6909052242276</v>
       </c>
       <c r="Q11">
-        <v>339.2090379842276</v>
+        <v>339.2909052242276</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.116163927777563</v>
+        <v>0.116148047231261</v>
       </c>
       <c r="T11">
         <v>1.023649803703414</v>
       </c>
       <c r="U11">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V11">
         <v>0.35</v>
       </c>
       <c r="W11">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>42.83485871280259</v>
+        <v>43.70199260877747</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1096060128602715</v>
+        <v>0.109500613787752</v>
       </c>
       <c r="C12">
-        <v>876.6160844210873</v>
+        <v>877.3329648373831</v>
       </c>
       <c r="D12">
-        <v>853.1760844210874</v>
+        <v>853.8929648373831</v>
       </c>
       <c r="E12">
         <v>-425.04</v>
@@ -2271,37 +2271,37 @@
         <v>271.9</v>
       </c>
       <c r="M12">
-        <v>7.052926522687826</v>
+        <v>6.912982522687826</v>
       </c>
       <c r="N12">
-        <v>264.8470734773122</v>
+        <v>264.9870174773122</v>
       </c>
       <c r="O12">
-        <v>92.69647571705926</v>
+        <v>92.74545611705926</v>
       </c>
       <c r="P12">
-        <v>172.1505977602529</v>
+        <v>172.2415613602529</v>
       </c>
       <c r="Q12">
-        <v>338.7505977602529</v>
+        <v>338.8415613602529</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1166886401398118</v>
+        <v>0.1166726411703457</v>
       </c>
       <c r="T12">
         <v>1.031283284715371</v>
       </c>
       <c r="U12">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V12">
         <v>0.35</v>
       </c>
       <c r="W12">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>38.55137284152233</v>
+        <v>39.33179334789971</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1093752383819639</v>
+        <v>0.1092607915340597</v>
       </c>
       <c r="C13">
-        <v>868.3975707683417</v>
+        <v>869.1874199515117</v>
       </c>
       <c r="D13">
-        <v>854.9535707683417</v>
+        <v>855.7434199515118</v>
       </c>
       <c r="E13">
         <v>-415.044</v>
@@ -2353,37 +2353,37 @@
         <v>271.9</v>
       </c>
       <c r="M13">
-        <v>7.758219174956608</v>
+        <v>7.604280774956608</v>
       </c>
       <c r="N13">
-        <v>264.1417808250434</v>
+        <v>264.2957192250433</v>
       </c>
       <c r="O13">
-        <v>92.44962328876518</v>
+        <v>92.50350172876516</v>
       </c>
       <c r="P13">
-        <v>171.6921575362782</v>
+        <v>171.7922174962782</v>
       </c>
       <c r="Q13">
-        <v>338.2921575362782</v>
+        <v>338.3922174962781</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1172251437910999</v>
+        <v>0.117209023737275</v>
       </c>
       <c r="T13">
         <v>1.039088304626473</v>
       </c>
       <c r="U13">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V13">
         <v>0.35</v>
       </c>
       <c r="W13">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>35.04670258320213</v>
+        <v>35.75617577081791</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1091444639036562</v>
+        <v>0.1090209692803674</v>
       </c>
       <c r="C14">
-        <v>860.1864789218379</v>
+        <v>861.0499126555269</v>
       </c>
       <c r="D14">
-        <v>856.7384789218379</v>
+        <v>857.6019126555269</v>
       </c>
       <c r="E14">
         <v>-405.048</v>
@@ -2435,37 +2435,37 @@
         <v>271.9</v>
       </c>
       <c r="M14">
-        <v>8.463511827225391</v>
+        <v>8.29557902722539</v>
       </c>
       <c r="N14">
-        <v>263.4364881727746</v>
+        <v>263.6044209727746</v>
       </c>
       <c r="O14">
-        <v>92.20277086047111</v>
+        <v>92.2615473404711</v>
       </c>
       <c r="P14">
-        <v>171.2337173123035</v>
+        <v>171.3428736323035</v>
       </c>
       <c r="Q14">
-        <v>337.8337173123035</v>
+        <v>337.9428736323034</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.11777384070719</v>
+        <v>0.1177575968170891</v>
       </c>
       <c r="T14">
         <v>1.047070711353736</v>
       </c>
       <c r="U14">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V14">
         <v>0.35</v>
       </c>
       <c r="W14">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>32.12614403460194</v>
+        <v>32.77649445658309</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1089136894253486</v>
+        <v>0.1087811470266752</v>
       </c>
       <c r="C15">
-        <v>851.9828554629014</v>
+        <v>852.9204954312145</v>
       </c>
       <c r="D15">
-        <v>858.5308554629014</v>
+        <v>859.4684954312145</v>
       </c>
       <c r="E15">
         <v>-395.052</v>
@@ -2517,37 +2517,37 @@
         <v>271.9</v>
       </c>
       <c r="M15">
-        <v>9.168804479494174</v>
+        <v>8.986877279494173</v>
       </c>
       <c r="N15">
-        <v>262.7311955205058</v>
+        <v>262.9131227205058</v>
       </c>
       <c r="O15">
-        <v>91.95591843217703</v>
+        <v>92.01959295217702</v>
       </c>
       <c r="P15">
-        <v>170.7752770883288</v>
+        <v>170.8935297683288</v>
       </c>
       <c r="Q15">
-        <v>337.3752770883287</v>
+        <v>337.4935297683288</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1183351513454891</v>
+        <v>0.1183187807723012</v>
       </c>
       <c r="T15">
         <v>1.055236621683925</v>
       </c>
       <c r="U15">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V15">
         <v>0.35</v>
       </c>
       <c r="W15">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>29.65490218578641</v>
+        <v>30.25522565223054</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.108682914947041</v>
+        <v>0.1085413247729829</v>
       </c>
       <c r="C16">
-        <v>843.7867473634851</v>
+        <v>844.7992212182676</v>
       </c>
       <c r="D16">
-        <v>860.3307473634852</v>
+        <v>861.3432212182677</v>
       </c>
       <c r="E16">
         <v>-385.056</v>
@@ -2599,37 +2599,37 @@
         <v>271.9</v>
       </c>
       <c r="M16">
-        <v>9.874097131762957</v>
+        <v>9.678175531762957</v>
       </c>
       <c r="N16">
-        <v>262.025902868237</v>
+        <v>262.221824468237</v>
       </c>
       <c r="O16">
-        <v>91.70906600388295</v>
+        <v>91.77763856388295</v>
       </c>
       <c r="P16">
-        <v>170.3168368643541</v>
+        <v>170.4441859043541</v>
       </c>
       <c r="Q16">
-        <v>336.9168368643541</v>
+        <v>337.0441859043541</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1189095157195625</v>
+        <v>0.1188930155171694</v>
       </c>
       <c r="T16">
         <v>1.063592436905514</v>
       </c>
       <c r="U16">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V16">
         <v>0.35</v>
       </c>
       <c r="W16">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>27.53669488680167</v>
+        <v>28.09413810564265</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1084521404687333</v>
+        <v>0.1083015025192906</v>
       </c>
       <c r="C17">
-        <v>835.5982019902729</v>
+        <v>836.6861434192899</v>
       </c>
       <c r="D17">
-        <v>862.1382019902728</v>
+        <v>863.2261434192899</v>
       </c>
       <c r="E17">
         <v>-375.06</v>
@@ -2681,37 +2681,37 @@
         <v>271.9</v>
       </c>
       <c r="M17">
-        <v>10.57938978403174</v>
+        <v>10.36947378403174</v>
       </c>
       <c r="N17">
-        <v>261.3206102159683</v>
+        <v>261.5305262159682</v>
       </c>
       <c r="O17">
-        <v>91.46221357558889</v>
+        <v>91.53568417558887</v>
       </c>
       <c r="P17">
-        <v>169.8583966403794</v>
+        <v>169.9948420403794</v>
       </c>
       <c r="Q17">
-        <v>336.4583966403794</v>
+        <v>336.5948420403794</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1194973945494965</v>
+        <v>0.1194807616677992</v>
       </c>
       <c r="T17">
         <v>1.072144859544081</v>
       </c>
       <c r="U17">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V17">
         <v>0.35</v>
       </c>
       <c r="W17">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>25.70091522768156</v>
+        <v>26.22119556526647</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1082213659904257</v>
+        <v>0.1080616802655983</v>
       </c>
       <c r="C18">
-        <v>827.4172671088327</v>
+        <v>828.5813159048664</v>
       </c>
       <c r="D18">
-        <v>863.9532671088327</v>
+        <v>865.1173159048665</v>
       </c>
       <c r="E18">
         <v>-365.064</v>
@@ -2763,37 +2763,37 @@
         <v>271.9</v>
       </c>
       <c r="M18">
-        <v>11.28468243630052</v>
+        <v>11.06077203630052</v>
       </c>
       <c r="N18">
-        <v>260.6153175636995</v>
+        <v>260.8392279636994</v>
       </c>
       <c r="O18">
-        <v>91.21536114729481</v>
+        <v>91.29372978729479</v>
       </c>
       <c r="P18">
-        <v>169.3999564164047</v>
+        <v>169.5454981764046</v>
       </c>
       <c r="Q18">
-        <v>335.9999564164046</v>
+        <v>336.1454981764047</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.120099270494429</v>
+        <v>0.1200825017743964</v>
       </c>
       <c r="T18">
         <v>1.08090091129309</v>
       </c>
       <c r="U18">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V18">
         <v>0.35</v>
       </c>
       <c r="W18">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>24.09460802595146</v>
+        <v>24.58237084243732</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1079905915121181</v>
+        <v>0.1078218580119061</v>
       </c>
       <c r="C19">
-        <v>819.2439908878272</v>
+        <v>820.4847930187027</v>
       </c>
       <c r="D19">
-        <v>865.7759908878272</v>
+        <v>867.0167930187027</v>
       </c>
       <c r="E19">
         <v>-355.068</v>
@@ -2845,37 +2845,37 @@
         <v>271.9</v>
       </c>
       <c r="M19">
-        <v>11.9899750885693</v>
+        <v>11.75207028856931</v>
       </c>
       <c r="N19">
-        <v>259.9100249114307</v>
+        <v>260.1479297114307</v>
       </c>
       <c r="O19">
-        <v>90.96850871900074</v>
+        <v>91.05177539900073</v>
       </c>
       <c r="P19">
-        <v>168.94151619243</v>
+        <v>169.0961543124299</v>
       </c>
       <c r="Q19">
-        <v>335.54151619243</v>
+        <v>335.6961543124299</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.120715649474179</v>
+        <v>0.1206987416425983</v>
       </c>
       <c r="T19">
         <v>1.089867952240871</v>
       </c>
       <c r="U19">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>22.67727814207196</v>
+        <v>23.1363490281763</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1077598170338104</v>
+        <v>0.1075820357582138</v>
       </c>
       <c r="C20">
-        <v>811.0784219032723</v>
+        <v>812.3966295828277</v>
       </c>
       <c r="D20">
-        <v>867.6064219032723</v>
+        <v>868.9246295828277</v>
       </c>
       <c r="E20">
         <v>-345.072</v>
@@ -2927,37 +2927,37 @@
         <v>271.9</v>
       </c>
       <c r="M20">
-        <v>12.69526774083809</v>
+        <v>12.44336854083808</v>
       </c>
       <c r="N20">
-        <v>259.2047322591619</v>
+        <v>259.4566314591619</v>
       </c>
       <c r="O20">
-        <v>90.72165629070666</v>
+        <v>90.80982101070666</v>
       </c>
       <c r="P20">
-        <v>168.4830759684552</v>
+        <v>168.6468104484552</v>
       </c>
       <c r="Q20">
-        <v>335.0830759684552</v>
+        <v>335.2468104484552</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1213470620875816</v>
+        <v>0.1213300117514881</v>
       </c>
       <c r="T20">
         <v>1.099053701504451</v>
       </c>
       <c r="U20">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V20">
         <v>0.35</v>
       </c>
       <c r="W20">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>21.4174293564013</v>
+        <v>21.85099630438873</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1075290425555028</v>
+        <v>0.1073422135045215</v>
       </c>
       <c r="C21">
-        <v>802.9206091428548</v>
+        <v>804.3168809028704</v>
       </c>
       <c r="D21">
-        <v>869.4446091428548</v>
+        <v>870.8408809028704</v>
       </c>
       <c r="E21">
         <v>-335.076</v>
@@ -3009,37 +3009,37 @@
         <v>271.9</v>
       </c>
       <c r="M21">
-        <v>13.40056039310687</v>
+        <v>13.13466679310687</v>
       </c>
       <c r="N21">
-        <v>258.4994396068931</v>
+        <v>258.7653332068931</v>
       </c>
       <c r="O21">
-        <v>90.47480386241259</v>
+        <v>90.56786662241258</v>
       </c>
       <c r="P21">
-        <v>168.0246357444805</v>
+        <v>168.1974665844805</v>
       </c>
       <c r="Q21">
-        <v>334.6246357444805</v>
+        <v>334.7974665844805</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1219940651358829</v>
+        <v>0.1219768687766468</v>
       </c>
       <c r="T21">
         <v>1.108466259391824</v>
       </c>
       <c r="U21">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V21">
         <v>0.35</v>
       </c>
       <c r="W21">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>20.29019623238018</v>
+        <v>20.70094386731564</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1072982680771952</v>
+        <v>0.1071023912508293</v>
       </c>
       <c r="C22">
-        <v>794.7706020103003</v>
+        <v>796.2456027734029</v>
       </c>
       <c r="D22">
-        <v>871.2906020103003</v>
+        <v>872.765602773403</v>
       </c>
       <c r="E22">
         <v>-325.08</v>
@@ -3091,37 +3091,37 @@
         <v>271.9</v>
       </c>
       <c r="M22">
-        <v>14.10585304537565</v>
+        <v>13.82596504537565</v>
       </c>
       <c r="N22">
-        <v>257.7941469546244</v>
+        <v>258.0740349546243</v>
       </c>
       <c r="O22">
-        <v>90.22795143411852</v>
+        <v>90.3259122341185</v>
       </c>
       <c r="P22">
-        <v>167.5661955205058</v>
+        <v>167.7481227205058</v>
       </c>
       <c r="Q22">
-        <v>334.1661955205058</v>
+        <v>334.3481227205058</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1226572432603918</v>
+        <v>0.1226398972274344</v>
       </c>
       <c r="T22">
         <v>1.11811413122638</v>
       </c>
       <c r="U22">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V22">
         <v>0.35</v>
       </c>
       <c r="W22">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>19.27568642076117</v>
+        <v>19.66589667394986</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1070674935988876</v>
+        <v>0.106862568997137</v>
       </c>
       <c r="C23">
-        <v>786.6284503298009</v>
+        <v>788.1828514833562</v>
       </c>
       <c r="D23">
-        <v>873.144450329801</v>
+        <v>874.6988514833562</v>
       </c>
       <c r="E23">
         <v>-315.084</v>
@@ -3173,37 +3173,37 @@
         <v>271.9</v>
       </c>
       <c r="M23">
-        <v>14.81114569764443</v>
+        <v>14.51726329764443</v>
       </c>
       <c r="N23">
-        <v>257.0888543023556</v>
+        <v>257.3827367023555</v>
       </c>
       <c r="O23">
-        <v>89.98109900582445</v>
+        <v>90.08395784582443</v>
       </c>
       <c r="P23">
-        <v>167.1077552965311</v>
+        <v>167.2987788565311</v>
       </c>
       <c r="Q23">
-        <v>333.7077552965311</v>
+        <v>333.8987788565311</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1233372107045085</v>
+        <v>0.1233197112086217</v>
       </c>
       <c r="T23">
         <v>1.128006252980799</v>
       </c>
       <c r="U23">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V23">
         <v>0.35</v>
       </c>
       <c r="W23">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.35779659120112</v>
+        <v>18.72942540376177</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1068367191205799</v>
+        <v>0.1066227467434447</v>
       </c>
       <c r="C24">
-        <v>778.4942043504979</v>
+        <v>780.1286838215057</v>
       </c>
       <c r="D24">
-        <v>875.0062043504979</v>
+        <v>876.6406838215057</v>
       </c>
       <c r="E24">
         <v>-305.088</v>
@@ -3255,37 +3255,37 @@
         <v>271.9</v>
       </c>
       <c r="M24">
-        <v>15.51643834991322</v>
+        <v>15.20856154991322</v>
       </c>
       <c r="N24">
-        <v>256.3835616500868</v>
+        <v>256.6914384500868</v>
       </c>
       <c r="O24">
-        <v>89.73424657753037</v>
+        <v>89.84200345753037</v>
       </c>
       <c r="P24">
-        <v>166.6493150725564</v>
+        <v>166.8494349925564</v>
       </c>
       <c r="Q24">
-        <v>333.2493150725564</v>
+        <v>333.4494349925563</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1240346132112949</v>
+        <v>0.1240169563175318</v>
       </c>
       <c r="T24">
         <v>1.138152018882767</v>
       </c>
       <c r="U24">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V24">
         <v>0.35</v>
       </c>
       <c r="W24">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>17.52335129160106</v>
+        <v>17.87808788540896</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1066059446422723</v>
+        <v>0.1063829244897524</v>
       </c>
       <c r="C25">
-        <v>770.3679147510197</v>
+        <v>772.0831570820357</v>
       </c>
       <c r="D25">
-        <v>876.8759147510198</v>
+        <v>878.5911570820357</v>
       </c>
       <c r="E25">
         <v>-295.092</v>
@@ -3337,37 +3337,37 @@
         <v>271.9</v>
       </c>
       <c r="M25">
-        <v>16.221731002182</v>
+        <v>15.899859802182</v>
       </c>
       <c r="N25">
-        <v>255.678268997818</v>
+        <v>256.000140197818</v>
       </c>
       <c r="O25">
-        <v>89.48739414923629</v>
+        <v>89.60004906923629</v>
       </c>
       <c r="P25">
-        <v>166.1908748485817</v>
+        <v>166.4000911285817</v>
       </c>
       <c r="Q25">
-        <v>332.7908748485817</v>
+        <v>333.0000911285817</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1247501300689069</v>
+        <v>0.1247323116890109</v>
       </c>
       <c r="T25">
         <v>1.148561311171799</v>
       </c>
       <c r="U25">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V25">
         <v>0.35</v>
       </c>
       <c r="W25">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>16.76146645283579</v>
+        <v>17.10077971647813</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1063751701639647</v>
+        <v>0.1061431022360601</v>
       </c>
       <c r="C26">
-        <v>762.2496326440843</v>
+        <v>764.04632907017</v>
       </c>
       <c r="D26">
-        <v>878.7536326440843</v>
+        <v>880.5503290701701</v>
       </c>
       <c r="E26">
         <v>-285.096</v>
@@ -3419,37 +3419,37 @@
         <v>271.9</v>
       </c>
       <c r="M26">
-        <v>16.92702365445078</v>
+        <v>16.59115805445078</v>
       </c>
       <c r="N26">
-        <v>254.9729763455492</v>
+        <v>255.3088419455492</v>
       </c>
       <c r="O26">
-        <v>89.24054172094222</v>
+        <v>89.35809468094222</v>
       </c>
       <c r="P26">
-        <v>165.732434624607</v>
+        <v>165.950747264607</v>
       </c>
       <c r="Q26">
-        <v>332.332434624607</v>
+        <v>332.550747264607</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1254844763175087</v>
+        <v>0.1254664922018448</v>
       </c>
       <c r="T26">
         <v>1.159244532205279</v>
       </c>
       <c r="U26">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V26">
         <v>0.35</v>
       </c>
       <c r="W26">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.06307201730097</v>
+        <v>16.38824722829155</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.106144395685657</v>
+        <v>0.1059032799823679</v>
       </c>
       <c r="C27">
-        <v>754.1394095811526</v>
+        <v>756.0182581078858</v>
       </c>
       <c r="D27">
-        <v>880.6394095811526</v>
+        <v>882.5182581078858</v>
       </c>
       <c r="E27">
         <v>-275.1</v>
@@ -3501,37 +3501,37 @@
         <v>271.9</v>
       </c>
       <c r="M27">
-        <v>17.63231630671956</v>
+        <v>17.28245630671956</v>
       </c>
       <c r="N27">
-        <v>254.2676836932804</v>
+        <v>254.6175436932804</v>
       </c>
       <c r="O27">
-        <v>88.99368929264814</v>
+        <v>89.11614029264814</v>
       </c>
       <c r="P27">
-        <v>165.2739944006323</v>
+        <v>165.5014034006323</v>
       </c>
       <c r="Q27">
-        <v>331.8739944006322</v>
+        <v>332.1014034006323</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1262384051327398</v>
+        <v>0.1262202508616876</v>
       </c>
       <c r="T27">
         <v>1.170212639132986</v>
       </c>
       <c r="U27">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V27">
         <v>0.35</v>
       </c>
       <c r="W27">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.42054913660893</v>
+        <v>15.73271733915989</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1059136212073494</v>
+        <v>0.1056634577286756</v>
       </c>
       <c r="C28">
-        <v>746.0372975571495</v>
+        <v>747.9990030396993</v>
       </c>
       <c r="D28">
-        <v>882.5332975571495</v>
+        <v>884.4950030396994</v>
       </c>
       <c r="E28">
         <v>-265.104</v>
@@ -3583,37 +3583,37 @@
         <v>271.9</v>
       </c>
       <c r="M28">
-        <v>18.33760895898835</v>
+        <v>17.97375455898835</v>
       </c>
       <c r="N28">
-        <v>253.5623910410116</v>
+        <v>253.9262454410116</v>
       </c>
       <c r="O28">
-        <v>88.74683686435407</v>
+        <v>88.87418590435406</v>
       </c>
       <c r="P28">
-        <v>164.8155541766576</v>
+        <v>165.0520595366576</v>
       </c>
       <c r="Q28">
-        <v>331.4155541766576</v>
+        <v>331.6520595366576</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1270127104024367</v>
+        <v>0.1269943813772018</v>
       </c>
       <c r="T28">
         <v>1.181477181383062</v>
       </c>
       <c r="U28">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V28">
         <v>0.35</v>
       </c>
       <c r="W28">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>14.8274510928932</v>
+        <v>15.12761282611527</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1056828467290418</v>
+        <v>0.1054236354749833</v>
       </c>
       <c r="C29">
-        <v>737.9433490152405</v>
+        <v>739.9886232385325</v>
       </c>
       <c r="D29">
-        <v>884.4353490152406</v>
+        <v>886.4806232385324</v>
       </c>
       <c r="E29">
         <v>-255.108</v>
@@ -3665,37 +3665,37 @@
         <v>271.9</v>
       </c>
       <c r="M29">
-        <v>19.04290161125713</v>
+        <v>18.66505281125713</v>
       </c>
       <c r="N29">
-        <v>252.8570983887429</v>
+        <v>253.2349471887428</v>
       </c>
       <c r="O29">
-        <v>88.49998443605999</v>
+        <v>88.63223151605999</v>
       </c>
       <c r="P29">
-        <v>164.3571139526829</v>
+        <v>164.6027156726828</v>
       </c>
       <c r="Q29">
-        <v>330.9571139526829</v>
+        <v>331.2027156726829</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.127808229515139</v>
+        <v>0.1277897209479356</v>
       </c>
       <c r="T29">
         <v>1.193050341229032</v>
       </c>
       <c r="U29">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V29">
         <v>0.35</v>
       </c>
       <c r="W29">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.27828623760086</v>
+        <v>14.56733086959248</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1054520722507341</v>
+        <v>0.1051838132212911</v>
       </c>
       <c r="C30">
-        <v>729.8576168516747</v>
+        <v>731.9871786116549</v>
       </c>
       <c r="D30">
-        <v>886.3456168516748</v>
+        <v>888.475178611655</v>
       </c>
       <c r="E30">
         <v>-245.112</v>
@@ -3747,37 +3747,37 @@
         <v>271.9</v>
       </c>
       <c r="M30">
-        <v>19.74819426352591</v>
+        <v>19.35635106352591</v>
       </c>
       <c r="N30">
-        <v>252.1518057364741</v>
+        <v>252.5436489364741</v>
       </c>
       <c r="O30">
-        <v>88.25313200776593</v>
+        <v>88.39027712776591</v>
       </c>
       <c r="P30">
-        <v>163.8986737287082</v>
+        <v>164.1533718087081</v>
       </c>
       <c r="Q30">
-        <v>330.4986737287081</v>
+        <v>330.7533718087082</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1286258463809718</v>
+        <v>0.1286071532845231</v>
       </c>
       <c r="T30">
         <v>1.204944977737389</v>
       </c>
       <c r="U30">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V30">
         <v>0.35</v>
       </c>
       <c r="W30">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>13.76834744340083</v>
+        <v>14.04706905282132</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1052212977724265</v>
+        <v>0.1049439909675988</v>
       </c>
       <c r="C31">
-        <v>721.780154420686</v>
+        <v>723.9947296067124</v>
       </c>
       <c r="D31">
-        <v>888.2641544206861</v>
+        <v>890.4787296067125</v>
       </c>
       <c r="E31">
         <v>-235.116</v>
@@ -3829,37 +3829,37 @@
         <v>271.9</v>
       </c>
       <c r="M31">
-        <v>20.4534869157947</v>
+        <v>20.04764931579469</v>
       </c>
       <c r="N31">
-        <v>251.4465130842053</v>
+        <v>251.8523506842053</v>
       </c>
       <c r="O31">
-        <v>88.00627957947185</v>
+        <v>88.14832273947184</v>
       </c>
       <c r="P31">
-        <v>163.4402335047334</v>
+        <v>163.7040279447334</v>
       </c>
       <c r="Q31">
-        <v>330.0402335047335</v>
+        <v>330.3040279447334</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1294664947078141</v>
+        <v>0.129447611884113</v>
       </c>
       <c r="T31">
         <v>1.217174674429081</v>
       </c>
       <c r="U31">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V31">
         <v>0.35</v>
       </c>
       <c r="W31">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.29357684190425</v>
+        <v>13.56268736134473</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1049905232941189</v>
+        <v>0.1047041687139065</v>
       </c>
       <c r="C32">
-        <v>713.7110155394614</v>
+        <v>716.0113372178299</v>
       </c>
       <c r="D32">
-        <v>890.1910155394614</v>
+        <v>892.4913372178299</v>
       </c>
       <c r="E32">
         <v>-225.12</v>
@@ -3911,37 +3911,37 @@
         <v>271.9</v>
       </c>
       <c r="M32">
-        <v>21.15877956806348</v>
+        <v>20.73894756806348</v>
       </c>
       <c r="N32">
-        <v>250.7412204319365</v>
+        <v>251.1610524319365</v>
       </c>
       <c r="O32">
-        <v>87.75942715117777</v>
+        <v>87.90636835117778</v>
       </c>
       <c r="P32">
-        <v>162.9817932807587</v>
+        <v>163.2546840807587</v>
       </c>
       <c r="Q32">
-        <v>329.5817932807587</v>
+        <v>329.8546840807587</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1303311615582804</v>
+        <v>0.1303120835865484</v>
       </c>
       <c r="T32">
         <v>1.229753791026249</v>
       </c>
       <c r="U32">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V32">
         <v>0.35</v>
       </c>
       <c r="W32">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>12.85045761384078</v>
+        <v>13.11059778263324</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1049813988158112</v>
+        <v>0.1047665964602142</v>
       </c>
       <c r="C33">
-        <v>703.7913725644437</v>
+        <v>705.4905632150862</v>
       </c>
       <c r="D33">
-        <v>890.2673725644438</v>
+        <v>891.9665632150862</v>
       </c>
       <c r="E33">
         <v>-215.124</v>
@@ -3993,37 +3993,37 @@
         <v>271.9</v>
       </c>
       <c r="M33">
-        <v>22.20493582033226</v>
+        <v>21.89505982033226</v>
       </c>
       <c r="N33">
-        <v>249.6950641796677</v>
+        <v>250.0049401796677</v>
       </c>
       <c r="O33">
-        <v>87.3932724628837</v>
+        <v>87.5017290628837</v>
       </c>
       <c r="P33">
-        <v>162.301791716784</v>
+        <v>162.503211116784</v>
       </c>
       <c r="Q33">
-        <v>328.901791716784</v>
+        <v>329.103211116784</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1312208912160066</v>
+        <v>0.131201612439779</v>
       </c>
       <c r="T33">
         <v>1.242697519698698</v>
       </c>
       <c r="U33">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V33">
         <v>0.35</v>
       </c>
       <c r="W33">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>12.24502525925029</v>
+        <v>12.41832642756735</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1047577743375036</v>
+        <v>0.1045365242065219</v>
       </c>
       <c r="C34">
-        <v>695.6708484661249</v>
+        <v>697.431634465521</v>
       </c>
       <c r="D34">
-        <v>892.142848466125</v>
+        <v>893.903634465521</v>
       </c>
       <c r="E34">
         <v>-205.128</v>
@@ -4075,37 +4075,37 @@
         <v>271.9</v>
       </c>
       <c r="M34">
-        <v>22.92122407260104</v>
+        <v>22.60135207260104</v>
       </c>
       <c r="N34">
-        <v>248.9787759273989</v>
+        <v>249.2986479273989</v>
       </c>
       <c r="O34">
-        <v>87.14257157458962</v>
+        <v>87.25452677458962</v>
       </c>
       <c r="P34">
-        <v>161.8362043528093</v>
+        <v>162.0441211528093</v>
       </c>
       <c r="Q34">
-        <v>328.4362043528093</v>
+        <v>328.6441211528094</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1321367893930777</v>
+        <v>0.13211730390634</v>
       </c>
       <c r="T34">
         <v>1.256021946273277</v>
       </c>
       <c r="U34">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V34">
         <v>0.35</v>
       </c>
       <c r="W34">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.86236821989872</v>
+        <v>12.03025372670587</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.104534149859196</v>
+        <v>0.1043064519528296</v>
       </c>
       <c r="C35">
-        <v>687.5582429674037</v>
+        <v>689.3811374478548</v>
       </c>
       <c r="D35">
-        <v>894.0262429674037</v>
+        <v>895.8491374478549</v>
       </c>
       <c r="E35">
         <v>-195.132</v>
@@ -4157,37 +4157,37 @@
         <v>271.9</v>
       </c>
       <c r="M35">
-        <v>23.63751232486982</v>
+        <v>23.30764432486982</v>
       </c>
       <c r="N35">
-        <v>248.2624876751302</v>
+        <v>248.5923556751302</v>
       </c>
       <c r="O35">
-        <v>86.89187068629555</v>
+        <v>87.00732448629556</v>
       </c>
       <c r="P35">
-        <v>161.3706169888346</v>
+        <v>161.5850311888346</v>
       </c>
       <c r="Q35">
-        <v>327.9706169888346</v>
+        <v>328.1850311888346</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1330800278142405</v>
+        <v>0.1330603294465296</v>
       </c>
       <c r="T35">
         <v>1.269744116924709</v>
       </c>
       <c r="U35">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V35">
         <v>0.35</v>
       </c>
       <c r="W35">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.50290251626542</v>
+        <v>11.66570058347236</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1043105253808883</v>
+        <v>0.1040763796991374</v>
       </c>
       <c r="C36">
-        <v>679.4536063250235</v>
+        <v>681.339127334945</v>
       </c>
       <c r="D36">
-        <v>895.9176063250236</v>
+        <v>897.8031273349451</v>
       </c>
       <c r="E36">
         <v>-185.136</v>
@@ -4239,37 +4239,37 @@
         <v>271.9</v>
       </c>
       <c r="M36">
-        <v>24.3538005771386</v>
+        <v>24.0139365771386</v>
       </c>
       <c r="N36">
-        <v>247.5461994228614</v>
+        <v>247.8860634228614</v>
       </c>
       <c r="O36">
-        <v>86.64116979800147</v>
+        <v>86.76012219800148</v>
       </c>
       <c r="P36">
-        <v>160.9050296248599</v>
+        <v>161.1259412248599</v>
       </c>
       <c r="Q36">
-        <v>327.5050296248599</v>
+        <v>327.7259412248599</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1340518492178627</v>
+        <v>0.1340319315182401</v>
       </c>
       <c r="T36">
         <v>1.283882110929216</v>
       </c>
       <c r="U36">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V36">
         <v>0.35</v>
       </c>
       <c r="W36">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.16458185402232</v>
+        <v>11.32259174278199</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1040869009025807</v>
+        <v>0.1038463074454451</v>
       </c>
       <c r="C37">
-        <v>671.356989221913</v>
+        <v>673.3056597820643</v>
       </c>
       <c r="D37">
-        <v>897.816989221913</v>
+        <v>899.7656597820643</v>
       </c>
       <c r="E37">
         <v>-175.14</v>
@@ -4321,37 +4321,37 @@
         <v>271.9</v>
       </c>
       <c r="M37">
-        <v>25.07008882940739</v>
+        <v>24.72022882940739</v>
       </c>
       <c r="N37">
-        <v>246.8299111705926</v>
+        <v>247.1797711705926</v>
       </c>
       <c r="O37">
-        <v>86.39046890970741</v>
+        <v>86.51291990970741</v>
       </c>
       <c r="P37">
-        <v>160.4394422608852</v>
+        <v>160.6668512608852</v>
       </c>
       <c r="Q37">
-        <v>327.0394422608852</v>
+        <v>327.2668512608852</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1350535728185195</v>
+        <v>0.1350334290383109</v>
       </c>
       <c r="T37">
         <v>1.298455120133861</v>
       </c>
       <c r="U37">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V37">
         <v>0.35</v>
       </c>
       <c r="W37">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.84559380105025</v>
+        <v>10.99908912155965</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1038632764242731</v>
+        <v>0.1036162351917528</v>
       </c>
       <c r="C38">
-        <v>663.2684427717146</v>
+        <v>665.2807909321848</v>
       </c>
       <c r="D38">
-        <v>899.7244427717146</v>
+        <v>901.7367909321848</v>
       </c>
       <c r="E38">
         <v>-165.144</v>
@@ -4403,37 +4403,37 @@
         <v>271.9</v>
       </c>
       <c r="M38">
-        <v>25.78637708167617</v>
+        <v>25.42652108167617</v>
       </c>
       <c r="N38">
-        <v>246.1136229183238</v>
+        <v>246.4734789183238</v>
       </c>
       <c r="O38">
-        <v>86.13976802141333</v>
+        <v>86.26571762141333</v>
       </c>
       <c r="P38">
-        <v>159.9738548969105</v>
+        <v>160.2077612969105</v>
       </c>
       <c r="Q38">
-        <v>326.5738548969105</v>
+        <v>326.8077612969105</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1360866002816968</v>
+        <v>0.1360662233558839</v>
       </c>
       <c r="T38">
         <v>1.313483535876151</v>
       </c>
       <c r="U38">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V38">
         <v>0.35</v>
       </c>
       <c r="W38">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.54432730657664</v>
+        <v>10.69355886818299</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1036396519459655</v>
+        <v>0.1033861629380605</v>
       </c>
       <c r="C39">
-        <v>655.1880185233672</v>
+        <v>657.2645774213324</v>
       </c>
       <c r="D39">
-        <v>901.6400185233673</v>
+        <v>903.7165774213324</v>
       </c>
       <c r="E39">
         <v>-155.148</v>
@@ -4485,37 +4485,37 @@
         <v>271.9</v>
       </c>
       <c r="M39">
-        <v>26.50266533394495</v>
+        <v>26.13281333394495</v>
       </c>
       <c r="N39">
-        <v>245.397334666055</v>
+        <v>245.767186666055</v>
       </c>
       <c r="O39">
-        <v>85.88906713311926</v>
+        <v>86.01851533311925</v>
       </c>
       <c r="P39">
-        <v>159.5082675329358</v>
+        <v>159.7486713329358</v>
       </c>
       <c r="Q39">
-        <v>326.1082675329358</v>
+        <v>326.3486713329357</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1371524222675147</v>
+        <v>0.1371318047946498</v>
       </c>
       <c r="T39">
         <v>1.328989044181688</v>
       </c>
       <c r="U39">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V39">
         <v>0.35</v>
       </c>
       <c r="W39">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.25934548747997</v>
+        <v>10.4045437636375</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1034160274676578</v>
+        <v>0.1031560906843683</v>
       </c>
       <c r="C40">
-        <v>647.1157684657528</v>
+        <v>649.2570763840106</v>
       </c>
       <c r="D40">
-        <v>903.5637684657528</v>
+        <v>905.7050763840105</v>
       </c>
       <c r="E40">
         <v>-145.152</v>
@@ -4567,37 +4567,37 @@
         <v>271.9</v>
       </c>
       <c r="M40">
-        <v>27.21895358621373</v>
+        <v>26.83910558621373</v>
       </c>
       <c r="N40">
-        <v>244.6810464137862</v>
+        <v>245.0608944137862</v>
       </c>
       <c r="O40">
-        <v>85.63836624482518</v>
+        <v>85.77131304482518</v>
       </c>
       <c r="P40">
-        <v>159.0426801689611</v>
+        <v>159.2895813689611</v>
       </c>
       <c r="Q40">
-        <v>325.6426801689611</v>
+        <v>325.889581368961</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1382526256077138</v>
+        <v>0.1382317598282145</v>
       </c>
       <c r="T40">
         <v>1.344994730174501</v>
       </c>
       <c r="U40">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V40">
         <v>0.35</v>
       </c>
       <c r="W40">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>9.989362711493657</v>
+        <v>10.13073998038389</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1037501029893502</v>
+        <v>0.102926018430676</v>
       </c>
       <c r="C41">
-        <v>634.2488723256529</v>
+        <v>641.2583454586972</v>
       </c>
       <c r="D41">
-        <v>900.6928723256528</v>
+        <v>907.7023454586972</v>
       </c>
       <c r="E41">
         <v>-135.156</v>
@@ -4649,45 +4649,45 @@
         <v>271.9</v>
       </c>
       <c r="M41">
-        <v>28.79289863848252</v>
+        <v>27.54539783848251</v>
       </c>
       <c r="N41">
-        <v>243.1071013615175</v>
+        <v>244.3546021615174</v>
       </c>
       <c r="O41">
-        <v>85.08748547653111</v>
+        <v>85.5241107565311</v>
       </c>
       <c r="P41">
-        <v>158.0196158849864</v>
+        <v>158.8304914049863</v>
       </c>
       <c r="Q41">
-        <v>324.6196158849864</v>
+        <v>325.4304914049864</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1393889011885751</v>
+        <v>0.1393677789612404</v>
       </c>
       <c r="T41">
         <v>1.361525192757242</v>
       </c>
       <c r="U41">
-        <v>0.07385748822216712</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V41">
         <v>0.35</v>
       </c>
       <c r="W41">
-        <v>0.04800736734440863</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y41">
-        <v>9.443300704591028</v>
+        <v>9.870977416784299</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1035407785110426</v>
+        <v>0.1031379461769837</v>
       </c>
       <c r="C42">
-        <v>626.0495750631425</v>
+        <v>629.4222704785656</v>
       </c>
       <c r="D42">
-        <v>902.4895750631425</v>
+        <v>905.8622704785656</v>
       </c>
       <c r="E42">
         <v>-125.16</v>
@@ -4731,37 +4731,37 @@
         <v>271.9</v>
       </c>
       <c r="M42">
-        <v>29.5311780907513</v>
+        <v>28.9314180907513</v>
       </c>
       <c r="N42">
-        <v>242.3688219092487</v>
+        <v>242.9685819092487</v>
       </c>
       <c r="O42">
-        <v>84.82908766823704</v>
+        <v>85.03900366823703</v>
       </c>
       <c r="P42">
-        <v>157.5397342410116</v>
+        <v>157.9295782410117</v>
       </c>
       <c r="Q42">
-        <v>324.1397342410116</v>
+        <v>324.5295782410117</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1405630526221318</v>
+        <v>0.1405416653987005</v>
       </c>
       <c r="T42">
         <v>1.378606670759408</v>
       </c>
       <c r="U42">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V42">
         <v>0.35</v>
       </c>
       <c r="W42">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.207218186976251</v>
+        <v>9.398087544382074</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1033314540327349</v>
+        <v>0.1029189239232915</v>
       </c>
       <c r="C43">
-        <v>617.8574602558172</v>
+        <v>621.3280732538326</v>
       </c>
       <c r="D43">
-        <v>904.2934602558171</v>
+        <v>907.7640732538326</v>
       </c>
       <c r="E43">
         <v>-115.164</v>
@@ -4813,37 +4813,37 @@
         <v>271.9</v>
       </c>
       <c r="M43">
-        <v>30.26945754302008</v>
+        <v>29.65470354302008</v>
       </c>
       <c r="N43">
-        <v>241.6305424569799</v>
+        <v>242.2452964569799</v>
       </c>
       <c r="O43">
-        <v>84.57068985994296</v>
+        <v>84.78585375994297</v>
       </c>
       <c r="P43">
-        <v>157.0598525970369</v>
+        <v>157.4594426970369</v>
       </c>
       <c r="Q43">
-        <v>323.6598525970369</v>
+        <v>324.059442697037</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.141777005799199</v>
+        <v>0.1417553445967524</v>
       </c>
       <c r="T43">
         <v>1.396267181914189</v>
       </c>
       <c r="U43">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V43">
         <v>0.35</v>
       </c>
       <c r="W43">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.982651889732928</v>
+        <v>9.16886589695812</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1031221295544273</v>
+        <v>0.1026999016695992</v>
       </c>
       <c r="C44">
-        <v>609.6725710585457</v>
+        <v>613.24187826797</v>
       </c>
       <c r="D44">
-        <v>906.1045710585457</v>
+        <v>909.6738782679701</v>
       </c>
       <c r="E44">
         <v>-105.168</v>
@@ -4895,37 +4895,37 @@
         <v>271.9</v>
       </c>
       <c r="M44">
-        <v>31.00773699528887</v>
+        <v>30.37798899528886</v>
       </c>
       <c r="N44">
-        <v>240.8922630047111</v>
+        <v>241.5220110047111</v>
       </c>
       <c r="O44">
-        <v>84.31229205164888</v>
+        <v>84.53270385164889</v>
       </c>
       <c r="P44">
-        <v>156.5799709530622</v>
+        <v>156.9893071530622</v>
       </c>
       <c r="Q44">
-        <v>323.1799709530623</v>
+        <v>323.5893071530622</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1430328194306477</v>
+        <v>0.1430108748016337</v>
       </c>
       <c r="T44">
         <v>1.414536676212239</v>
       </c>
       <c r="U44">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V44">
         <v>0.35</v>
       </c>
       <c r="W44">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.768779225691667</v>
+        <v>8.950559566078166</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1029128050761197</v>
+        <v>0.1024808794159069</v>
       </c>
       <c r="C45">
-        <v>601.4949509726137</v>
+        <v>605.1637361341391</v>
       </c>
       <c r="D45">
-        <v>907.9229509726135</v>
+        <v>911.591736134139</v>
       </c>
       <c r="E45">
         <v>-95.17199999999997</v>
@@ -4977,37 +4977,37 @@
         <v>271.9</v>
       </c>
       <c r="M45">
-        <v>31.74601644755765</v>
+        <v>31.10127444755765</v>
       </c>
       <c r="N45">
-        <v>240.1539835524423</v>
+        <v>240.7987255524423</v>
       </c>
       <c r="O45">
-        <v>84.0538942433548</v>
+        <v>84.27955394335481</v>
       </c>
       <c r="P45">
-        <v>156.1000893090875</v>
+        <v>156.5191716090875</v>
       </c>
       <c r="Q45">
-        <v>322.7000893090875</v>
+        <v>323.1191716090875</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1443326966982877</v>
+        <v>0.1443104586979144</v>
       </c>
       <c r="T45">
         <v>1.43344720539794</v>
       </c>
       <c r="U45">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V45">
         <v>0.35</v>
       </c>
       <c r="W45">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.564854127419768</v>
+        <v>8.742407018029835</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.102703480597812</v>
+        <v>0.1022618571622146</v>
       </c>
       <c r="C46">
-        <v>593.3246438492024</v>
+        <v>597.0936978932311</v>
       </c>
       <c r="D46">
-        <v>909.7486438492024</v>
+        <v>913.5176978932311</v>
       </c>
       <c r="E46">
         <v>-85.17599999999999</v>
@@ -5059,37 +5059,37 @@
         <v>271.9</v>
       </c>
       <c r="M46">
-        <v>32.48429589982643</v>
+        <v>31.82455989982643</v>
       </c>
       <c r="N46">
-        <v>239.4157041001735</v>
+        <v>240.0754401001736</v>
       </c>
       <c r="O46">
-        <v>83.79549643506074</v>
+        <v>84.02640403506074</v>
       </c>
       <c r="P46">
-        <v>155.6202076651128</v>
+        <v>156.0490360651128</v>
       </c>
       <c r="Q46">
-        <v>322.2202076651128</v>
+        <v>322.6490360651128</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1456789981540575</v>
+        <v>0.1456564563047765</v>
       </c>
       <c r="T46">
         <v>1.453033110625987</v>
       </c>
       <c r="U46">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V46">
         <v>0.35</v>
       </c>
       <c r="W46">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.370198351796592</v>
+        <v>8.543715949438248</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1024941561195044</v>
+        <v>0.1020428349085224</v>
       </c>
       <c r="C47">
-        <v>585.1616938929158</v>
+        <v>589.0318150183971</v>
       </c>
       <c r="D47">
-        <v>911.5816938929157</v>
+        <v>915.4518150183969</v>
       </c>
       <c r="E47">
         <v>-75.18000000000001</v>
@@ -5141,37 +5141,37 @@
         <v>271.9</v>
       </c>
       <c r="M47">
-        <v>33.22257535209521</v>
+        <v>32.54784535209521</v>
       </c>
       <c r="N47">
-        <v>238.6774246479048</v>
+        <v>239.3521546479048</v>
       </c>
       <c r="O47">
-        <v>83.53709862676666</v>
+        <v>83.77325412676666</v>
       </c>
       <c r="P47">
-        <v>155.1403260211381</v>
+        <v>155.5789005211381</v>
       </c>
       <c r="Q47">
-        <v>321.7403260211381</v>
+        <v>322.1789005211381</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1470742560264009</v>
+        <v>0.1470513992791609</v>
       </c>
       <c r="T47">
         <v>1.473331230589599</v>
       </c>
       <c r="U47">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V47">
         <v>0.35</v>
       </c>
       <c r="W47">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.18419394397889</v>
+        <v>8.353855595006287</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1022848316411968</v>
+        <v>0.1018238126548301</v>
       </c>
       <c r="C48">
-        <v>577.0061456653482</v>
+        <v>580.9781394196323</v>
       </c>
       <c r="D48">
-        <v>913.4221456653482</v>
+        <v>917.3941394196322</v>
       </c>
       <c r="E48">
         <v>-65.18399999999997</v>
@@ -5223,37 +5223,37 @@
         <v>271.9</v>
       </c>
       <c r="M48">
-        <v>33.960854804364</v>
+        <v>33.271130804364</v>
       </c>
       <c r="N48">
-        <v>237.939145195636</v>
+        <v>238.628869195636</v>
       </c>
       <c r="O48">
-        <v>83.27870081847259</v>
+        <v>83.5201042184726</v>
       </c>
       <c r="P48">
-        <v>154.6604443771634</v>
+        <v>155.1087649771634</v>
       </c>
       <c r="Q48">
-        <v>321.2604443771634</v>
+        <v>321.7087649771634</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1485211901162385</v>
+        <v>0.1484980068081521</v>
       </c>
       <c r="T48">
         <v>1.494381132774087</v>
       </c>
       <c r="U48">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V48">
         <v>0.35</v>
       </c>
       <c r="W48">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.006276684327174</v>
+        <v>8.172250038593106</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1020755071628891</v>
+        <v>0.1016047904011378</v>
       </c>
       <c r="C49">
-        <v>568.8580440886968</v>
+        <v>572.9327234484211</v>
       </c>
       <c r="D49">
-        <v>915.2700440886967</v>
+        <v>919.3447234484212</v>
       </c>
       <c r="E49">
         <v>-55.18799999999999</v>
@@ -5305,37 +5305,37 @@
         <v>271.9</v>
       </c>
       <c r="M49">
-        <v>34.69913425663278</v>
+        <v>33.99441625663277</v>
       </c>
       <c r="N49">
-        <v>237.2008657433672</v>
+        <v>237.9055837433672</v>
       </c>
       <c r="O49">
-        <v>83.02030301017851</v>
+        <v>83.26695431017852</v>
       </c>
       <c r="P49">
-        <v>154.1805627331887</v>
+        <v>154.6386294331887</v>
       </c>
       <c r="Q49">
-        <v>320.7805627331887</v>
+        <v>321.2386294331886</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.150022725492485</v>
+        <v>0.1499992033005014</v>
       </c>
       <c r="T49">
         <v>1.516225370890064</v>
       </c>
       <c r="U49">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V49">
         <v>0.35</v>
       </c>
       <c r="W49">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.835930371894681</v>
+        <v>7.99837237819751</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1018661826845815</v>
+        <v>0.1013857681474455</v>
       </c>
       <c r="C50">
-        <v>560.7174344494122</v>
+        <v>564.8956199024406</v>
       </c>
       <c r="D50">
-        <v>917.1254344494122</v>
+        <v>921.3036199024405</v>
       </c>
       <c r="E50">
         <v>-45.19200000000001</v>
@@ -5387,37 +5387,37 @@
         <v>271.9</v>
       </c>
       <c r="M50">
-        <v>35.43741370890156</v>
+        <v>34.71770170890156</v>
       </c>
       <c r="N50">
-        <v>236.4625862910984</v>
+        <v>237.1822982910984</v>
       </c>
       <c r="O50">
-        <v>82.76190520188445</v>
+        <v>83.01380440188444</v>
       </c>
       <c r="P50">
-        <v>153.700681089214</v>
+        <v>154.168493889214</v>
       </c>
       <c r="Q50">
-        <v>320.300681089214</v>
+        <v>320.768493889214</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1515820122293565</v>
+        <v>0.1515581381194796</v>
       </c>
       <c r="T50">
         <v>1.538909772010502</v>
       </c>
       <c r="U50">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V50">
         <v>0.35</v>
       </c>
       <c r="W50">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.67268182248021</v>
+        <v>7.831739620318395</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1021346082062739</v>
+        <v>0.1011667458937533</v>
       </c>
       <c r="C51">
-        <v>548.3435481214024</v>
+        <v>556.8668820303228</v>
       </c>
       <c r="D51">
-        <v>914.7475481214025</v>
+        <v>923.2708820303229</v>
       </c>
       <c r="E51">
         <v>-35.19599999999997</v>
@@ -5469,45 +5469,45 @@
         <v>271.9</v>
       </c>
       <c r="M51">
-        <v>36.91039916117035</v>
+        <v>35.44098716117034</v>
       </c>
       <c r="N51">
-        <v>234.9896008388296</v>
+        <v>236.4590128388296</v>
       </c>
       <c r="O51">
-        <v>82.24636029359037</v>
+        <v>82.76065449359037</v>
       </c>
       <c r="P51">
-        <v>152.7432405452392</v>
+        <v>153.6983583452393</v>
       </c>
       <c r="Q51">
-        <v>319.3432405452393</v>
+        <v>320.2983583452393</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.153202447465713</v>
+        <v>0.1531782076372412</v>
       </c>
       <c r="T51">
         <v>1.562483757488603</v>
       </c>
       <c r="U51">
-        <v>0.07535748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V51">
         <v>0.35</v>
       </c>
       <c r="W51">
-        <v>0.04898236734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>7.366487661451197</v>
+        <v>7.67190819949557</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1019350337279663</v>
+        <v>0.101207723640061</v>
       </c>
       <c r="C52">
-        <v>540.1143294799172</v>
+        <v>546.5021804901071</v>
       </c>
       <c r="D52">
-        <v>916.514329479917</v>
+        <v>922.902180490107</v>
       </c>
       <c r="E52">
         <v>-25.19999999999999</v>
@@ -5551,37 +5551,37 @@
         <v>271.9</v>
       </c>
       <c r="M52">
-        <v>37.66367261343913</v>
+        <v>36.56411261343912</v>
       </c>
       <c r="N52">
-        <v>234.2363273865608</v>
+        <v>235.3358873865608</v>
       </c>
       <c r="O52">
-        <v>81.98271458529629</v>
+        <v>82.36756058529629</v>
       </c>
       <c r="P52">
-        <v>152.2536128012646</v>
+        <v>152.9683268012645</v>
       </c>
       <c r="Q52">
-        <v>318.8536128012645</v>
+        <v>319.5683268012646</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1548877001115239</v>
+        <v>0.1548630799357133</v>
       </c>
       <c r="T52">
         <v>1.58700070238583</v>
       </c>
       <c r="U52">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V52">
         <v>0.35</v>
       </c>
       <c r="W52">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.219157908222174</v>
+        <v>7.436253215675286</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1017354592496586</v>
+        <v>0.1009939013863687</v>
       </c>
       <c r="C53">
-        <v>531.8919489153823</v>
+        <v>538.4333159114221</v>
       </c>
       <c r="D53">
-        <v>918.2879489153823</v>
+        <v>924.8293159114222</v>
       </c>
       <c r="E53">
         <v>-15.20400000000001</v>
@@ -5633,37 +5633,37 @@
         <v>271.9</v>
       </c>
       <c r="M53">
-        <v>38.4169460657079</v>
+        <v>37.29539486570791</v>
       </c>
       <c r="N53">
-        <v>233.4830539342921</v>
+        <v>234.6046051342921</v>
       </c>
       <c r="O53">
-        <v>81.71906887700221</v>
+        <v>82.11161179700221</v>
       </c>
       <c r="P53">
-        <v>151.7639850572899</v>
+        <v>152.4929933372898</v>
       </c>
       <c r="Q53">
-        <v>318.3639850572898</v>
+        <v>319.0929933372898</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1566417385796127</v>
+        <v>0.1566167225320823</v>
       </c>
       <c r="T53">
         <v>1.612518338911514</v>
       </c>
       <c r="U53">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V53">
         <v>0.35</v>
       </c>
       <c r="W53">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.077605792374681</v>
+        <v>7.290444329093417</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.101535884771351</v>
+        <v>0.1007800791326764</v>
       </c>
       <c r="C54">
-        <v>523.6764462034834</v>
+        <v>530.3725163741343</v>
       </c>
       <c r="D54">
-        <v>920.0684462034834</v>
+        <v>926.7645163741344</v>
       </c>
       <c r="E54">
         <v>-5.20799999999997</v>
@@ -5715,37 +5715,37 @@
         <v>271.9</v>
       </c>
       <c r="M54">
-        <v>39.17021951797669</v>
+        <v>38.02667711797669</v>
       </c>
       <c r="N54">
-        <v>232.7297804820233</v>
+        <v>233.8733228820233</v>
       </c>
       <c r="O54">
-        <v>81.45542316870814</v>
+        <v>81.85566300870813</v>
       </c>
       <c r="P54">
-        <v>151.2743573133151</v>
+        <v>152.0176598733152</v>
       </c>
       <c r="Q54">
-        <v>317.8743573133152</v>
+        <v>318.6176598733151</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1584688619838719</v>
+        <v>0.1584434335699665</v>
       </c>
       <c r="T54">
         <v>1.639099210292435</v>
       </c>
       <c r="U54">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V54">
         <v>0.35</v>
       </c>
       <c r="W54">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.941497988675167</v>
+        <v>7.150243476610852</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1013363102930434</v>
+        <v>0.1005662568789842</v>
       </c>
       <c r="C55">
-        <v>515.4678614289942</v>
+        <v>522.3198326125746</v>
       </c>
       <c r="D55">
-        <v>921.8558614289942</v>
+        <v>928.7078326125746</v>
       </c>
       <c r="E55">
         <v>4.788000000000011</v>
@@ -5797,37 +5797,37 @@
         <v>271.9</v>
       </c>
       <c r="M55">
-        <v>39.92349297024548</v>
+        <v>38.75795937024547</v>
       </c>
       <c r="N55">
-        <v>231.9765070297545</v>
+        <v>233.1420406297545</v>
       </c>
       <c r="O55">
-        <v>81.19177746041406</v>
+        <v>81.59971422041407</v>
       </c>
       <c r="P55">
-        <v>150.7847295693404</v>
+        <v>151.5423264093404</v>
       </c>
       <c r="Q55">
-        <v>317.3847295693404</v>
+        <v>318.1423264093404</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1603737353202272</v>
+        <v>0.1603478769924417</v>
       </c>
       <c r="T55">
         <v>1.666811182583183</v>
       </c>
       <c r="U55">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V55">
         <v>0.35</v>
       </c>
       <c r="W55">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.810526328511484</v>
+        <v>7.015333222335175</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1011367358147357</v>
+        <v>0.1003524346252919</v>
       </c>
       <c r="C56">
-        <v>507.2662349887854</v>
+        <v>514.2753157875042</v>
       </c>
       <c r="D56">
-        <v>923.6502349887853</v>
+        <v>930.6593157875041</v>
       </c>
       <c r="E56">
         <v>14.78399999999999</v>
@@ -5879,37 +5879,37 @@
         <v>271.9</v>
       </c>
       <c r="M56">
-        <v>40.67676642251426</v>
+        <v>39.48924162251425</v>
       </c>
       <c r="N56">
-        <v>231.2232335774857</v>
+        <v>232.4107583774857</v>
       </c>
       <c r="O56">
-        <v>80.92813175212</v>
+        <v>81.34376543212001</v>
       </c>
       <c r="P56">
-        <v>150.2951018253657</v>
+        <v>151.0669929453657</v>
       </c>
       <c r="Q56">
-        <v>316.8951018253657</v>
+        <v>317.6669929453657</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.162361429236424</v>
+        <v>0.1623351223028505</v>
       </c>
       <c r="T56">
         <v>1.695728023234398</v>
       </c>
       <c r="U56">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V56">
         <v>0.35</v>
       </c>
       <c r="W56">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.684405470576087</v>
+        <v>6.885419644143784</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1009371613364281</v>
+        <v>0.1001386123715996</v>
       </c>
       <c r="C57">
-        <v>499.0716075948673</v>
+        <v>506.2390174906028</v>
       </c>
       <c r="D57">
-        <v>925.4516075948673</v>
+        <v>932.6190174906029</v>
       </c>
       <c r="E57">
         <v>24.78000000000009</v>
@@ -5961,37 +5961,37 @@
         <v>271.9</v>
       </c>
       <c r="M57">
-        <v>41.43003987478304</v>
+        <v>40.22052387478304</v>
       </c>
       <c r="N57">
-        <v>230.4699601252169</v>
+        <v>231.6794761252169</v>
       </c>
       <c r="O57">
-        <v>80.66448604382593</v>
+        <v>81.08781664382592</v>
       </c>
       <c r="P57">
-        <v>149.805474081391</v>
+        <v>150.591659481391</v>
       </c>
       <c r="Q57">
-        <v>316.405474081391</v>
+        <v>317.191659481391</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1644374651044519</v>
+        <v>0.1644106896270552</v>
       </c>
       <c r="T57">
         <v>1.725930056803445</v>
       </c>
       <c r="U57">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V57">
         <v>0.35</v>
       </c>
       <c r="W57">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.562870825656521</v>
+        <v>6.760230196068441</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1007375868581205</v>
+        <v>0.09992479011790732</v>
       </c>
       <c r="C58">
-        <v>490.8840202774704</v>
+        <v>498.2109897490177</v>
       </c>
       <c r="D58">
-        <v>927.2600202774705</v>
+        <v>934.5869897490178</v>
       </c>
       <c r="E58">
         <v>34.77600000000007</v>
@@ -6043,37 +6043,37 @@
         <v>271.9</v>
       </c>
       <c r="M58">
-        <v>42.18331332705183</v>
+        <v>40.95180612705182</v>
       </c>
       <c r="N58">
-        <v>229.7166866729482</v>
+        <v>230.9481938729481</v>
       </c>
       <c r="O58">
-        <v>80.40084033553185</v>
+        <v>80.83186785553184</v>
       </c>
       <c r="P58">
-        <v>149.3158463374163</v>
+        <v>150.1163260174163</v>
       </c>
       <c r="Q58">
-        <v>315.9158463374163</v>
+        <v>316.7163260174163</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1666078662392083</v>
+        <v>0.1665806009205421</v>
       </c>
       <c r="T58">
         <v>1.757504910080175</v>
       </c>
       <c r="U58">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V58">
         <v>0.35</v>
       </c>
       <c r="W58">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.445676703769798</v>
+        <v>6.639511799710076</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1005380123798128</v>
+        <v>0.09971096786421504</v>
       </c>
       <c r="C59">
-        <v>482.7035143881586</v>
+        <v>490.1912850299656</v>
       </c>
       <c r="D59">
-        <v>929.0755143881587</v>
+        <v>936.5632850299655</v>
       </c>
       <c r="E59">
         <v>44.77200000000005</v>
@@ -6125,37 +6125,37 @@
         <v>271.9</v>
       </c>
       <c r="M59">
-        <v>42.93658677932061</v>
+        <v>41.6830883793206</v>
       </c>
       <c r="N59">
-        <v>228.9634132206794</v>
+        <v>230.2169116206794</v>
       </c>
       <c r="O59">
-        <v>80.13719462723778</v>
+        <v>80.57591906723778</v>
       </c>
       <c r="P59">
-        <v>148.8262185934416</v>
+        <v>149.6409925534416</v>
       </c>
       <c r="Q59">
-        <v>315.4262185934416</v>
+        <v>316.2409925534416</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1688792162639533</v>
+        <v>0.1688514383207027</v>
       </c>
       <c r="T59">
         <v>1.790548361183731</v>
       </c>
       <c r="U59">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V59">
         <v>0.35</v>
       </c>
       <c r="W59">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.33259465633524</v>
+        <v>6.523029136557269</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1003384379015052</v>
+        <v>0.09949714561052278</v>
       </c>
       <c r="C60">
-        <v>474.5301316029827</v>
+        <v>482.1799562453964</v>
       </c>
       <c r="D60">
-        <v>930.8981316029826</v>
+        <v>938.5479562453963</v>
       </c>
       <c r="E60">
         <v>54.76800000000003</v>
@@ -6207,37 +6207,37 @@
         <v>271.9</v>
       </c>
       <c r="M60">
-        <v>43.68986023158939</v>
+        <v>42.41437063158939</v>
       </c>
       <c r="N60">
-        <v>228.2101397684106</v>
+        <v>229.4856293684106</v>
       </c>
       <c r="O60">
-        <v>79.8735489189437</v>
+        <v>80.3199702789437</v>
       </c>
       <c r="P60">
-        <v>148.3365908494669</v>
+        <v>149.1656590894669</v>
       </c>
       <c r="Q60">
-        <v>314.9365908494669</v>
+        <v>315.7656590894669</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1712587258136862</v>
+        <v>0.1712304108351566</v>
       </c>
       <c r="T60">
         <v>1.825165309958883</v>
       </c>
       <c r="U60">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V60">
         <v>0.35</v>
       </c>
       <c r="W60">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.223411989846702</v>
+        <v>6.410563116961454</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1001388634231976</v>
+        <v>0.09928332335683049</v>
       </c>
       <c r="C61">
-        <v>466.363913925669</v>
+        <v>474.1770567567156</v>
       </c>
       <c r="D61">
-        <v>932.727913925669</v>
+        <v>940.5410567567155</v>
       </c>
       <c r="E61">
         <v>64.76400000000001</v>
@@ -6289,37 +6289,37 @@
         <v>271.9</v>
       </c>
       <c r="M61">
-        <v>44.44313368385817</v>
+        <v>43.14565288385816</v>
       </c>
       <c r="N61">
-        <v>227.4568663161418</v>
+        <v>228.7543471161418</v>
       </c>
       <c r="O61">
-        <v>79.60990321064962</v>
+        <v>80.06402149064964</v>
       </c>
       <c r="P61">
-        <v>147.8469631054922</v>
+        <v>148.6903256254922</v>
       </c>
       <c r="Q61">
-        <v>314.4469631054922</v>
+        <v>315.2903256254922</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1737543089999914</v>
+        <v>0.17372543078934</v>
       </c>
       <c r="T61">
         <v>1.861470890381605</v>
       </c>
       <c r="U61">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V61">
         <v>0.35</v>
       </c>
       <c r="W61">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.117930430696757</v>
+        <v>6.301909504809565</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1004852889448899</v>
+        <v>0.09906950110313822</v>
       </c>
       <c r="C62">
-        <v>453.1963179876707</v>
+        <v>466.1826403795658</v>
       </c>
       <c r="D62">
-        <v>929.5563179876706</v>
+        <v>942.5426403795658</v>
       </c>
       <c r="E62">
         <v>74.75999999999999</v>
@@ -6371,45 +6371,45 @@
         <v>271.9</v>
       </c>
       <c r="M62">
-        <v>46.03607113612695</v>
+        <v>43.87693513612695</v>
       </c>
       <c r="N62">
-        <v>225.863928863873</v>
+        <v>228.023064863873</v>
       </c>
       <c r="O62">
-        <v>79.05237510235555</v>
+        <v>79.80807270235556</v>
       </c>
       <c r="P62">
-        <v>146.8115537615175</v>
+        <v>148.2149921615175</v>
       </c>
       <c r="Q62">
-        <v>313.4115537615174</v>
+        <v>314.8149921615175</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1763746713456119</v>
+        <v>0.1763452017412326</v>
       </c>
       <c r="T62">
         <v>1.899591749825463</v>
       </c>
       <c r="U62">
-        <v>0.07675748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V62">
         <v>0.35</v>
       </c>
       <c r="W62">
-        <v>0.04989236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y62">
-        <v>5.906238158247731</v>
+        <v>6.196877679729406</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1002948144665823</v>
+        <v>0.09885567884944596</v>
       </c>
       <c r="C63">
-        <v>444.9414761290585</v>
+        <v>458.1967613886721</v>
       </c>
       <c r="D63">
-        <v>931.2974761290585</v>
+        <v>944.552761388672</v>
       </c>
       <c r="E63">
         <v>84.75599999999997</v>
@@ -6453,45 +6453,45 @@
         <v>271.9</v>
       </c>
       <c r="M63">
-        <v>46.80333898839573</v>
+        <v>44.60821738839573</v>
       </c>
       <c r="N63">
-        <v>225.0966610116043</v>
+        <v>227.2917826116042</v>
       </c>
       <c r="O63">
-        <v>78.78383135406149</v>
+        <v>79.55212391406148</v>
       </c>
       <c r="P63">
-        <v>146.3128296575427</v>
+        <v>147.7396586975428</v>
       </c>
       <c r="Q63">
-        <v>312.9128296575427</v>
+        <v>314.3396586975427</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.179129411247418</v>
+        <v>0.1790993199214274</v>
       </c>
       <c r="T63">
         <v>1.939667525138236</v>
       </c>
       <c r="U63">
-        <v>0.07675748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V63">
         <v>0.35</v>
       </c>
       <c r="W63">
-        <v>0.04989236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y63">
-        <v>5.809414581883015</v>
+        <v>6.095289521045316</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1001043399882747</v>
+        <v>0.09904485659575368</v>
       </c>
       <c r="C64">
-        <v>436.6931692610448</v>
+        <v>446.4218845340796</v>
       </c>
       <c r="D64">
-        <v>933.0451692610447</v>
+        <v>942.7738845340797</v>
       </c>
       <c r="E64">
         <v>94.75200000000007</v>
@@ -6535,37 +6535,37 @@
         <v>271.9</v>
       </c>
       <c r="M64">
-        <v>47.57060684066452</v>
+        <v>45.95925164066452</v>
       </c>
       <c r="N64">
-        <v>224.3293931593355</v>
+        <v>225.9407483593355</v>
       </c>
       <c r="O64">
-        <v>78.51528760576741</v>
+        <v>79.07926192576741</v>
       </c>
       <c r="P64">
-        <v>145.8141055535681</v>
+        <v>146.861486433568</v>
       </c>
       <c r="Q64">
-        <v>312.414105553568</v>
+        <v>313.461486433568</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1820291374598456</v>
+        <v>0.1819983916900535</v>
       </c>
       <c r="T64">
         <v>1.981852551783261</v>
       </c>
       <c r="U64">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V64">
         <v>0.35</v>
       </c>
       <c r="W64">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.715714346691352</v>
+        <v>5.916110256230199</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.09991386550996705</v>
+        <v>0.0988375343420614</v>
       </c>
       <c r="C65">
-        <v>428.4514342439195</v>
+        <v>438.3757307540886</v>
       </c>
       <c r="D65">
-        <v>934.7994342439196</v>
+        <v>944.7237307540886</v>
       </c>
       <c r="E65">
         <v>104.748</v>
@@ -6617,37 +6617,37 @@
         <v>271.9</v>
       </c>
       <c r="M65">
-        <v>48.3378746929333</v>
+        <v>46.7005298929333</v>
       </c>
       <c r="N65">
-        <v>223.5621253070667</v>
+        <v>225.1994701070667</v>
       </c>
       <c r="O65">
-        <v>78.24674385747333</v>
+        <v>78.81981453747333</v>
       </c>
       <c r="P65">
-        <v>145.3153814495934</v>
+        <v>146.3796555695934</v>
       </c>
       <c r="Q65">
-        <v>311.9153814495934</v>
+        <v>312.9796555695933</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1850856056297016</v>
+        <v>0.1850541700407675</v>
       </c>
       <c r="T65">
         <v>2.026317850138827</v>
       </c>
       <c r="U65">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V65">
         <v>0.35</v>
       </c>
       <c r="W65">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.624988722140697</v>
+        <v>5.822203744226546</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.09972339103165942</v>
+        <v>0.09863021208836914</v>
       </c>
       <c r="C66">
-        <v>420.2163082157061</v>
+        <v>430.3376590386</v>
       </c>
       <c r="D66">
-        <v>936.5603082157062</v>
+        <v>946.6816590385999</v>
       </c>
       <c r="E66">
         <v>114.744</v>
@@ -6699,37 +6699,37 @@
         <v>271.9</v>
       </c>
       <c r="M66">
-        <v>49.10514254520209</v>
+        <v>47.44180814520208</v>
       </c>
       <c r="N66">
-        <v>222.7948574547979</v>
+        <v>224.4581918547979</v>
       </c>
       <c r="O66">
-        <v>77.97820010917926</v>
+        <v>78.56036714917926</v>
       </c>
       <c r="P66">
-        <v>144.8166573456186</v>
+        <v>145.8978247056186</v>
       </c>
       <c r="Q66">
-        <v>311.4166573456187</v>
+        <v>312.4978247056187</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.188311877586772</v>
+        <v>0.18827971385541</v>
       </c>
       <c r="T66">
         <v>2.073253442847482</v>
       </c>
       <c r="U66">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V66">
         <v>0.35</v>
       </c>
       <c r="W66">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.537098273357247</v>
+        <v>5.731231810723005</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.09953291655335178</v>
+        <v>0.09842288983467685</v>
       </c>
       <c r="C67">
-        <v>411.9878285947834</v>
+        <v>422.30771974191</v>
       </c>
       <c r="D67">
-        <v>938.3278285947833</v>
+        <v>948.64771974191</v>
       </c>
       <c r="E67">
         <v>124.74</v>
@@ -6781,37 +6781,37 @@
         <v>271.9</v>
       </c>
       <c r="M67">
-        <v>49.87241039747087</v>
+        <v>48.18308639747086</v>
       </c>
       <c r="N67">
-        <v>222.0275896025291</v>
+        <v>223.7169136025291</v>
       </c>
       <c r="O67">
-        <v>77.70965636088518</v>
+        <v>78.30091976088519</v>
       </c>
       <c r="P67">
-        <v>144.3179332416439</v>
+        <v>145.4159938416439</v>
       </c>
       <c r="Q67">
-        <v>310.9179332416439</v>
+        <v>312.0159938416439</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1917225079413891</v>
+        <v>0.1916895744594607</v>
       </c>
       <c r="T67">
         <v>2.122871069425201</v>
       </c>
       <c r="U67">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V67">
         <v>0.35</v>
       </c>
       <c r="W67">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.451912146074829</v>
+        <v>5.643059013634961</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.09934244207504415</v>
+        <v>0.09821556758098457</v>
       </c>
       <c r="C68">
-        <v>403.7660330825337</v>
+        <v>414.2859636374866</v>
       </c>
       <c r="D68">
-        <v>940.1020330825336</v>
+        <v>950.6219636374865</v>
       </c>
       <c r="E68">
         <v>134.736</v>
@@ -6863,37 +6863,37 @@
         <v>271.9</v>
       </c>
       <c r="M68">
-        <v>50.63967824973965</v>
+        <v>48.92436464973964</v>
       </c>
       <c r="N68">
-        <v>221.2603217502603</v>
+        <v>222.9756353502603</v>
       </c>
       <c r="O68">
-        <v>77.44111261259111</v>
+        <v>78.04147237259112</v>
       </c>
       <c r="P68">
-        <v>143.8192091376692</v>
+        <v>144.9341629776692</v>
       </c>
       <c r="Q68">
-        <v>310.4192091376692</v>
+        <v>311.5341629776692</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1953337636109837</v>
+        <v>0.1953000150990438</v>
       </c>
       <c r="T68">
         <v>2.175407379919257</v>
       </c>
       <c r="U68">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V68">
         <v>0.35</v>
       </c>
       <c r="W68">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.369307416588847</v>
+        <v>5.557558119488976</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.09915196759673653</v>
+        <v>0.0980082453272923</v>
       </c>
       <c r="C69">
-        <v>395.5509596660257</v>
+        <v>406.2724419223399</v>
       </c>
       <c r="D69">
-        <v>941.8829596660257</v>
+        <v>952.6044419223399</v>
       </c>
       <c r="E69">
         <v>144.7320000000001</v>
@@ -6945,37 +6945,37 @@
         <v>271.9</v>
       </c>
       <c r="M69">
-        <v>51.40694610200843</v>
+        <v>49.66564290200843</v>
       </c>
       <c r="N69">
-        <v>220.4930538979916</v>
+        <v>222.2343570979916</v>
       </c>
       <c r="O69">
-        <v>77.17256886429703</v>
+        <v>77.78202498429704</v>
       </c>
       <c r="P69">
-        <v>143.3204850336945</v>
+        <v>144.4523321136945</v>
       </c>
       <c r="Q69">
-        <v>309.9204850336945</v>
+        <v>311.0523321136945</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1991638832605538</v>
+        <v>0.1991292703228441</v>
       </c>
       <c r="T69">
         <v>2.231127709231135</v>
       </c>
       <c r="U69">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V69">
         <v>0.35</v>
       </c>
       <c r="W69">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.289168499923341</v>
+        <v>5.474609490839886</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.09896149311842889</v>
+        <v>0.09780092307360003</v>
       </c>
       <c r="C70">
-        <v>387.3426466207254</v>
+        <v>398.2672062214497</v>
       </c>
       <c r="D70">
-        <v>943.6706466207255</v>
+        <v>954.5952062214498</v>
       </c>
       <c r="E70">
         <v>154.7280000000001</v>
@@ -7027,37 +7027,37 @@
         <v>271.9</v>
       </c>
       <c r="M70">
-        <v>52.17421395427721</v>
+        <v>50.40692115427721</v>
       </c>
       <c r="N70">
-        <v>219.7257860457228</v>
+        <v>221.4930788457228</v>
       </c>
       <c r="O70">
-        <v>76.90402511600297</v>
+        <v>77.52257759600296</v>
       </c>
       <c r="P70">
-        <v>142.8217609297198</v>
+        <v>143.9705012497198</v>
       </c>
       <c r="Q70">
-        <v>309.4217609297198</v>
+        <v>310.5705012497198</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.203233385388222</v>
+        <v>0.2031978539981318</v>
       </c>
       <c r="T70">
         <v>2.290330559125005</v>
       </c>
       <c r="U70">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V70">
         <v>0.35</v>
       </c>
       <c r="W70">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.211386610218586</v>
+        <v>5.3941005277393</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09877101864012125</v>
+        <v>0.09759360081990774</v>
       </c>
       <c r="C71">
-        <v>379.1411325132366</v>
+        <v>390.2703085922452</v>
       </c>
       <c r="D71">
-        <v>945.4651325132365</v>
+        <v>956.5943085922452</v>
       </c>
       <c r="E71">
         <v>164.724</v>
@@ -7109,37 +7109,37 @@
         <v>271.9</v>
       </c>
       <c r="M71">
-        <v>52.94148180654599</v>
+        <v>51.14819940654599</v>
       </c>
       <c r="N71">
-        <v>218.958518193454</v>
+        <v>220.751800593454</v>
       </c>
       <c r="O71">
-        <v>76.63548136770889</v>
+        <v>77.2631302077089</v>
       </c>
       <c r="P71">
-        <v>142.3230368257451</v>
+        <v>143.4886703857451</v>
       </c>
       <c r="Q71">
-        <v>308.923036825745</v>
+        <v>310.0886703857451</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2075654360402558</v>
+        <v>0.2075289269427929</v>
       </c>
       <c r="T71">
         <v>2.353352947721705</v>
       </c>
       <c r="U71">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V71">
         <v>0.35</v>
       </c>
       <c r="W71">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.135859268041505</v>
+        <v>5.315925157772064</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09858054416181364</v>
+        <v>0.09738627856621547</v>
       </c>
       <c r="C72">
-        <v>370.9464562040753</v>
+        <v>382.2818015291427</v>
       </c>
       <c r="D72">
-        <v>947.2664562040752</v>
+        <v>958.6018015291427</v>
       </c>
       <c r="E72">
         <v>174.72</v>
@@ -7191,37 +7191,37 @@
         <v>271.9</v>
       </c>
       <c r="M72">
-        <v>53.70874965881477</v>
+        <v>51.88947765881478</v>
       </c>
       <c r="N72">
-        <v>218.1912503411852</v>
+        <v>220.0105223411852</v>
       </c>
       <c r="O72">
-        <v>76.36693761941481</v>
+        <v>77.00368281941482</v>
       </c>
       <c r="P72">
-        <v>141.8243127217704</v>
+        <v>143.0068395217704</v>
       </c>
       <c r="Q72">
-        <v>308.4243127217704</v>
+        <v>309.6068395217704</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.212186290069092</v>
+        <v>0.2121487380837648</v>
       </c>
       <c r="T72">
         <v>2.420576828891519</v>
       </c>
       <c r="U72">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V72">
         <v>0.35</v>
       </c>
       <c r="W72">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.062489849926627</v>
+        <v>5.239983369803891</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.098390069683506</v>
+        <v>0.09717895631252321</v>
       </c>
       <c r="C73">
-        <v>362.7586568504756</v>
+        <v>374.3017379681406</v>
       </c>
       <c r="D73">
-        <v>949.0746568504757</v>
+        <v>960.6177379681405</v>
       </c>
       <c r="E73">
         <v>184.716</v>
@@ -7273,37 +7273,37 @@
         <v>271.9</v>
       </c>
       <c r="M73">
-        <v>54.47601751108355</v>
+        <v>52.63075591108355</v>
       </c>
       <c r="N73">
-        <v>217.4239824889164</v>
+        <v>219.2692440889164</v>
       </c>
       <c r="O73">
-        <v>76.09839387112073</v>
+        <v>76.74423543112074</v>
       </c>
       <c r="P73">
-        <v>141.3255886177957</v>
+        <v>142.5250086577957</v>
       </c>
       <c r="Q73">
-        <v>307.9255886177957</v>
+        <v>309.1250086577957</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2171258236861237</v>
+        <v>0.2170871568896313</v>
       </c>
       <c r="T73">
         <v>2.492436839797181</v>
       </c>
       <c r="U73">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V73">
         <v>0.35</v>
       </c>
       <c r="W73">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.991187175983998</v>
+        <v>5.166180787130598</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.09819959520519836</v>
+        <v>0.09697163405883093</v>
       </c>
       <c r="C74">
-        <v>354.5777739092264</v>
+        <v>366.3301712914738</v>
       </c>
       <c r="D74">
-        <v>950.8897739092264</v>
+        <v>962.6421712914738</v>
       </c>
       <c r="E74">
         <v>194.712</v>
@@ -7355,37 +7355,37 @@
         <v>271.9</v>
       </c>
       <c r="M74">
-        <v>55.24328536335234</v>
+        <v>53.37203416335234</v>
       </c>
       <c r="N74">
-        <v>216.6567146366476</v>
+        <v>218.5279658366476</v>
       </c>
       <c r="O74">
-        <v>75.82985012282666</v>
+        <v>76.48478804282666</v>
       </c>
       <c r="P74">
-        <v>140.826864513821</v>
+        <v>142.043177793821</v>
       </c>
       <c r="Q74">
-        <v>307.426864513821</v>
+        <v>308.643177793821</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2224181811329434</v>
+        <v>0.2223783198959168</v>
       </c>
       <c r="T74">
         <v>2.569429708624677</v>
       </c>
       <c r="U74">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V74">
         <v>0.35</v>
       </c>
       <c r="W74">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.921865131873108</v>
+        <v>5.094428276198228</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.09800912072689073</v>
+        <v>0.09676431180513864</v>
       </c>
       <c r="C75">
-        <v>346.4038471395403</v>
+        <v>358.3671553323235</v>
       </c>
       <c r="D75">
-        <v>952.7118471395403</v>
+        <v>964.6751553323235</v>
       </c>
       <c r="E75">
         <v>204.708</v>
@@ -7437,37 +7437,37 @@
         <v>271.9</v>
       </c>
       <c r="M75">
-        <v>56.01055321562112</v>
+        <v>54.11331241562112</v>
       </c>
       <c r="N75">
-        <v>215.8894467843789</v>
+        <v>217.7866875843789</v>
       </c>
       <c r="O75">
-        <v>75.56130637453259</v>
+        <v>76.22534065453259</v>
       </c>
       <c r="P75">
-        <v>140.3281404098463</v>
+        <v>141.5613469298463</v>
       </c>
       <c r="Q75">
-        <v>306.9281404098463</v>
+        <v>308.1613469298462</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2281025650573053</v>
+        <v>0.228061420902668</v>
       </c>
       <c r="T75">
         <v>2.652125752920876</v>
       </c>
       <c r="U75">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V75">
         <v>0.35</v>
       </c>
       <c r="W75">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.854442321847451</v>
+        <v>5.024641587483184</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.09781864624858309</v>
+        <v>0.09655698955144637</v>
       </c>
       <c r="C76">
-        <v>338.236916605959</v>
+        <v>350.4127443795904</v>
       </c>
       <c r="D76">
-        <v>954.540916605959</v>
+        <v>966.7167443795904</v>
       </c>
       <c r="E76">
         <v>214.7040000000001</v>
@@ -7519,37 +7519,37 @@
         <v>271.9</v>
       </c>
       <c r="M76">
-        <v>56.77782106788991</v>
+        <v>54.85459066788991</v>
       </c>
       <c r="N76">
-        <v>215.1221789321101</v>
+        <v>217.0454093321101</v>
       </c>
       <c r="O76">
-        <v>75.29276262623853</v>
+        <v>75.96589326623852</v>
       </c>
       <c r="P76">
-        <v>139.8294163058715</v>
+        <v>141.0795160658715</v>
       </c>
       <c r="Q76">
-        <v>306.4294163058715</v>
+        <v>307.6795160658716</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2342242092835412</v>
+        <v>0.234181683525323</v>
       </c>
       <c r="T76">
         <v>2.741183031393705</v>
       </c>
       <c r="U76">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V76">
         <v>0.35</v>
       </c>
       <c r="W76">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.788841749930592</v>
+        <v>4.956741025490167</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.09762817177027547</v>
+        <v>0.0963496672977541</v>
       </c>
       <c r="C77">
-        <v>330.0770226812879</v>
+        <v>342.4669931827268</v>
       </c>
       <c r="D77">
-        <v>956.3770226812878</v>
+        <v>968.7669931827268</v>
       </c>
       <c r="E77">
         <v>224.7</v>
@@ -7601,37 +7601,37 @@
         <v>271.9</v>
       </c>
       <c r="M77">
-        <v>57.54508892015869</v>
+        <v>55.59586892015869</v>
       </c>
       <c r="N77">
-        <v>214.3549110798413</v>
+        <v>216.3041310798413</v>
       </c>
       <c r="O77">
-        <v>75.02421887794445</v>
+        <v>75.70644587794445</v>
       </c>
       <c r="P77">
-        <v>139.3306922018969</v>
+        <v>140.5976852018968</v>
       </c>
       <c r="Q77">
-        <v>305.9306922018968</v>
+        <v>307.1976852018968</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.240835585047876</v>
+        <v>0.2407915671577905</v>
       </c>
       <c r="T77">
         <v>2.837364892144362</v>
       </c>
       <c r="U77">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V77">
         <v>0.35</v>
       </c>
       <c r="W77">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.724990526598185</v>
+        <v>4.890651145150299</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.09743769729196786</v>
+        <v>0.09614234504406183</v>
       </c>
       <c r="C78">
-        <v>321.9242060495675</v>
+        <v>334.5299569566306</v>
       </c>
       <c r="D78">
-        <v>958.2202060495675</v>
+        <v>970.8259569566306</v>
       </c>
       <c r="E78">
         <v>234.696</v>
@@ -7683,37 +7683,37 @@
         <v>271.9</v>
       </c>
       <c r="M78">
-        <v>58.31235677242747</v>
+        <v>56.33714717242747</v>
       </c>
       <c r="N78">
-        <v>213.5876432275725</v>
+        <v>215.5628528275725</v>
       </c>
       <c r="O78">
-        <v>74.75567512965037</v>
+        <v>75.44699848965037</v>
       </c>
       <c r="P78">
-        <v>138.8319680979221</v>
+        <v>140.1158543379221</v>
       </c>
       <c r="Q78">
-        <v>305.4319680979221</v>
+        <v>306.7158543379221</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2479979087925721</v>
+        <v>0.247952274426297</v>
       </c>
       <c r="T78">
         <v>2.941561907957574</v>
       </c>
       <c r="U78">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V78">
         <v>0.35</v>
       </c>
       <c r="W78">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.66281959861663</v>
+        <v>4.826300472187794</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.0972472228136602</v>
+        <v>0.09593502279036953</v>
       </c>
       <c r="C79">
-        <v>313.7785077090784</v>
+        <v>326.6016913866035</v>
       </c>
       <c r="D79">
-        <v>960.0705077090784</v>
+        <v>972.8936913866035</v>
       </c>
       <c r="E79">
         <v>244.692</v>
@@ -7765,37 +7765,37 @@
         <v>271.9</v>
       </c>
       <c r="M79">
-        <v>59.07962462469625</v>
+        <v>57.07842542469625</v>
       </c>
       <c r="N79">
-        <v>212.8203753753037</v>
+        <v>214.8215745753037</v>
       </c>
       <c r="O79">
-        <v>74.48713138135631</v>
+        <v>75.18755110135629</v>
       </c>
       <c r="P79">
-        <v>138.3332439939474</v>
+        <v>139.6340234739474</v>
       </c>
       <c r="Q79">
-        <v>304.9332439939474</v>
+        <v>306.2340234739474</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2557830432976764</v>
+        <v>0.2557356518920648</v>
       </c>
       <c r="T79">
         <v>3.054819533841498</v>
       </c>
       <c r="U79">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V79">
         <v>0.35</v>
       </c>
       <c r="W79">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.602263499933297</v>
+        <v>4.763621245276265</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.09705674833535258</v>
+        <v>0.09572770053667726</v>
       </c>
       <c r="C80">
-        <v>305.6399689753806</v>
+        <v>318.6822526333677</v>
       </c>
       <c r="D80">
-        <v>961.9279689753805</v>
+        <v>974.9702526333676</v>
       </c>
       <c r="E80">
         <v>254.688</v>
@@ -7847,37 +7847,37 @@
         <v>271.9</v>
       </c>
       <c r="M80">
-        <v>59.84689247696503</v>
+        <v>57.81970367696503</v>
       </c>
       <c r="N80">
-        <v>212.053107523035</v>
+        <v>214.080296323035</v>
       </c>
       <c r="O80">
-        <v>74.21858763306223</v>
+        <v>74.92810371306223</v>
       </c>
       <c r="P80">
-        <v>137.8345198899727</v>
+        <v>139.1521926099727</v>
       </c>
       <c r="Q80">
-        <v>304.4345198899728</v>
+        <v>305.7521926099727</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2642759173032447</v>
+        <v>0.2642266091274479</v>
       </c>
       <c r="T80">
         <v>3.178373307533053</v>
       </c>
       <c r="U80">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V80">
         <v>0.35</v>
       </c>
       <c r="W80">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.543260121729024</v>
+        <v>4.702549178029134</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.09820137385704494</v>
+        <v>0.09552037828298499</v>
       </c>
       <c r="C81">
-        <v>284.5887922220057</v>
+        <v>310.7716973381545</v>
       </c>
       <c r="D81">
-        <v>950.8727922220057</v>
+        <v>977.0556973381545</v>
       </c>
       <c r="E81">
         <v>264.6840000000001</v>
@@ -7929,45 +7929,45 @@
         <v>271.9</v>
       </c>
       <c r="M81">
-        <v>62.66733872923383</v>
+        <v>58.56098192923382</v>
       </c>
       <c r="N81">
-        <v>209.2326612707662</v>
+        <v>213.3390180707661</v>
       </c>
       <c r="O81">
-        <v>73.23143144476815</v>
+        <v>74.66865632476815</v>
       </c>
       <c r="P81">
-        <v>136.001229825998</v>
+        <v>138.670361745998</v>
       </c>
       <c r="Q81">
-        <v>302.601229825998</v>
+        <v>305.270361745998</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2735776364522006</v>
+        <v>0.2735262289566771</v>
       </c>
       <c r="T81">
         <v>3.31369410729047</v>
       </c>
       <c r="U81">
-        <v>0.07935748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V81">
         <v>0.35</v>
       </c>
       <c r="W81">
-        <v>0.05158236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y81">
-        <v>4.338783256375314</v>
+        <v>4.643023239066739</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.09802779937873732</v>
+        <v>0.09531305602929271</v>
       </c>
       <c r="C82">
-        <v>276.2528589597978</v>
+        <v>302.8700826278514</v>
       </c>
       <c r="D82">
-        <v>952.5328589597977</v>
+        <v>979.1500826278515</v>
       </c>
       <c r="E82">
         <v>274.6800000000001</v>
@@ -8011,45 +8011,45 @@
         <v>271.9</v>
       </c>
       <c r="M82">
-        <v>63.46059618150261</v>
+        <v>59.3022601815026</v>
       </c>
       <c r="N82">
-        <v>208.4394038184974</v>
+        <v>212.5977398184974</v>
       </c>
       <c r="O82">
-        <v>72.95379133647407</v>
+        <v>74.40920893647407</v>
       </c>
       <c r="P82">
-        <v>135.4856124820233</v>
+        <v>138.1885308820233</v>
       </c>
       <c r="Q82">
-        <v>302.0856124820233</v>
+        <v>304.7885308820233</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2838095275160521</v>
+        <v>0.2837558107688291</v>
       </c>
       <c r="T82">
         <v>3.462546987023629</v>
       </c>
       <c r="U82">
-        <v>0.07935748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V82">
         <v>0.35</v>
       </c>
       <c r="W82">
-        <v>0.05158236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>4.284548465670623</v>
+        <v>4.584985448578404</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09785422490042969</v>
+        <v>0.09510573377560044</v>
       </c>
       <c r="C83">
-        <v>267.9227322391583</v>
+        <v>294.977466120221</v>
       </c>
       <c r="D83">
-        <v>954.1987322391583</v>
+        <v>981.2534661202211</v>
       </c>
       <c r="E83">
         <v>284.676</v>
@@ -8093,45 +8093,45 @@
         <v>271.9</v>
       </c>
       <c r="M83">
-        <v>64.25385363377139</v>
+        <v>60.04353843377138</v>
       </c>
       <c r="N83">
-        <v>207.6461463662286</v>
+        <v>211.8564615662286</v>
       </c>
       <c r="O83">
-        <v>72.67615122818</v>
+        <v>74.14976154818001</v>
       </c>
       <c r="P83">
-        <v>134.9699951380486</v>
+        <v>137.7067000180486</v>
       </c>
       <c r="Q83">
-        <v>301.5699951380486</v>
+        <v>304.3067000180486</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2951184597445195</v>
+        <v>0.2950621906664709</v>
       </c>
       <c r="T83">
         <v>3.627068590939226</v>
       </c>
       <c r="U83">
-        <v>0.07935748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V83">
         <v>0.35</v>
       </c>
       <c r="W83">
-        <v>0.05158236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y83">
-        <v>4.231652805600616</v>
+        <v>4.52838068995398</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09768065042212205</v>
+        <v>0.09623091152190816</v>
       </c>
       <c r="C84">
-        <v>259.5984425784332</v>
+        <v>273.6733135788827</v>
       </c>
       <c r="D84">
-        <v>955.8704425784332</v>
+        <v>969.9453135788827</v>
       </c>
       <c r="E84">
         <v>294.672</v>
@@ -8175,37 +8175,37 @@
         <v>271.9</v>
       </c>
       <c r="M84">
-        <v>65.04711108604018</v>
+        <v>62.83399668604017</v>
       </c>
       <c r="N84">
-        <v>206.8528889139598</v>
+        <v>209.0660033139598</v>
       </c>
       <c r="O84">
-        <v>72.39851111988592</v>
+        <v>73.17310115988593</v>
       </c>
       <c r="P84">
-        <v>134.4543777940739</v>
+        <v>135.8929021540739</v>
       </c>
       <c r="Q84">
-        <v>301.0543777940738</v>
+        <v>302.4929021540739</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3076839399983722</v>
+        <v>0.3076248349971839</v>
       </c>
       <c r="T84">
         <v>3.809870373067666</v>
       </c>
       <c r="U84">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V84">
         <v>0.35</v>
       </c>
       <c r="W84">
-        <v>0.05158236734440863</v>
+        <v>0.04982736734440862</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.180047283581096</v>
+        <v>4.327275270401636</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09750707594381443</v>
+        <v>0.09603983926821588</v>
       </c>
       <c r="C85">
-        <v>251.2800207102098</v>
+        <v>265.5792015641637</v>
       </c>
       <c r="D85">
-        <v>957.5480207102098</v>
+        <v>971.8472015641638</v>
       </c>
       <c r="E85">
         <v>304.6680000000001</v>
@@ -8257,37 +8257,37 @@
         <v>271.9</v>
       </c>
       <c r="M85">
-        <v>65.84036853830897</v>
+        <v>63.60026493830895</v>
       </c>
       <c r="N85">
-        <v>206.059631461691</v>
+        <v>208.299735061691</v>
       </c>
       <c r="O85">
-        <v>72.12087101159186</v>
+        <v>72.90490727159185</v>
       </c>
       <c r="P85">
-        <v>133.9387604500992</v>
+        <v>135.3948277900992</v>
       </c>
       <c r="Q85">
-        <v>300.5387604500992</v>
+        <v>301.9948277900992</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3217277120467958</v>
+        <v>0.3216654374844515</v>
       </c>
       <c r="T85">
         <v>4.014178247211218</v>
       </c>
       <c r="U85">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V85">
         <v>0.35</v>
       </c>
       <c r="W85">
-        <v>0.05158236734440863</v>
+        <v>0.04982736734440862</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.129685268116262</v>
+        <v>4.275139423770291</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.09733350146550679</v>
+        <v>0.09584876701452361</v>
       </c>
       <c r="C86">
-        <v>242.9674975832013</v>
+        <v>257.4925627222653</v>
       </c>
       <c r="D86">
-        <v>959.2314975832012</v>
+        <v>973.7565627222652</v>
       </c>
       <c r="E86">
         <v>314.664</v>
@@ -8339,37 +8339,37 @@
         <v>271.9</v>
       </c>
       <c r="M86">
-        <v>66.63362599057773</v>
+        <v>64.36653319057773</v>
       </c>
       <c r="N86">
-        <v>205.2663740094222</v>
+        <v>207.5334668094222</v>
       </c>
       <c r="O86">
-        <v>71.84323090329778</v>
+        <v>72.63671338329777</v>
       </c>
       <c r="P86">
-        <v>133.4231431061245</v>
+        <v>134.8967534261245</v>
       </c>
       <c r="Q86">
-        <v>300.0231431061245</v>
+        <v>301.4967534261244</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3375269556012721</v>
+        <v>0.3374611152826273</v>
       </c>
       <c r="T86">
         <v>4.244024605622711</v>
       </c>
       <c r="U86">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V86">
         <v>0.35</v>
       </c>
       <c r="W86">
-        <v>0.05158236734440863</v>
+        <v>0.04982736734440862</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.080522348257736</v>
+        <v>4.224244906820645</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.09715992698719916</v>
+        <v>0.09565769476083136</v>
       </c>
       <c r="C87">
-        <v>234.6609043641491</v>
+        <v>249.4134411868994</v>
       </c>
       <c r="D87">
-        <v>960.920904364149</v>
+        <v>975.6734411868993</v>
       </c>
       <c r="E87">
         <v>324.66</v>
@@ -8421,37 +8421,37 @@
         <v>271.9</v>
       </c>
       <c r="M87">
-        <v>67.42688344284652</v>
+        <v>65.13280144284651</v>
       </c>
       <c r="N87">
-        <v>204.4731165571534</v>
+        <v>206.7671985571534</v>
       </c>
       <c r="O87">
-        <v>71.5655907950037</v>
+        <v>72.3685194950037</v>
       </c>
       <c r="P87">
-        <v>132.9075257621498</v>
+        <v>134.3986790621498</v>
       </c>
       <c r="Q87">
-        <v>299.5075257621497</v>
+        <v>300.9986790621498</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3554327649630122</v>
+        <v>0.3553628834538934</v>
       </c>
       <c r="T87">
         <v>4.504517145155739</v>
       </c>
       <c r="U87">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V87">
         <v>0.35</v>
       </c>
       <c r="W87">
-        <v>0.05158236734440863</v>
+        <v>0.04982736734440862</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.032516202984116</v>
+        <v>4.174547907916873</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.09849565250889153</v>
+        <v>0.09546662250713908</v>
       </c>
       <c r="C88">
-        <v>211.8154926246317</v>
+        <v>241.3418814399801</v>
       </c>
       <c r="D88">
-        <v>948.0714926246318</v>
+        <v>977.5978814399801</v>
       </c>
       <c r="E88">
         <v>334.6560000000001</v>
@@ -8503,45 +8503,45 @@
         <v>271.9</v>
       </c>
       <c r="M88">
-        <v>70.5412120951153</v>
+        <v>65.8990696951153</v>
       </c>
       <c r="N88">
-        <v>201.3587879048847</v>
+        <v>206.0009303048847</v>
       </c>
       <c r="O88">
-        <v>70.47557576670964</v>
+        <v>72.10032560670963</v>
       </c>
       <c r="P88">
-        <v>130.8832121381751</v>
+        <v>133.900604698175</v>
       </c>
       <c r="Q88">
-        <v>297.4832121381751</v>
+        <v>300.500604698175</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3758965470907151</v>
+        <v>0.3758220470781975</v>
       </c>
       <c r="T88">
         <v>4.802222904622056</v>
       </c>
       <c r="U88">
-        <v>0.08205748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V88">
         <v>0.35</v>
       </c>
       <c r="W88">
-        <v>0.05333736734440863</v>
+        <v>0.04982736734440862</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y88">
-        <v>3.854484377634163</v>
+        <v>4.126006653173652</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.09833962803058391</v>
+        <v>0.09527555025344678</v>
       </c>
       <c r="C89">
-        <v>203.302663163365</v>
+        <v>233.2779283150637</v>
       </c>
       <c r="D89">
-        <v>949.5546631633649</v>
+        <v>979.5299283150638</v>
       </c>
       <c r="E89">
         <v>344.652</v>
@@ -8585,45 +8585,45 @@
         <v>271.9</v>
       </c>
       <c r="M89">
-        <v>71.36145874738408</v>
+        <v>66.66533794738407</v>
       </c>
       <c r="N89">
-        <v>200.5385412526159</v>
+        <v>205.2346620526159</v>
       </c>
       <c r="O89">
-        <v>70.18848943841556</v>
+        <v>71.83213171841557</v>
       </c>
       <c r="P89">
-        <v>130.3500518142004</v>
+        <v>133.4025303342003</v>
       </c>
       <c r="Q89">
-        <v>296.9500518142004</v>
+        <v>300.0025303342003</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3995086033919107</v>
+        <v>0.3994287743370099</v>
       </c>
       <c r="T89">
         <v>5.145729550160114</v>
       </c>
       <c r="U89">
-        <v>0.08205748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V89">
         <v>0.35</v>
       </c>
       <c r="W89">
-        <v>0.05333736734440863</v>
+        <v>0.04982736734440862</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y89">
-        <v>3.810179959500438</v>
+        <v>4.078581289344071</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.09818360355227626</v>
+        <v>0.09508447799975453</v>
       </c>
       <c r="C90">
-        <v>194.7944815406478</v>
+        <v>225.2216270008288</v>
       </c>
       <c r="D90">
-        <v>951.0424815406478</v>
+        <v>981.4696270008288</v>
       </c>
       <c r="E90">
         <v>354.648</v>
@@ -8667,45 +8667,45 @@
         <v>271.9</v>
       </c>
       <c r="M90">
-        <v>72.18170539965286</v>
+        <v>67.43160619965286</v>
       </c>
       <c r="N90">
-        <v>199.7182946003471</v>
+        <v>204.4683938003471</v>
       </c>
       <c r="O90">
-        <v>69.90140311012149</v>
+        <v>71.56393783012149</v>
       </c>
       <c r="P90">
-        <v>129.8168914902256</v>
+        <v>132.9044559702256</v>
       </c>
       <c r="Q90">
-        <v>296.4168914902256</v>
+        <v>299.5044559702256</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.4270560024099723</v>
+        <v>0.4269699561389578</v>
       </c>
       <c r="T90">
         <v>5.54648730328785</v>
       </c>
       <c r="U90">
-        <v>0.08205748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V90">
         <v>0.35</v>
       </c>
       <c r="W90">
-        <v>0.05333736734440863</v>
+        <v>0.04982736734440862</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y90">
-        <v>3.76688245996066</v>
+        <v>4.032233774692434</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.09802757907396864</v>
+        <v>0.09691815574606225</v>
       </c>
       <c r="C91">
-        <v>186.2909696382903</v>
+        <v>196.9217544687372</v>
       </c>
       <c r="D91">
-        <v>952.5349696382904</v>
+        <v>963.1657544687372</v>
       </c>
       <c r="E91">
         <v>364.644</v>
@@ -8749,37 +8749,37 @@
         <v>271.9</v>
       </c>
       <c r="M91">
-        <v>73.00195205192165</v>
+        <v>71.31162845192165</v>
       </c>
       <c r="N91">
-        <v>198.8980479480783</v>
+        <v>200.5883715480783</v>
       </c>
       <c r="O91">
-        <v>69.61431678182741</v>
+        <v>70.20593004182741</v>
       </c>
       <c r="P91">
-        <v>129.2837311662509</v>
+        <v>130.3824415062509</v>
       </c>
       <c r="Q91">
-        <v>295.8837311662509</v>
+        <v>296.9824415062509</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4596120194313179</v>
+        <v>0.4595186255412597</v>
       </c>
       <c r="T91">
         <v>6.020110102438809</v>
       </c>
       <c r="U91">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V91">
         <v>0.35</v>
       </c>
       <c r="W91">
-        <v>0.05333736734440863</v>
+        <v>0.05210236734440863</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.724557937938629</v>
+        <v>3.812842391943344</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.09787155459566101</v>
+        <v>0.09674983349236996</v>
       </c>
       <c r="C92">
-        <v>177.7921494756769</v>
+        <v>188.5774492276756</v>
       </c>
       <c r="D92">
-        <v>954.0321494756769</v>
+        <v>964.8174492276755</v>
       </c>
       <c r="E92">
         <v>374.64</v>
@@ -8831,37 +8831,37 @@
         <v>271.9</v>
       </c>
       <c r="M92">
-        <v>73.82219870419043</v>
+        <v>72.11288270419043</v>
       </c>
       <c r="N92">
-        <v>198.0778012958095</v>
+        <v>199.7871172958095</v>
       </c>
       <c r="O92">
-        <v>69.32723045353333</v>
+        <v>69.92549105353334</v>
       </c>
       <c r="P92">
-        <v>128.7505708422762</v>
+        <v>129.8616262422762</v>
       </c>
       <c r="Q92">
-        <v>295.3505708422762</v>
+        <v>296.4616262422762</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4986792398569325</v>
+        <v>0.4985770288240221</v>
       </c>
       <c r="T92">
         <v>6.588457461419961</v>
       </c>
       <c r="U92">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V92">
         <v>0.35</v>
       </c>
       <c r="W92">
-        <v>0.05333736734440863</v>
+        <v>0.05210236734440863</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.683173960850422</v>
+        <v>3.770477476477307</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.09771553011735337</v>
+        <v>0.0965815112386777</v>
       </c>
       <c r="C93">
-        <v>169.2980432108487</v>
+        <v>180.2388185694218</v>
       </c>
       <c r="D93">
-        <v>955.5340432108488</v>
+        <v>966.4748185694218</v>
       </c>
       <c r="E93">
         <v>384.6360000000001</v>
@@ -8913,37 +8913,37 @@
         <v>271.9</v>
       </c>
       <c r="M93">
-        <v>74.64244535645922</v>
+        <v>72.91413695645922</v>
       </c>
       <c r="N93">
-        <v>197.2575546435407</v>
+        <v>198.9858630435407</v>
       </c>
       <c r="O93">
-        <v>69.04014412523925</v>
+        <v>69.64505206523926</v>
       </c>
       <c r="P93">
-        <v>128.2174105183015</v>
+        <v>129.3408109783015</v>
       </c>
       <c r="Q93">
-        <v>294.8174105183015</v>
+        <v>295.9408109783014</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.5464280648215726</v>
+        <v>0.5463150772807317</v>
       </c>
       <c r="T93">
         <v>7.283104233508036</v>
       </c>
       <c r="U93">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V93">
         <v>0.35</v>
       </c>
       <c r="W93">
-        <v>0.05333736734440863</v>
+        <v>0.05210236734440863</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.642699521720197</v>
+        <v>3.729043658054479</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.09755950563904574</v>
+        <v>0.09641318898498541</v>
       </c>
       <c r="C94">
-        <v>160.8086731415967</v>
+        <v>171.9058917877978</v>
       </c>
       <c r="D94">
-        <v>957.0406731415968</v>
+        <v>968.1378917877978</v>
       </c>
       <c r="E94">
         <v>394.6320000000001</v>
@@ -8995,37 +8995,37 @@
         <v>271.9</v>
       </c>
       <c r="M94">
-        <v>75.462692008728</v>
+        <v>73.71539120872799</v>
       </c>
       <c r="N94">
-        <v>196.437307991272</v>
+        <v>198.184608791272</v>
       </c>
       <c r="O94">
-        <v>68.75305779694519</v>
+        <v>69.36461307694519</v>
       </c>
       <c r="P94">
-        <v>127.6842501943268</v>
+        <v>128.8199957143268</v>
       </c>
       <c r="Q94">
-        <v>294.2842501943268</v>
+        <v>295.4199957143268</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.6061140960273728</v>
+        <v>0.6059876378516187</v>
       </c>
       <c r="T94">
         <v>8.151412698618129</v>
       </c>
       <c r="U94">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V94">
         <v>0.35</v>
       </c>
       <c r="W94">
-        <v>0.05333736734440863</v>
+        <v>0.05210236734440863</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.6031049617015</v>
+        <v>3.688510574814757</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.0974034811607381</v>
+        <v>0.09624486673129314</v>
       </c>
       <c r="C95">
-        <v>152.3240617065657</v>
+        <v>163.5786983786021</v>
       </c>
       <c r="D95">
-        <v>958.5520617065657</v>
+        <v>969.8066983786022</v>
       </c>
       <c r="E95">
         <v>404.628</v>
@@ -9077,37 +9077,37 @@
         <v>271.9</v>
       </c>
       <c r="M95">
-        <v>76.28293866099678</v>
+        <v>74.51664546099677</v>
       </c>
       <c r="N95">
-        <v>195.6170613390032</v>
+        <v>197.3833545390032</v>
       </c>
       <c r="O95">
-        <v>68.46597146865112</v>
+        <v>69.08417408865112</v>
       </c>
       <c r="P95">
-        <v>127.1510898703521</v>
+        <v>128.2991804503521</v>
       </c>
       <c r="Q95">
-        <v>293.7510898703521</v>
+        <v>294.8991804503521</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6828532790062587</v>
+        <v>0.6827095014427591</v>
       </c>
       <c r="T95">
         <v>9.26780929661682</v>
       </c>
       <c r="U95">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V95">
         <v>0.35</v>
       </c>
       <c r="W95">
-        <v>0.05333736734440863</v>
+        <v>0.05210236734440863</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.564361897597183</v>
+        <v>3.648849170784491</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09724745668243048</v>
+        <v>0.09607654447760086</v>
       </c>
       <c r="C96">
-        <v>143.8442314863673</v>
+        <v>155.2572680413559</v>
       </c>
       <c r="D96">
-        <v>960.0682314863674</v>
+        <v>971.481268041356</v>
       </c>
       <c r="E96">
         <v>414.624</v>
@@ -9159,37 +9159,37 @@
         <v>271.9</v>
       </c>
       <c r="M96">
-        <v>77.10318531326556</v>
+        <v>75.31789971326556</v>
       </c>
       <c r="N96">
-        <v>194.7968146867344</v>
+        <v>196.5821002867344</v>
       </c>
       <c r="O96">
-        <v>68.17888514035704</v>
+        <v>68.80373510035704</v>
       </c>
       <c r="P96">
-        <v>126.6179295463774</v>
+        <v>127.7783651863774</v>
       </c>
       <c r="Q96">
-        <v>293.2179295463774</v>
+        <v>294.3783651863774</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7851721896447734</v>
+        <v>0.7850053195642799</v>
       </c>
       <c r="T96">
         <v>10.75633809394841</v>
       </c>
       <c r="U96">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V96">
         <v>0.35</v>
       </c>
       <c r="W96">
-        <v>0.05333736734440863</v>
+        <v>0.05210236734440863</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.526443154005724</v>
+        <v>3.610031626414443</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09999368220412284</v>
+        <v>0.0959082222239086</v>
       </c>
       <c r="C97">
-        <v>107.8435222498128</v>
+        <v>146.9416306810642</v>
       </c>
       <c r="D97">
-        <v>934.0635222498129</v>
+        <v>973.1616306810644</v>
       </c>
       <c r="E97">
         <v>424.6200000000001</v>
@@ -9241,45 +9241,45 @@
         <v>271.9</v>
       </c>
       <c r="M97">
-        <v>82.38664596553434</v>
+        <v>76.11915396553435</v>
       </c>
       <c r="N97">
-        <v>189.5133540344656</v>
+        <v>195.7808460344656</v>
       </c>
       <c r="O97">
-        <v>66.32967391206297</v>
+        <v>68.52329611206297</v>
       </c>
       <c r="P97">
-        <v>123.1836801224027</v>
+        <v>127.2575499224027</v>
       </c>
       <c r="Q97">
-        <v>289.7836801224026</v>
+        <v>293.8575499224027</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.9284186645386943</v>
+        <v>0.9282194649344091</v>
       </c>
       <c r="T97">
         <v>12.84027841021264</v>
       </c>
       <c r="U97">
-        <v>0.08675748822216711</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V97">
         <v>0.35</v>
       </c>
       <c r="W97">
-        <v>0.05639236734440863</v>
+        <v>0.05210236734440863</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y97">
-        <v>3.300292138531125</v>
+        <v>3.572031293504817</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.09986820772581523</v>
+        <v>0.09573989997021631</v>
       </c>
       <c r="C98">
-        <v>99.00492181976438</v>
+        <v>138.6318164099973</v>
       </c>
       <c r="D98">
-        <v>935.2209218197643</v>
+        <v>974.8478164099972</v>
       </c>
       <c r="E98">
         <v>434.616</v>
@@ -9323,45 +9323,45 @@
         <v>271.9</v>
       </c>
       <c r="M98">
-        <v>83.25387381780311</v>
+        <v>76.92040821780311</v>
       </c>
       <c r="N98">
-        <v>188.6461261821969</v>
+        <v>194.9795917821968</v>
       </c>
       <c r="O98">
-        <v>66.0261441637689</v>
+        <v>68.24285712376889</v>
       </c>
       <c r="P98">
-        <v>122.619982018428</v>
+        <v>126.736734658428</v>
       </c>
       <c r="Q98">
-        <v>289.219982018428</v>
+        <v>293.336734658428</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.143288376879573</v>
+        <v>1.1430406829896</v>
       </c>
       <c r="T98">
         <v>15.96618888460894</v>
       </c>
       <c r="U98">
-        <v>0.08675748822216711</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V98">
         <v>0.35</v>
       </c>
       <c r="W98">
-        <v>0.05639236734440863</v>
+        <v>0.05210236734440863</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y98">
-        <v>3.265914095421426</v>
+        <v>3.534822634197476</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.0997427332475076</v>
+        <v>0.09733697771652405</v>
       </c>
       <c r="C99">
-        <v>90.1691932194359</v>
+        <v>112.8684203157187</v>
       </c>
       <c r="D99">
-        <v>936.3811932194358</v>
+        <v>959.0804203157186</v>
       </c>
       <c r="E99">
         <v>444.612</v>
@@ -9405,37 +9405,37 @@
         <v>271.9</v>
       </c>
       <c r="M99">
-        <v>84.12110167007189</v>
+        <v>80.43657607007189</v>
       </c>
       <c r="N99">
-        <v>187.7788983299281</v>
+        <v>191.4634239299281</v>
       </c>
       <c r="O99">
-        <v>65.72261441547484</v>
+        <v>67.01219837547482</v>
       </c>
       <c r="P99">
-        <v>122.0562839144533</v>
+        <v>124.4512255544532</v>
       </c>
       <c r="Q99">
-        <v>288.6562839144532</v>
+        <v>291.0512255544533</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.501404564114373</v>
+        <v>1.501076046414921</v>
       </c>
       <c r="T99">
         <v>21.17603967526949</v>
       </c>
       <c r="U99">
-        <v>0.08675748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V99">
         <v>0.35</v>
       </c>
       <c r="W99">
-        <v>0.05639236734440863</v>
+        <v>0.05392236734440863</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.232244877942855</v>
+        <v>3.380303007466849</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.09961725876919995</v>
+        <v>0.09718685546283176</v>
       </c>
       <c r="C100">
-        <v>81.33634715081519</v>
+        <v>104.3327737510934</v>
       </c>
       <c r="D100">
-        <v>937.5443471508152</v>
+        <v>960.5407737510935</v>
       </c>
       <c r="E100">
         <v>454.6080000000001</v>
@@ -9487,37 +9487,37 @@
         <v>271.9</v>
       </c>
       <c r="M100">
-        <v>84.98832952234069</v>
+        <v>81.26581912234069</v>
       </c>
       <c r="N100">
-        <v>186.9116704776593</v>
+        <v>190.6341808776593</v>
       </c>
       <c r="O100">
-        <v>65.41908466718075</v>
+        <v>66.72196330718074</v>
       </c>
       <c r="P100">
-        <v>121.4925858104785</v>
+        <v>123.9122175704785</v>
       </c>
       <c r="Q100">
-        <v>288.0925858104786</v>
+        <v>290.5122175704785</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.217636938583973</v>
+        <v>2.217146773265563</v>
       </c>
       <c r="T100">
         <v>31.59574125659058</v>
       </c>
       <c r="U100">
-        <v>0.08675748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V100">
         <v>0.35</v>
       </c>
       <c r="W100">
-        <v>0.05639236734440863</v>
+        <v>0.05392236734440863</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.1992627873516</v>
+        <v>3.345810119635554</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.09949178429089234</v>
+        <v>0.0970367332091395</v>
       </c>
       <c r="C101">
-        <v>72.50639436913116</v>
+        <v>95.80158121208842</v>
       </c>
       <c r="D101">
-        <v>938.7103943691311</v>
+        <v>962.0055812120884</v>
       </c>
       <c r="E101">
         <v>464.604</v>
@@ -9569,37 +9569,37 @@
         <v>271.9</v>
       </c>
       <c r="M101">
-        <v>85.85555737460946</v>
+        <v>82.09506217460947</v>
       </c>
       <c r="N101">
-        <v>186.0444426253905</v>
+        <v>189.8049378253905</v>
       </c>
       <c r="O101">
-        <v>65.11555491888667</v>
+        <v>66.43172823888668</v>
       </c>
       <c r="P101">
-        <v>120.9288877065038</v>
+        <v>123.3732095865038</v>
       </c>
       <c r="Q101">
-        <v>287.5288877065038</v>
+        <v>289.9732095865038</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.366334061992776</v>
+        <v>4.365358953817491</v>
       </c>
       <c r="T101">
         <v>62.85484600055388</v>
       </c>
       <c r="U101">
-        <v>0.08675748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V101">
         <v>0.35</v>
       </c>
       <c r="W101">
-        <v>0.05639236734440863</v>
+        <v>0.05392236734440863</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>3.166947001620776</v>
+        <v>3.312014057821053</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/colombia/colombia_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_oil_gas_production_and_exploration.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1118988363246747</v>
+        <v>0.1116590140709825</v>
       </c>
       <c r="C2">
-        <v>959.2192528477892</v>
+        <v>950.9961212736974</v>
       </c>
       <c r="D2">
-        <v>835.8192528477892</v>
+        <v>837.5921212736974</v>
       </c>
       <c r="E2">
-        <v>-525</v>
+        <v>-515.004</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.996</v>
       </c>
       <c r="G2">
         <v>123.4</v>
@@ -1451,28 +1451,28 @@
         <v>271.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.6912982522687826</v>
       </c>
       <c r="N2">
-        <v>271.9</v>
+        <v>271.2087017477312</v>
       </c>
       <c r="O2">
-        <v>95.16499999999999</v>
+        <v>94.92304561170592</v>
       </c>
       <c r="P2">
-        <v>176.735</v>
+        <v>176.2856561360253</v>
       </c>
       <c r="Q2">
-        <v>343.335</v>
+        <v>342.8856561360253</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1118988363246747</v>
+        <v>0.1123328185833721</v>
       </c>
       <c r="T2">
-        <v>0.9618186075065634</v>
+        <v>0.9681335781619097</v>
       </c>
       <c r="U2">
         <v>0.06915748822216712</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>393.3179334789971</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1116590140709825</v>
+        <v>0.1114191918172902</v>
       </c>
       <c r="C3">
-        <v>950.9961212736974</v>
+        <v>942.7805266004647</v>
       </c>
       <c r="D3">
-        <v>837.5921212736974</v>
+        <v>839.3725266004647</v>
       </c>
       <c r="E3">
-        <v>-515.004</v>
+        <v>-505.008</v>
       </c>
       <c r="F3">
-        <v>9.996</v>
+        <v>19.992</v>
       </c>
       <c r="G3">
         <v>123.4</v>
@@ -1533,28 +1533,28 @@
         <v>271.9</v>
       </c>
       <c r="M3">
-        <v>0.6912982522687826</v>
+        <v>1.382596504537565</v>
       </c>
       <c r="N3">
-        <v>271.2087017477312</v>
+        <v>270.5174034954624</v>
       </c>
       <c r="O3">
-        <v>94.92304561170592</v>
+        <v>94.68109122341184</v>
       </c>
       <c r="P3">
-        <v>176.2856561360253</v>
+        <v>175.8363122720506</v>
       </c>
       <c r="Q3">
-        <v>342.8856561360253</v>
+        <v>342.4363122720506</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1123328185833721</v>
+        <v>0.1127756576228592</v>
       </c>
       <c r="T3">
-        <v>0.9681335781619097</v>
+        <v>0.9745774257694056</v>
       </c>
       <c r="U3">
         <v>0.06915748822216712</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>393.3179334789971</v>
+        <v>196.6589667394985</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1114191918172902</v>
+        <v>0.1111793695635979</v>
       </c>
       <c r="C4">
-        <v>942.7805266004647</v>
+        <v>934.5725169923062</v>
       </c>
       <c r="D4">
-        <v>839.3725266004647</v>
+        <v>841.1605169923062</v>
       </c>
       <c r="E4">
-        <v>-505.008</v>
+        <v>-495.012</v>
       </c>
       <c r="F4">
-        <v>19.992</v>
+        <v>29.988</v>
       </c>
       <c r="G4">
         <v>123.4</v>
@@ -1615,28 +1615,28 @@
         <v>271.9</v>
       </c>
       <c r="M4">
-        <v>1.382596504537565</v>
+        <v>2.073894756806347</v>
       </c>
       <c r="N4">
-        <v>270.5174034954624</v>
+        <v>269.8261052431936</v>
       </c>
       <c r="O4">
-        <v>94.68109122341184</v>
+        <v>94.43913683511776</v>
       </c>
       <c r="P4">
-        <v>175.8363122720506</v>
+        <v>175.3869684080759</v>
       </c>
       <c r="Q4">
-        <v>342.4363122720506</v>
+        <v>341.9869684080759</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1127756576228592</v>
+        <v>0.1132276273641914</v>
       </c>
       <c r="T4">
-        <v>0.9745774257694056</v>
+        <v>0.9811541362141696</v>
       </c>
       <c r="U4">
         <v>0.06915748822216712</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>196.6589667394985</v>
+        <v>131.1059778263324</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1111793695635979</v>
+        <v>0.1109395473099056</v>
       </c>
       <c r="C5">
-        <v>934.5725169923062</v>
+        <v>926.3721410247009</v>
       </c>
       <c r="D5">
-        <v>841.1605169923062</v>
+        <v>842.956141024701</v>
       </c>
       <c r="E5">
-        <v>-495.012</v>
+        <v>-485.016</v>
       </c>
       <c r="F5">
-        <v>29.988</v>
+        <v>39.984</v>
       </c>
       <c r="G5">
         <v>123.4</v>
@@ -1697,28 +1697,28 @@
         <v>271.9</v>
       </c>
       <c r="M5">
-        <v>2.073894756806347</v>
+        <v>2.76519300907513</v>
       </c>
       <c r="N5">
-        <v>269.8261052431936</v>
+        <v>269.1348069909249</v>
       </c>
       <c r="O5">
-        <v>94.43913683511776</v>
+        <v>94.19718244682369</v>
       </c>
       <c r="P5">
-        <v>175.3869684080759</v>
+        <v>174.9376245441012</v>
       </c>
       <c r="Q5">
-        <v>341.9869684080759</v>
+        <v>341.5376245441012</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1132276273641914</v>
+        <v>0.1136890131418014</v>
       </c>
       <c r="T5">
-        <v>0.9811541362141696</v>
+        <v>0.9878678614598663</v>
       </c>
       <c r="U5">
         <v>0.06915748822216712</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>131.1059778263324</v>
+        <v>98.32948336974927</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1109395473099056</v>
+        <v>0.1106997250562134</v>
       </c>
       <c r="C6">
-        <v>926.3721410247009</v>
+        <v>918.1794476887922</v>
       </c>
       <c r="D6">
-        <v>842.956141024701</v>
+        <v>844.7594476887922</v>
       </c>
       <c r="E6">
-        <v>-485.016</v>
+        <v>-475.02</v>
       </c>
       <c r="F6">
-        <v>39.984</v>
+        <v>49.98</v>
       </c>
       <c r="G6">
         <v>123.4</v>
@@ -1779,28 +1779,28 @@
         <v>271.9</v>
       </c>
       <c r="M6">
-        <v>2.76519300907513</v>
+        <v>3.456491261343913</v>
       </c>
       <c r="N6">
-        <v>269.1348069909249</v>
+        <v>268.4435087386561</v>
       </c>
       <c r="O6">
-        <v>94.19718244682369</v>
+        <v>93.95522805852963</v>
       </c>
       <c r="P6">
-        <v>174.9376245441012</v>
+        <v>174.4882806801265</v>
       </c>
       <c r="Q6">
-        <v>341.5376245441012</v>
+        <v>341.0882806801264</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1136890131418014</v>
+        <v>0.1141601123042031</v>
       </c>
       <c r="T6">
-        <v>0.9878678614598663</v>
+        <v>0.9947229282896827</v>
       </c>
       <c r="U6">
         <v>0.06915748822216712</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>98.32948336974927</v>
+        <v>78.66358669579942</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1106997250562134</v>
+        <v>0.1104599028025211</v>
       </c>
       <c r="C7">
-        <v>918.1794476887922</v>
+        <v>909.9944863958412</v>
       </c>
       <c r="D7">
-        <v>844.7594476887922</v>
+        <v>846.5704863958413</v>
       </c>
       <c r="E7">
-        <v>-475.02</v>
+        <v>-465.024</v>
       </c>
       <c r="F7">
-        <v>49.98</v>
+        <v>59.97600000000001</v>
       </c>
       <c r="G7">
         <v>123.4</v>
@@ -1861,28 +1861,28 @@
         <v>271.9</v>
       </c>
       <c r="M7">
-        <v>3.456491261343913</v>
+        <v>4.147789513612696</v>
       </c>
       <c r="N7">
-        <v>268.4435087386561</v>
+        <v>267.7522104863873</v>
       </c>
       <c r="O7">
-        <v>93.95522805852963</v>
+        <v>93.71327367023555</v>
       </c>
       <c r="P7">
-        <v>174.4882806801265</v>
+        <v>174.0389368161518</v>
       </c>
       <c r="Q7">
-        <v>341.0882806801264</v>
+        <v>340.6389368161517</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1141601123042031</v>
+        <v>0.1146412348530389</v>
       </c>
       <c r="T7">
-        <v>0.9947229282896827</v>
+        <v>1.00172384760524</v>
       </c>
       <c r="U7">
         <v>0.06915748822216712</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>78.66358669579942</v>
+        <v>65.55298891316617</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1104599028025211</v>
+        <v>0.1102200805488288</v>
       </c>
       <c r="C8">
-        <v>909.9944863958412</v>
+        <v>901.817306981742</v>
       </c>
       <c r="D8">
-        <v>846.5704863958413</v>
+        <v>848.389306981742</v>
       </c>
       <c r="E8">
-        <v>-465.024</v>
+        <v>-455.028</v>
       </c>
       <c r="F8">
-        <v>59.976</v>
+        <v>69.97199999999999</v>
       </c>
       <c r="G8">
         <v>123.4</v>
@@ -1943,28 +1943,28 @@
         <v>271.9</v>
       </c>
       <c r="M8">
-        <v>4.147789513612695</v>
+        <v>4.839087765881477</v>
       </c>
       <c r="N8">
-        <v>267.7522104863873</v>
+        <v>267.0609122341185</v>
       </c>
       <c r="O8">
-        <v>93.71327367023555</v>
+        <v>93.47131928194148</v>
       </c>
       <c r="P8">
-        <v>174.0389368161518</v>
+        <v>173.589592952177</v>
       </c>
       <c r="Q8">
-        <v>340.6389368161517</v>
+        <v>340.189592952177</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1146412348530389</v>
+        <v>0.1151327041233551</v>
       </c>
       <c r="T8">
-        <v>1.00172384760524</v>
+        <v>1.008875324325433</v>
       </c>
       <c r="U8">
         <v>0.06915748822216712</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>65.55298891316619</v>
+        <v>56.18827621128531</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1102200805488288</v>
+        <v>0.1099802582951366</v>
       </c>
       <c r="C9">
-        <v>901.8173069817421</v>
+        <v>893.6479597115915</v>
       </c>
       <c r="D9">
-        <v>848.3893069817422</v>
+        <v>850.2159597115915</v>
       </c>
       <c r="E9">
-        <v>-455.028</v>
+        <v>-445.032</v>
       </c>
       <c r="F9">
-        <v>69.97200000000001</v>
+        <v>79.968</v>
       </c>
       <c r="G9">
         <v>123.4</v>
@@ -2025,28 +2025,28 @@
         <v>271.9</v>
       </c>
       <c r="M9">
-        <v>4.839087765881478</v>
+        <v>5.530386018150261</v>
       </c>
       <c r="N9">
-        <v>267.0609122341185</v>
+        <v>266.3696139818497</v>
       </c>
       <c r="O9">
-        <v>93.47131928194148</v>
+        <v>93.2293648936474</v>
       </c>
       <c r="P9">
-        <v>173.589592952177</v>
+        <v>173.1402490882023</v>
       </c>
       <c r="Q9">
-        <v>340.189592952177</v>
+        <v>339.7402490882023</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1151327041233551</v>
+        <v>0.1156348575082433</v>
       </c>
       <c r="T9">
-        <v>1.008875324325433</v>
+        <v>1.016182267930847</v>
       </c>
       <c r="U9">
         <v>0.06915748822216712</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>56.1882762112853</v>
+        <v>49.16474168487464</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1099802582951366</v>
+        <v>0.1097404360414443</v>
       </c>
       <c r="C10">
-        <v>893.6479597115915</v>
+        <v>885.4864952843202</v>
       </c>
       <c r="D10">
-        <v>850.2159597115915</v>
+        <v>852.0504952843202</v>
       </c>
       <c r="E10">
-        <v>-445.032</v>
+        <v>-435.036</v>
       </c>
       <c r="F10">
-        <v>79.968</v>
+        <v>89.964</v>
       </c>
       <c r="G10">
         <v>123.4</v>
@@ -2107,28 +2107,28 @@
         <v>271.9</v>
       </c>
       <c r="M10">
-        <v>5.530386018150261</v>
+        <v>6.221684270419042</v>
       </c>
       <c r="N10">
-        <v>266.3696139818497</v>
+        <v>265.678315729581</v>
       </c>
       <c r="O10">
-        <v>93.2293648936474</v>
+        <v>92.98741050535332</v>
       </c>
       <c r="P10">
-        <v>173.1402490882023</v>
+        <v>172.6909052242276</v>
       </c>
       <c r="Q10">
-        <v>339.7402490882023</v>
+        <v>339.2909052242276</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1156348575082433</v>
+        <v>0.116148047231261</v>
       </c>
       <c r="T10">
-        <v>1.016182267930847</v>
+        <v>1.023649803703414</v>
       </c>
       <c r="U10">
         <v>0.06915748822216712</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>49.16474168487464</v>
+        <v>43.70199260877747</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1097404360414443</v>
+        <v>0.109500613787752</v>
       </c>
       <c r="C11">
-        <v>885.4864952843202</v>
+        <v>877.3329648373831</v>
       </c>
       <c r="D11">
-        <v>852.0504952843202</v>
+        <v>853.8929648373831</v>
       </c>
       <c r="E11">
-        <v>-435.036</v>
+        <v>-425.04</v>
       </c>
       <c r="F11">
-        <v>89.964</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="G11">
         <v>123.4</v>
@@ -2189,28 +2189,28 @@
         <v>271.9</v>
       </c>
       <c r="M11">
-        <v>6.221684270419042</v>
+        <v>6.912982522687825</v>
       </c>
       <c r="N11">
-        <v>265.678315729581</v>
+        <v>264.9870174773122</v>
       </c>
       <c r="O11">
-        <v>92.98741050535332</v>
+        <v>92.74545611705926</v>
       </c>
       <c r="P11">
-        <v>172.6909052242276</v>
+        <v>172.2415613602529</v>
       </c>
       <c r="Q11">
-        <v>339.2909052242276</v>
+        <v>338.8415613602529</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.116148047231261</v>
+        <v>0.1166726411703457</v>
       </c>
       <c r="T11">
-        <v>1.023649803703414</v>
+        <v>1.031283284715371</v>
       </c>
       <c r="U11">
         <v>0.06915748822216712</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>43.70199260877747</v>
+        <v>39.33179334789972</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.109500613787752</v>
+        <v>0.1092607915340597</v>
       </c>
       <c r="C12">
-        <v>877.3329648373831</v>
+        <v>869.1874199515117</v>
       </c>
       <c r="D12">
-        <v>853.8929648373831</v>
+        <v>855.7434199515118</v>
       </c>
       <c r="E12">
-        <v>-425.04</v>
+        <v>-415.044</v>
       </c>
       <c r="F12">
-        <v>99.96000000000001</v>
+        <v>109.956</v>
       </c>
       <c r="G12">
         <v>123.4</v>
@@ -2271,28 +2271,28 @@
         <v>271.9</v>
       </c>
       <c r="M12">
-        <v>6.912982522687826</v>
+        <v>7.604280774956608</v>
       </c>
       <c r="N12">
-        <v>264.9870174773122</v>
+        <v>264.2957192250433</v>
       </c>
       <c r="O12">
-        <v>92.74545611705926</v>
+        <v>92.50350172876516</v>
       </c>
       <c r="P12">
-        <v>172.2415613602529</v>
+        <v>171.7922174962782</v>
       </c>
       <c r="Q12">
-        <v>338.8415613602529</v>
+        <v>338.3922174962781</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1166726411703457</v>
+        <v>0.117209023737275</v>
       </c>
       <c r="T12">
-        <v>1.031283284715371</v>
+        <v>1.039088304626473</v>
       </c>
       <c r="U12">
         <v>0.06915748822216712</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>39.33179334789971</v>
+        <v>35.75617577081791</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1092607915340597</v>
+        <v>0.1090209692803674</v>
       </c>
       <c r="C13">
-        <v>869.1874199515117</v>
+        <v>861.0499126555269</v>
       </c>
       <c r="D13">
-        <v>855.7434199515118</v>
+        <v>857.6019126555269</v>
       </c>
       <c r="E13">
-        <v>-415.044</v>
+        <v>-405.048</v>
       </c>
       <c r="F13">
-        <v>109.956</v>
+        <v>119.952</v>
       </c>
       <c r="G13">
         <v>123.4</v>
@@ -2353,28 +2353,28 @@
         <v>271.9</v>
       </c>
       <c r="M13">
-        <v>7.604280774956608</v>
+        <v>8.29557902722539</v>
       </c>
       <c r="N13">
-        <v>264.2957192250433</v>
+        <v>263.6044209727746</v>
       </c>
       <c r="O13">
-        <v>92.50350172876516</v>
+        <v>92.2615473404711</v>
       </c>
       <c r="P13">
-        <v>171.7922174962782</v>
+        <v>171.3428736323035</v>
       </c>
       <c r="Q13">
-        <v>338.3922174962781</v>
+        <v>337.9428736323034</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.117209023737275</v>
+        <v>0.1177575968170891</v>
       </c>
       <c r="T13">
-        <v>1.039088304626473</v>
+        <v>1.047070711353736</v>
       </c>
       <c r="U13">
         <v>0.06915748822216712</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>35.75617577081791</v>
+        <v>32.77649445658309</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1090209692803674</v>
+        <v>0.1087811470266752</v>
       </c>
       <c r="C14">
-        <v>861.0499126555269</v>
+        <v>852.9204954312145</v>
       </c>
       <c r="D14">
-        <v>857.6019126555269</v>
+        <v>859.4684954312145</v>
       </c>
       <c r="E14">
-        <v>-405.048</v>
+        <v>-395.052</v>
       </c>
       <c r="F14">
-        <v>119.952</v>
+        <v>129.948</v>
       </c>
       <c r="G14">
         <v>123.4</v>
@@ -2435,28 +2435,28 @@
         <v>271.9</v>
       </c>
       <c r="M14">
-        <v>8.29557902722539</v>
+        <v>8.986877279494173</v>
       </c>
       <c r="N14">
-        <v>263.6044209727746</v>
+        <v>262.9131227205058</v>
       </c>
       <c r="O14">
-        <v>92.2615473404711</v>
+        <v>92.01959295217702</v>
       </c>
       <c r="P14">
-        <v>171.3428736323035</v>
+        <v>170.8935297683288</v>
       </c>
       <c r="Q14">
-        <v>337.9428736323034</v>
+        <v>337.4935297683288</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1177575968170891</v>
+        <v>0.1183187807723012</v>
       </c>
       <c r="T14">
-        <v>1.047070711353736</v>
+        <v>1.055236621683925</v>
       </c>
       <c r="U14">
         <v>0.06915748822216712</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>32.77649445658309</v>
+        <v>30.25522565223054</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1087811470266752</v>
+        <v>0.1085413247729829</v>
       </c>
       <c r="C15">
-        <v>852.9204954312145</v>
+        <v>844.7992212182676</v>
       </c>
       <c r="D15">
-        <v>859.4684954312145</v>
+        <v>861.3432212182677</v>
       </c>
       <c r="E15">
-        <v>-395.052</v>
+        <v>-385.056</v>
       </c>
       <c r="F15">
-        <v>129.948</v>
+        <v>139.944</v>
       </c>
       <c r="G15">
         <v>123.4</v>
@@ -2517,28 +2517,28 @@
         <v>271.9</v>
       </c>
       <c r="M15">
-        <v>8.986877279494173</v>
+        <v>9.678175531762957</v>
       </c>
       <c r="N15">
-        <v>262.9131227205058</v>
+        <v>262.221824468237</v>
       </c>
       <c r="O15">
-        <v>92.01959295217702</v>
+        <v>91.77763856388295</v>
       </c>
       <c r="P15">
-        <v>170.8935297683288</v>
+        <v>170.4441859043541</v>
       </c>
       <c r="Q15">
-        <v>337.4935297683288</v>
+        <v>337.0441859043541</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1183187807723012</v>
+        <v>0.1188930155171694</v>
       </c>
       <c r="T15">
-        <v>1.055236621683925</v>
+        <v>1.063592436905514</v>
       </c>
       <c r="U15">
         <v>0.06915748822216712</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>30.25522565223054</v>
+        <v>28.09413810564265</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1085413247729829</v>
+        <v>0.1083015025192906</v>
       </c>
       <c r="C16">
-        <v>844.7992212182676</v>
+        <v>836.6861434192898</v>
       </c>
       <c r="D16">
-        <v>861.3432212182677</v>
+        <v>863.2261434192899</v>
       </c>
       <c r="E16">
-        <v>-385.056</v>
+        <v>-375.0599999999999</v>
       </c>
       <c r="F16">
-        <v>139.944</v>
+        <v>149.94</v>
       </c>
       <c r="G16">
         <v>123.4</v>
@@ -2599,28 +2599,28 @@
         <v>271.9</v>
       </c>
       <c r="M16">
-        <v>9.678175531762957</v>
+        <v>10.36947378403174</v>
       </c>
       <c r="N16">
-        <v>262.221824468237</v>
+        <v>261.5305262159682</v>
       </c>
       <c r="O16">
-        <v>91.77763856388295</v>
+        <v>91.53568417558887</v>
       </c>
       <c r="P16">
-        <v>170.4441859043541</v>
+        <v>169.9948420403794</v>
       </c>
       <c r="Q16">
-        <v>337.0441859043541</v>
+        <v>336.5948420403794</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1188930155171694</v>
+        <v>0.1194807616677992</v>
       </c>
       <c r="T16">
-        <v>1.063592436905514</v>
+        <v>1.072144859544081</v>
       </c>
       <c r="U16">
         <v>0.06915748822216712</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>28.09413810564265</v>
+        <v>26.22119556526647</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1083015025192906</v>
+        <v>0.1080616802655983</v>
       </c>
       <c r="C17">
-        <v>836.6861434192899</v>
+        <v>828.5813159048664</v>
       </c>
       <c r="D17">
-        <v>863.2261434192899</v>
+        <v>865.1173159048665</v>
       </c>
       <c r="E17">
-        <v>-375.06</v>
+        <v>-365.064</v>
       </c>
       <c r="F17">
-        <v>149.94</v>
+        <v>159.936</v>
       </c>
       <c r="G17">
         <v>123.4</v>
@@ -2681,28 +2681,28 @@
         <v>271.9</v>
       </c>
       <c r="M17">
-        <v>10.36947378403174</v>
+        <v>11.06077203630052</v>
       </c>
       <c r="N17">
-        <v>261.5305262159682</v>
+        <v>260.8392279636994</v>
       </c>
       <c r="O17">
-        <v>91.53568417558887</v>
+        <v>91.29372978729479</v>
       </c>
       <c r="P17">
-        <v>169.9948420403794</v>
+        <v>169.5454981764046</v>
       </c>
       <c r="Q17">
-        <v>336.5948420403794</v>
+        <v>336.1454981764047</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1194807616677992</v>
+        <v>0.1200825017743964</v>
       </c>
       <c r="T17">
-        <v>1.072144859544081</v>
+        <v>1.08090091129309</v>
       </c>
       <c r="U17">
         <v>0.06915748822216712</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>26.22119556526647</v>
+        <v>24.58237084243732</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1080616802655983</v>
+        <v>0.1078218580119061</v>
       </c>
       <c r="C18">
-        <v>828.5813159048664</v>
+        <v>820.4847930187027</v>
       </c>
       <c r="D18">
-        <v>865.1173159048665</v>
+        <v>867.0167930187027</v>
       </c>
       <c r="E18">
-        <v>-365.064</v>
+        <v>-355.068</v>
       </c>
       <c r="F18">
-        <v>159.936</v>
+        <v>169.932</v>
       </c>
       <c r="G18">
         <v>123.4</v>
@@ -2763,28 +2763,28 @@
         <v>271.9</v>
       </c>
       <c r="M18">
-        <v>11.06077203630052</v>
+        <v>11.75207028856931</v>
       </c>
       <c r="N18">
-        <v>260.8392279636994</v>
+        <v>260.1479297114307</v>
       </c>
       <c r="O18">
-        <v>91.29372978729479</v>
+        <v>91.05177539900073</v>
       </c>
       <c r="P18">
-        <v>169.5454981764046</v>
+        <v>169.0961543124299</v>
       </c>
       <c r="Q18">
-        <v>336.1454981764047</v>
+        <v>335.6961543124299</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1200825017743964</v>
+        <v>0.1206987416425983</v>
       </c>
       <c r="T18">
-        <v>1.08090091129309</v>
+        <v>1.089867952240871</v>
       </c>
       <c r="U18">
         <v>0.06915748822216712</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>24.58237084243732</v>
+        <v>23.1363490281763</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1078218580119061</v>
+        <v>0.1075820357582138</v>
       </c>
       <c r="C19">
-        <v>820.4847930187027</v>
+        <v>812.3966295828278</v>
       </c>
       <c r="D19">
-        <v>867.0167930187027</v>
+        <v>868.9246295828278</v>
       </c>
       <c r="E19">
-        <v>-355.068</v>
+        <v>-345.072</v>
       </c>
       <c r="F19">
-        <v>169.932</v>
+        <v>179.928</v>
       </c>
       <c r="G19">
         <v>123.4</v>
@@ -2845,28 +2845,28 @@
         <v>271.9</v>
       </c>
       <c r="M19">
-        <v>11.75207028856931</v>
+        <v>12.44336854083809</v>
       </c>
       <c r="N19">
-        <v>260.1479297114307</v>
+        <v>259.4566314591619</v>
       </c>
       <c r="O19">
-        <v>91.05177539900073</v>
+        <v>90.80982101070666</v>
       </c>
       <c r="P19">
-        <v>169.0961543124299</v>
+        <v>168.6468104484552</v>
       </c>
       <c r="Q19">
-        <v>335.6961543124299</v>
+        <v>335.2468104484552</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1206987416425983</v>
+        <v>0.1213300117514881</v>
       </c>
       <c r="T19">
-        <v>1.089867952240871</v>
+        <v>1.099053701504451</v>
       </c>
       <c r="U19">
         <v>0.06915748822216712</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>23.1363490281763</v>
+        <v>21.85099630438873</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1075820357582138</v>
+        <v>0.1073422135045215</v>
       </c>
       <c r="C20">
-        <v>812.3966295828277</v>
+        <v>804.3168809028704</v>
       </c>
       <c r="D20">
-        <v>868.9246295828277</v>
+        <v>870.8408809028704</v>
       </c>
       <c r="E20">
-        <v>-345.072</v>
+        <v>-335.076</v>
       </c>
       <c r="F20">
-        <v>179.928</v>
+        <v>189.924</v>
       </c>
       <c r="G20">
         <v>123.4</v>
@@ -2927,28 +2927,28 @@
         <v>271.9</v>
       </c>
       <c r="M20">
-        <v>12.44336854083808</v>
+        <v>13.13466679310687</v>
       </c>
       <c r="N20">
-        <v>259.4566314591619</v>
+        <v>258.7653332068931</v>
       </c>
       <c r="O20">
-        <v>90.80982101070666</v>
+        <v>90.56786662241258</v>
       </c>
       <c r="P20">
-        <v>168.6468104484552</v>
+        <v>168.1974665844805</v>
       </c>
       <c r="Q20">
-        <v>335.2468104484552</v>
+        <v>334.7974665844805</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1213300117514881</v>
+        <v>0.1219768687766468</v>
       </c>
       <c r="T20">
-        <v>1.099053701504451</v>
+        <v>1.108466259391824</v>
       </c>
       <c r="U20">
         <v>0.06915748822216712</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>21.85099630438873</v>
+        <v>20.70094386731564</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1073422135045215</v>
+        <v>0.1071023912508293</v>
       </c>
       <c r="C21">
-        <v>804.3168809028704</v>
+        <v>796.2456027734029</v>
       </c>
       <c r="D21">
-        <v>870.8408809028704</v>
+        <v>872.765602773403</v>
       </c>
       <c r="E21">
-        <v>-335.076</v>
+        <v>-325.08</v>
       </c>
       <c r="F21">
-        <v>189.924</v>
+        <v>199.92</v>
       </c>
       <c r="G21">
         <v>123.4</v>
@@ -3009,28 +3009,28 @@
         <v>271.9</v>
       </c>
       <c r="M21">
-        <v>13.13466679310687</v>
+        <v>13.82596504537565</v>
       </c>
       <c r="N21">
-        <v>258.7653332068931</v>
+        <v>258.0740349546243</v>
       </c>
       <c r="O21">
-        <v>90.56786662241258</v>
+        <v>90.3259122341185</v>
       </c>
       <c r="P21">
-        <v>168.1974665844805</v>
+        <v>167.7481227205058</v>
       </c>
       <c r="Q21">
-        <v>334.7974665844805</v>
+        <v>334.3481227205058</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1219768687766468</v>
+        <v>0.1226398972274344</v>
       </c>
       <c r="T21">
-        <v>1.108466259391824</v>
+        <v>1.11811413122638</v>
       </c>
       <c r="U21">
         <v>0.06915748822216712</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>20.70094386731564</v>
+        <v>19.66589667394986</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1071023912508293</v>
+        <v>0.106862568997137</v>
       </c>
       <c r="C22">
-        <v>796.2456027734029</v>
+        <v>788.1828514833561</v>
       </c>
       <c r="D22">
-        <v>872.765602773403</v>
+        <v>874.6988514833562</v>
       </c>
       <c r="E22">
-        <v>-325.08</v>
+        <v>-315.0839999999999</v>
       </c>
       <c r="F22">
-        <v>199.92</v>
+        <v>209.916</v>
       </c>
       <c r="G22">
         <v>123.4</v>
@@ -3091,28 +3091,28 @@
         <v>271.9</v>
       </c>
       <c r="M22">
-        <v>13.82596504537565</v>
+        <v>14.51726329764444</v>
       </c>
       <c r="N22">
-        <v>258.0740349546243</v>
+        <v>257.3827367023555</v>
       </c>
       <c r="O22">
-        <v>90.3259122341185</v>
+        <v>90.08395784582443</v>
       </c>
       <c r="P22">
-        <v>167.7481227205058</v>
+        <v>167.2987788565311</v>
       </c>
       <c r="Q22">
-        <v>334.3481227205058</v>
+        <v>333.8987788565311</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1226398972274344</v>
+        <v>0.1233197112086217</v>
       </c>
       <c r="T22">
-        <v>1.11811413122638</v>
+        <v>1.128006252980799</v>
       </c>
       <c r="U22">
         <v>0.06915748822216712</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>19.66589667394986</v>
+        <v>18.72942540376177</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.106862568997137</v>
+        <v>0.1066227467434447</v>
       </c>
       <c r="C23">
-        <v>788.1828514833562</v>
+        <v>780.1286838215057</v>
       </c>
       <c r="D23">
-        <v>874.6988514833562</v>
+        <v>876.6406838215057</v>
       </c>
       <c r="E23">
-        <v>-315.084</v>
+        <v>-305.088</v>
       </c>
       <c r="F23">
-        <v>209.916</v>
+        <v>219.912</v>
       </c>
       <c r="G23">
         <v>123.4</v>
@@ -3173,28 +3173,28 @@
         <v>271.9</v>
       </c>
       <c r="M23">
-        <v>14.51726329764443</v>
+        <v>15.20856154991322</v>
       </c>
       <c r="N23">
-        <v>257.3827367023555</v>
+        <v>256.6914384500868</v>
       </c>
       <c r="O23">
-        <v>90.08395784582443</v>
+        <v>89.84200345753037</v>
       </c>
       <c r="P23">
-        <v>167.2987788565311</v>
+        <v>166.8494349925564</v>
       </c>
       <c r="Q23">
-        <v>333.8987788565311</v>
+        <v>333.4494349925563</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1233197112086217</v>
+        <v>0.1240169563175318</v>
       </c>
       <c r="T23">
-        <v>1.128006252980799</v>
+        <v>1.138152018882767</v>
       </c>
       <c r="U23">
         <v>0.06915748822216712</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.72942540376177</v>
+        <v>17.87808788540896</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1066227467434447</v>
+        <v>0.1063829244897524</v>
       </c>
       <c r="C24">
-        <v>780.1286838215057</v>
+        <v>772.0831570820357</v>
       </c>
       <c r="D24">
-        <v>876.6406838215057</v>
+        <v>878.5911570820357</v>
       </c>
       <c r="E24">
-        <v>-305.088</v>
+        <v>-295.092</v>
       </c>
       <c r="F24">
-        <v>219.912</v>
+        <v>229.908</v>
       </c>
       <c r="G24">
         <v>123.4</v>
@@ -3255,28 +3255,28 @@
         <v>271.9</v>
       </c>
       <c r="M24">
-        <v>15.20856154991322</v>
+        <v>15.899859802182</v>
       </c>
       <c r="N24">
-        <v>256.6914384500868</v>
+        <v>256.000140197818</v>
       </c>
       <c r="O24">
-        <v>89.84200345753037</v>
+        <v>89.60004906923629</v>
       </c>
       <c r="P24">
-        <v>166.8494349925564</v>
+        <v>166.4000911285817</v>
       </c>
       <c r="Q24">
-        <v>333.4494349925563</v>
+        <v>333.0000911285817</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1240169563175318</v>
+        <v>0.1247323116890109</v>
       </c>
       <c r="T24">
-        <v>1.138152018882767</v>
+        <v>1.148561311171799</v>
       </c>
       <c r="U24">
         <v>0.06915748822216712</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>17.87808788540896</v>
+        <v>17.10077971647813</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1063829244897524</v>
+        <v>0.1061431022360601</v>
       </c>
       <c r="C25">
-        <v>772.0831570820357</v>
+        <v>764.04632907017</v>
       </c>
       <c r="D25">
-        <v>878.5911570820357</v>
+        <v>880.5503290701701</v>
       </c>
       <c r="E25">
-        <v>-295.092</v>
+        <v>-285.096</v>
       </c>
       <c r="F25">
-        <v>229.908</v>
+        <v>239.904</v>
       </c>
       <c r="G25">
         <v>123.4</v>
@@ -3337,28 +3337,28 @@
         <v>271.9</v>
       </c>
       <c r="M25">
-        <v>15.899859802182</v>
+        <v>16.59115805445078</v>
       </c>
       <c r="N25">
-        <v>256.000140197818</v>
+        <v>255.3088419455492</v>
       </c>
       <c r="O25">
-        <v>89.60004906923629</v>
+        <v>89.35809468094222</v>
       </c>
       <c r="P25">
-        <v>166.4000911285817</v>
+        <v>165.950747264607</v>
       </c>
       <c r="Q25">
-        <v>333.0000911285817</v>
+        <v>332.550747264607</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1247323116890109</v>
+        <v>0.1254664922018448</v>
       </c>
       <c r="T25">
-        <v>1.148561311171799</v>
+        <v>1.159244532205279</v>
       </c>
       <c r="U25">
         <v>0.06915748822216712</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.10077971647813</v>
+        <v>16.38824722829155</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1061431022360601</v>
+        <v>0.1059032799823679</v>
       </c>
       <c r="C26">
-        <v>764.04632907017</v>
+        <v>756.0182581078858</v>
       </c>
       <c r="D26">
-        <v>880.5503290701701</v>
+        <v>882.5182581078858</v>
       </c>
       <c r="E26">
-        <v>-285.096</v>
+        <v>-275.1</v>
       </c>
       <c r="F26">
-        <v>239.904</v>
+        <v>249.9</v>
       </c>
       <c r="G26">
         <v>123.4</v>
@@ -3419,28 +3419,28 @@
         <v>271.9</v>
       </c>
       <c r="M26">
-        <v>16.59115805445078</v>
+        <v>17.28245630671956</v>
       </c>
       <c r="N26">
-        <v>255.3088419455492</v>
+        <v>254.6175436932804</v>
       </c>
       <c r="O26">
-        <v>89.35809468094222</v>
+        <v>89.11614029264814</v>
       </c>
       <c r="P26">
-        <v>165.950747264607</v>
+        <v>165.5014034006323</v>
       </c>
       <c r="Q26">
-        <v>332.550747264607</v>
+        <v>332.1014034006323</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1254664922018448</v>
+        <v>0.1262202508616876</v>
       </c>
       <c r="T26">
-        <v>1.159244532205279</v>
+        <v>1.170212639132986</v>
       </c>
       <c r="U26">
         <v>0.06915748822216712</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.38824722829155</v>
+        <v>15.73271733915989</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1059032799823679</v>
+        <v>0.1056634577286756</v>
       </c>
       <c r="C27">
-        <v>756.0182581078858</v>
+        <v>747.9990030396993</v>
       </c>
       <c r="D27">
-        <v>882.5182581078858</v>
+        <v>884.4950030396994</v>
       </c>
       <c r="E27">
-        <v>-275.1</v>
+        <v>-265.104</v>
       </c>
       <c r="F27">
-        <v>249.9</v>
+        <v>259.896</v>
       </c>
       <c r="G27">
         <v>123.4</v>
@@ -3501,28 +3501,28 @@
         <v>271.9</v>
       </c>
       <c r="M27">
-        <v>17.28245630671956</v>
+        <v>17.97375455898835</v>
       </c>
       <c r="N27">
-        <v>254.6175436932804</v>
+        <v>253.9262454410116</v>
       </c>
       <c r="O27">
-        <v>89.11614029264814</v>
+        <v>88.87418590435406</v>
       </c>
       <c r="P27">
-        <v>165.5014034006323</v>
+        <v>165.0520595366576</v>
       </c>
       <c r="Q27">
-        <v>332.1014034006323</v>
+        <v>331.6520595366576</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1262202508616876</v>
+        <v>0.1269943813772018</v>
       </c>
       <c r="T27">
-        <v>1.170212639132986</v>
+        <v>1.181477181383062</v>
       </c>
       <c r="U27">
         <v>0.06915748822216712</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.73271733915989</v>
+        <v>15.12761282611527</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1056634577286756</v>
+        <v>0.1054236354749833</v>
       </c>
       <c r="C28">
-        <v>747.9990030396993</v>
+        <v>739.9886232385325</v>
       </c>
       <c r="D28">
-        <v>884.4950030396994</v>
+        <v>886.4806232385324</v>
       </c>
       <c r="E28">
-        <v>-265.104</v>
+        <v>-255.108</v>
       </c>
       <c r="F28">
-        <v>259.896</v>
+        <v>269.892</v>
       </c>
       <c r="G28">
         <v>123.4</v>
@@ -3583,28 +3583,28 @@
         <v>271.9</v>
       </c>
       <c r="M28">
-        <v>17.97375455898835</v>
+        <v>18.66505281125713</v>
       </c>
       <c r="N28">
-        <v>253.9262454410116</v>
+        <v>253.2349471887428</v>
       </c>
       <c r="O28">
-        <v>88.87418590435406</v>
+        <v>88.63223151605999</v>
       </c>
       <c r="P28">
-        <v>165.0520595366576</v>
+        <v>164.6027156726828</v>
       </c>
       <c r="Q28">
-        <v>331.6520595366576</v>
+        <v>331.2027156726829</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1269943813772018</v>
+        <v>0.1277897209479356</v>
       </c>
       <c r="T28">
-        <v>1.181477181383062</v>
+        <v>1.193050341229032</v>
       </c>
       <c r="U28">
         <v>0.06915748822216712</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.12761282611527</v>
+        <v>14.56733086959248</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1054236354749833</v>
+        <v>0.1051838132212911</v>
       </c>
       <c r="C29">
-        <v>739.9886232385325</v>
+        <v>731.9871786116549</v>
       </c>
       <c r="D29">
-        <v>886.4806232385324</v>
+        <v>888.475178611655</v>
       </c>
       <c r="E29">
-        <v>-255.108</v>
+        <v>-245.112</v>
       </c>
       <c r="F29">
-        <v>269.892</v>
+        <v>279.888</v>
       </c>
       <c r="G29">
         <v>123.4</v>
@@ -3665,28 +3665,28 @@
         <v>271.9</v>
       </c>
       <c r="M29">
-        <v>18.66505281125713</v>
+        <v>19.35635106352591</v>
       </c>
       <c r="N29">
-        <v>253.2349471887428</v>
+        <v>252.5436489364741</v>
       </c>
       <c r="O29">
-        <v>88.63223151605999</v>
+        <v>88.39027712776591</v>
       </c>
       <c r="P29">
-        <v>164.6027156726828</v>
+        <v>164.1533718087081</v>
       </c>
       <c r="Q29">
-        <v>331.2027156726829</v>
+        <v>330.7533718087082</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1277897209479356</v>
+        <v>0.1286071532845231</v>
       </c>
       <c r="T29">
-        <v>1.193050341229032</v>
+        <v>1.204944977737389</v>
       </c>
       <c r="U29">
         <v>0.06915748822216712</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.56733086959248</v>
+        <v>14.04706905282132</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1051838132212911</v>
+        <v>0.1049439909675988</v>
       </c>
       <c r="C30">
-        <v>731.9871786116549</v>
+        <v>723.9947296067124</v>
       </c>
       <c r="D30">
-        <v>888.475178611655</v>
+        <v>890.4787296067125</v>
       </c>
       <c r="E30">
-        <v>-245.112</v>
+        <v>-235.116</v>
       </c>
       <c r="F30">
-        <v>279.888</v>
+        <v>289.884</v>
       </c>
       <c r="G30">
         <v>123.4</v>
@@ -3747,28 +3747,28 @@
         <v>271.9</v>
       </c>
       <c r="M30">
-        <v>19.35635106352591</v>
+        <v>20.04764931579469</v>
       </c>
       <c r="N30">
-        <v>252.5436489364741</v>
+        <v>251.8523506842053</v>
       </c>
       <c r="O30">
-        <v>88.39027712776591</v>
+        <v>88.14832273947184</v>
       </c>
       <c r="P30">
-        <v>164.1533718087081</v>
+        <v>163.7040279447334</v>
       </c>
       <c r="Q30">
-        <v>330.7533718087082</v>
+        <v>330.3040279447334</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1286071532845231</v>
+        <v>0.129447611884113</v>
       </c>
       <c r="T30">
-        <v>1.204944977737389</v>
+        <v>1.217174674429081</v>
       </c>
       <c r="U30">
         <v>0.06915748822216712</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.04706905282132</v>
+        <v>13.56268736134473</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1049439909675988</v>
+        <v>0.1047041687139065</v>
       </c>
       <c r="C31">
-        <v>723.9947296067124</v>
+        <v>716.0113372178299</v>
       </c>
       <c r="D31">
-        <v>890.4787296067125</v>
+        <v>892.4913372178299</v>
       </c>
       <c r="E31">
-        <v>-235.116</v>
+        <v>-225.12</v>
       </c>
       <c r="F31">
-        <v>289.884</v>
+        <v>299.88</v>
       </c>
       <c r="G31">
         <v>123.4</v>
@@ -3829,28 +3829,28 @@
         <v>271.9</v>
       </c>
       <c r="M31">
-        <v>20.04764931579469</v>
+        <v>20.73894756806348</v>
       </c>
       <c r="N31">
-        <v>251.8523506842053</v>
+        <v>251.1610524319365</v>
       </c>
       <c r="O31">
-        <v>88.14832273947184</v>
+        <v>87.90636835117778</v>
       </c>
       <c r="P31">
-        <v>163.7040279447334</v>
+        <v>163.2546840807587</v>
       </c>
       <c r="Q31">
-        <v>330.3040279447334</v>
+        <v>329.8546840807587</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.129447611884113</v>
+        <v>0.1303120835865484</v>
       </c>
       <c r="T31">
-        <v>1.217174674429081</v>
+        <v>1.229753791026249</v>
       </c>
       <c r="U31">
         <v>0.06915748822216712</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.56268736134473</v>
+        <v>13.11059778263324</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1047041687139065</v>
+        <v>0.1047665964602142</v>
       </c>
       <c r="C32">
-        <v>716.0113372178299</v>
+        <v>705.4905632150862</v>
       </c>
       <c r="D32">
-        <v>892.4913372178299</v>
+        <v>891.9665632150862</v>
       </c>
       <c r="E32">
-        <v>-225.12</v>
+        <v>-215.124</v>
       </c>
       <c r="F32">
-        <v>299.88</v>
+        <v>309.876</v>
       </c>
       <c r="G32">
         <v>123.4</v>
@@ -3911,45 +3911,45 @@
         <v>271.9</v>
       </c>
       <c r="M32">
-        <v>20.73894756806348</v>
+        <v>21.89505982033226</v>
       </c>
       <c r="N32">
-        <v>251.1610524319365</v>
+        <v>250.0049401796677</v>
       </c>
       <c r="O32">
-        <v>87.90636835117778</v>
+        <v>87.5017290628837</v>
       </c>
       <c r="P32">
-        <v>163.2546840807587</v>
+        <v>162.503211116784</v>
       </c>
       <c r="Q32">
-        <v>329.8546840807587</v>
+        <v>329.103211116784</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1303120835865484</v>
+        <v>0.131201612439779</v>
       </c>
       <c r="T32">
-        <v>1.229753791026249</v>
+        <v>1.242697519698698</v>
       </c>
       <c r="U32">
-        <v>0.06915748822216712</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V32">
         <v>0.35</v>
       </c>
       <c r="W32">
-        <v>0.04495236734440863</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y32">
-        <v>13.11059778263324</v>
+        <v>12.41832642756735</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1047665964602142</v>
+        <v>0.1045365242065219</v>
       </c>
       <c r="C33">
-        <v>705.4905632150862</v>
+        <v>697.431634465521</v>
       </c>
       <c r="D33">
-        <v>891.9665632150862</v>
+        <v>893.903634465521</v>
       </c>
       <c r="E33">
-        <v>-215.124</v>
+        <v>-205.128</v>
       </c>
       <c r="F33">
-        <v>309.876</v>
+        <v>319.872</v>
       </c>
       <c r="G33">
         <v>123.4</v>
@@ -3993,28 +3993,28 @@
         <v>271.9</v>
       </c>
       <c r="M33">
-        <v>21.89505982033226</v>
+        <v>22.60135207260104</v>
       </c>
       <c r="N33">
-        <v>250.0049401796677</v>
+        <v>249.2986479273989</v>
       </c>
       <c r="O33">
-        <v>87.5017290628837</v>
+        <v>87.25452677458962</v>
       </c>
       <c r="P33">
-        <v>162.503211116784</v>
+        <v>162.0441211528093</v>
       </c>
       <c r="Q33">
-        <v>329.103211116784</v>
+        <v>328.6441211528094</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.131201612439779</v>
+        <v>0.13211730390634</v>
       </c>
       <c r="T33">
-        <v>1.242697519698698</v>
+        <v>1.256021946273277</v>
       </c>
       <c r="U33">
         <v>0.07065748822216711</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>12.41832642756735</v>
+        <v>12.03025372670587</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1045365242065219</v>
+        <v>0.1043064519528296</v>
       </c>
       <c r="C34">
-        <v>697.431634465521</v>
+        <v>689.3811374478548</v>
       </c>
       <c r="D34">
-        <v>893.903634465521</v>
+        <v>895.8491374478549</v>
       </c>
       <c r="E34">
-        <v>-205.128</v>
+        <v>-195.132</v>
       </c>
       <c r="F34">
-        <v>319.872</v>
+        <v>329.868</v>
       </c>
       <c r="G34">
         <v>123.4</v>
@@ -4075,28 +4075,28 @@
         <v>271.9</v>
       </c>
       <c r="M34">
-        <v>22.60135207260104</v>
+        <v>23.30764432486982</v>
       </c>
       <c r="N34">
-        <v>249.2986479273989</v>
+        <v>248.5923556751302</v>
       </c>
       <c r="O34">
-        <v>87.25452677458962</v>
+        <v>87.00732448629556</v>
       </c>
       <c r="P34">
-        <v>162.0441211528093</v>
+        <v>161.5850311888346</v>
       </c>
       <c r="Q34">
-        <v>328.6441211528094</v>
+        <v>328.1850311888346</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.13211730390634</v>
+        <v>0.1330603294465296</v>
       </c>
       <c r="T34">
-        <v>1.256021946273277</v>
+        <v>1.269744116924709</v>
       </c>
       <c r="U34">
         <v>0.07065748822216711</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>12.03025372670587</v>
+        <v>11.66570058347236</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1043064519528296</v>
+        <v>0.1040763796991374</v>
       </c>
       <c r="C35">
-        <v>689.3811374478548</v>
+        <v>681.339127334945</v>
       </c>
       <c r="D35">
-        <v>895.8491374478549</v>
+        <v>897.8031273349451</v>
       </c>
       <c r="E35">
-        <v>-195.132</v>
+        <v>-185.136</v>
       </c>
       <c r="F35">
-        <v>329.868</v>
+        <v>339.864</v>
       </c>
       <c r="G35">
         <v>123.4</v>
@@ -4157,28 +4157,28 @@
         <v>271.9</v>
       </c>
       <c r="M35">
-        <v>23.30764432486982</v>
+        <v>24.0139365771386</v>
       </c>
       <c r="N35">
-        <v>248.5923556751302</v>
+        <v>247.8860634228614</v>
       </c>
       <c r="O35">
-        <v>87.00732448629556</v>
+        <v>86.76012219800148</v>
       </c>
       <c r="P35">
-        <v>161.5850311888346</v>
+        <v>161.1259412248599</v>
       </c>
       <c r="Q35">
-        <v>328.1850311888346</v>
+        <v>327.7259412248599</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1330603294465296</v>
+        <v>0.1340319315182401</v>
       </c>
       <c r="T35">
-        <v>1.269744116924709</v>
+        <v>1.283882110929216</v>
       </c>
       <c r="U35">
         <v>0.07065748822216711</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.66570058347236</v>
+        <v>11.32259174278199</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1040763796991374</v>
+        <v>0.1038463074454451</v>
       </c>
       <c r="C36">
-        <v>681.339127334945</v>
+        <v>673.3056597820643</v>
       </c>
       <c r="D36">
-        <v>897.8031273349451</v>
+        <v>899.7656597820643</v>
       </c>
       <c r="E36">
-        <v>-185.136</v>
+        <v>-175.14</v>
       </c>
       <c r="F36">
-        <v>339.864</v>
+        <v>349.86</v>
       </c>
       <c r="G36">
         <v>123.4</v>
@@ -4239,28 +4239,28 @@
         <v>271.9</v>
       </c>
       <c r="M36">
-        <v>24.0139365771386</v>
+        <v>24.72022882940739</v>
       </c>
       <c r="N36">
-        <v>247.8860634228614</v>
+        <v>247.1797711705926</v>
       </c>
       <c r="O36">
-        <v>86.76012219800148</v>
+        <v>86.51291990970741</v>
       </c>
       <c r="P36">
-        <v>161.1259412248599</v>
+        <v>160.6668512608852</v>
       </c>
       <c r="Q36">
-        <v>327.7259412248599</v>
+        <v>327.2668512608852</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1340319315182401</v>
+        <v>0.1350334290383109</v>
       </c>
       <c r="T36">
-        <v>1.283882110929216</v>
+        <v>1.298455120133861</v>
       </c>
       <c r="U36">
         <v>0.07065748822216711</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.32259174278199</v>
+        <v>10.99908912155965</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1038463074454451</v>
+        <v>0.1036162351917528</v>
       </c>
       <c r="C37">
-        <v>673.3056597820643</v>
+        <v>665.2807909321848</v>
       </c>
       <c r="D37">
-        <v>899.7656597820643</v>
+        <v>901.7367909321848</v>
       </c>
       <c r="E37">
-        <v>-175.14</v>
+        <v>-165.1439999999999</v>
       </c>
       <c r="F37">
-        <v>349.86</v>
+        <v>359.8560000000001</v>
       </c>
       <c r="G37">
         <v>123.4</v>
@@ -4321,28 +4321,28 @@
         <v>271.9</v>
       </c>
       <c r="M37">
-        <v>24.72022882940739</v>
+        <v>25.42652108167617</v>
       </c>
       <c r="N37">
-        <v>247.1797711705926</v>
+        <v>246.4734789183238</v>
       </c>
       <c r="O37">
-        <v>86.51291990970741</v>
+        <v>86.26571762141332</v>
       </c>
       <c r="P37">
-        <v>160.6668512608852</v>
+        <v>160.2077612969105</v>
       </c>
       <c r="Q37">
-        <v>327.2668512608852</v>
+        <v>326.8077612969105</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1350334290383109</v>
+        <v>0.1360662233558839</v>
       </c>
       <c r="T37">
-        <v>1.298455120133861</v>
+        <v>1.313483535876151</v>
       </c>
       <c r="U37">
         <v>0.07065748822216711</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.99908912155965</v>
+        <v>10.69355886818299</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1036162351917528</v>
+        <v>0.1033861629380605</v>
       </c>
       <c r="C38">
-        <v>665.2807909321848</v>
+        <v>657.2645774213324</v>
       </c>
       <c r="D38">
-        <v>901.7367909321848</v>
+        <v>903.7165774213324</v>
       </c>
       <c r="E38">
-        <v>-165.144</v>
+        <v>-155.148</v>
       </c>
       <c r="F38">
-        <v>359.856</v>
+        <v>369.852</v>
       </c>
       <c r="G38">
         <v>123.4</v>
@@ -4403,28 +4403,28 @@
         <v>271.9</v>
       </c>
       <c r="M38">
-        <v>25.42652108167617</v>
+        <v>26.13281333394495</v>
       </c>
       <c r="N38">
-        <v>246.4734789183238</v>
+        <v>245.767186666055</v>
       </c>
       <c r="O38">
-        <v>86.26571762141333</v>
+        <v>86.01851533311925</v>
       </c>
       <c r="P38">
-        <v>160.2077612969105</v>
+        <v>159.7486713329358</v>
       </c>
       <c r="Q38">
-        <v>326.8077612969105</v>
+        <v>326.3486713329357</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1360662233558839</v>
+        <v>0.1371318047946498</v>
       </c>
       <c r="T38">
-        <v>1.313483535876151</v>
+        <v>1.328989044181688</v>
       </c>
       <c r="U38">
         <v>0.07065748822216711</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.69355886818299</v>
+        <v>10.4045437636375</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1033861629380605</v>
+        <v>0.1031560906843683</v>
       </c>
       <c r="C39">
-        <v>657.2645774213324</v>
+        <v>649.2570763840106</v>
       </c>
       <c r="D39">
-        <v>903.7165774213324</v>
+        <v>905.7050763840105</v>
       </c>
       <c r="E39">
-        <v>-155.148</v>
+        <v>-145.152</v>
       </c>
       <c r="F39">
-        <v>369.852</v>
+        <v>379.848</v>
       </c>
       <c r="G39">
         <v>123.4</v>
@@ -4485,28 +4485,28 @@
         <v>271.9</v>
       </c>
       <c r="M39">
-        <v>26.13281333394495</v>
+        <v>26.83910558621373</v>
       </c>
       <c r="N39">
-        <v>245.767186666055</v>
+        <v>245.0608944137862</v>
       </c>
       <c r="O39">
-        <v>86.01851533311925</v>
+        <v>85.77131304482518</v>
       </c>
       <c r="P39">
-        <v>159.7486713329358</v>
+        <v>159.2895813689611</v>
       </c>
       <c r="Q39">
-        <v>326.3486713329357</v>
+        <v>325.889581368961</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1371318047946498</v>
+        <v>0.1382317598282145</v>
       </c>
       <c r="T39">
-        <v>1.328989044181688</v>
+        <v>1.344994730174501</v>
       </c>
       <c r="U39">
         <v>0.07065748822216711</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.4045437636375</v>
+        <v>10.13073998038389</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1031560906843683</v>
+        <v>0.102926018430676</v>
       </c>
       <c r="C40">
-        <v>649.2570763840106</v>
+        <v>641.2583454586972</v>
       </c>
       <c r="D40">
-        <v>905.7050763840105</v>
+        <v>907.7023454586972</v>
       </c>
       <c r="E40">
-        <v>-145.152</v>
+        <v>-135.156</v>
       </c>
       <c r="F40">
-        <v>379.848</v>
+        <v>389.844</v>
       </c>
       <c r="G40">
         <v>123.4</v>
@@ -4567,28 +4567,28 @@
         <v>271.9</v>
       </c>
       <c r="M40">
-        <v>26.83910558621373</v>
+        <v>27.54539783848251</v>
       </c>
       <c r="N40">
-        <v>245.0608944137862</v>
+        <v>244.3546021615174</v>
       </c>
       <c r="O40">
-        <v>85.77131304482518</v>
+        <v>85.5241107565311</v>
       </c>
       <c r="P40">
-        <v>159.2895813689611</v>
+        <v>158.8304914049863</v>
       </c>
       <c r="Q40">
-        <v>325.889581368961</v>
+        <v>325.4304914049864</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1382317598282145</v>
+        <v>0.1393677789612404</v>
       </c>
       <c r="T40">
-        <v>1.344994730174501</v>
+        <v>1.361525192757242</v>
       </c>
       <c r="U40">
         <v>0.07065748822216711</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.13073998038389</v>
+        <v>9.870977416784299</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.102926018430676</v>
+        <v>0.1031379461769837</v>
       </c>
       <c r="C41">
-        <v>641.2583454586972</v>
+        <v>629.4222704785656</v>
       </c>
       <c r="D41">
-        <v>907.7023454586972</v>
+        <v>905.8622704785656</v>
       </c>
       <c r="E41">
-        <v>-135.156</v>
+        <v>-125.16</v>
       </c>
       <c r="F41">
-        <v>389.844</v>
+        <v>399.84</v>
       </c>
       <c r="G41">
         <v>123.4</v>
@@ -4649,45 +4649,45 @@
         <v>271.9</v>
       </c>
       <c r="M41">
-        <v>27.54539783848251</v>
+        <v>28.9314180907513</v>
       </c>
       <c r="N41">
-        <v>244.3546021615174</v>
+        <v>242.9685819092487</v>
       </c>
       <c r="O41">
-        <v>85.5241107565311</v>
+        <v>85.03900366823703</v>
       </c>
       <c r="P41">
-        <v>158.8304914049863</v>
+        <v>157.9295782410117</v>
       </c>
       <c r="Q41">
-        <v>325.4304914049864</v>
+        <v>324.5295782410117</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1393677789612404</v>
+        <v>0.1405416653987005</v>
       </c>
       <c r="T41">
-        <v>1.361525192757242</v>
+        <v>1.378606670759408</v>
       </c>
       <c r="U41">
-        <v>0.07065748822216711</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V41">
         <v>0.35</v>
       </c>
       <c r="W41">
-        <v>0.04592736734440862</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>9.870977416784299</v>
+        <v>9.398087544382074</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1031379461769837</v>
+        <v>0.1029189239232915</v>
       </c>
       <c r="C42">
-        <v>629.4222704785656</v>
+        <v>621.3280732538326</v>
       </c>
       <c r="D42">
-        <v>905.8622704785656</v>
+        <v>907.7640732538326</v>
       </c>
       <c r="E42">
-        <v>-125.16</v>
+        <v>-115.164</v>
       </c>
       <c r="F42">
-        <v>399.84</v>
+        <v>409.836</v>
       </c>
       <c r="G42">
         <v>123.4</v>
@@ -4731,28 +4731,28 @@
         <v>271.9</v>
       </c>
       <c r="M42">
-        <v>28.9314180907513</v>
+        <v>29.65470354302008</v>
       </c>
       <c r="N42">
-        <v>242.9685819092487</v>
+        <v>242.2452964569799</v>
       </c>
       <c r="O42">
-        <v>85.03900366823703</v>
+        <v>84.78585375994297</v>
       </c>
       <c r="P42">
-        <v>157.9295782410117</v>
+        <v>157.4594426970369</v>
       </c>
       <c r="Q42">
-        <v>324.5295782410117</v>
+        <v>324.059442697037</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1405416653987005</v>
+        <v>0.1417553445967524</v>
       </c>
       <c r="T42">
-        <v>1.378606670759408</v>
+        <v>1.396267181914189</v>
       </c>
       <c r="U42">
         <v>0.07235748822216712</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.398087544382074</v>
+        <v>9.16886589695812</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1029189239232915</v>
+        <v>0.1026999016695992</v>
       </c>
       <c r="C43">
-        <v>621.3280732538326</v>
+        <v>613.2418782679699</v>
       </c>
       <c r="D43">
-        <v>907.7640732538326</v>
+        <v>909.6738782679701</v>
       </c>
       <c r="E43">
-        <v>-115.164</v>
+        <v>-105.1679999999999</v>
       </c>
       <c r="F43">
-        <v>409.836</v>
+        <v>419.8320000000001</v>
       </c>
       <c r="G43">
         <v>123.4</v>
@@ -4813,28 +4813,28 @@
         <v>271.9</v>
       </c>
       <c r="M43">
-        <v>29.65470354302008</v>
+        <v>30.37798899528887</v>
       </c>
       <c r="N43">
-        <v>242.2452964569799</v>
+        <v>241.5220110047111</v>
       </c>
       <c r="O43">
-        <v>84.78585375994297</v>
+        <v>84.53270385164889</v>
       </c>
       <c r="P43">
-        <v>157.4594426970369</v>
+        <v>156.9893071530622</v>
       </c>
       <c r="Q43">
-        <v>324.059442697037</v>
+        <v>323.5893071530622</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1417553445967524</v>
+        <v>0.1430108748016337</v>
       </c>
       <c r="T43">
-        <v>1.396267181914189</v>
+        <v>1.414536676212239</v>
       </c>
       <c r="U43">
         <v>0.07235748822216712</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.16886589695812</v>
+        <v>8.950559566078166</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1026999016695992</v>
+        <v>0.1024808794159069</v>
       </c>
       <c r="C44">
-        <v>613.24187826797</v>
+        <v>605.1637361341391</v>
       </c>
       <c r="D44">
-        <v>909.6738782679701</v>
+        <v>911.591736134139</v>
       </c>
       <c r="E44">
-        <v>-105.168</v>
+        <v>-95.17199999999997</v>
       </c>
       <c r="F44">
-        <v>419.832</v>
+        <v>429.828</v>
       </c>
       <c r="G44">
         <v>123.4</v>
@@ -4895,28 +4895,28 @@
         <v>271.9</v>
       </c>
       <c r="M44">
-        <v>30.37798899528886</v>
+        <v>31.10127444755765</v>
       </c>
       <c r="N44">
-        <v>241.5220110047111</v>
+        <v>240.7987255524423</v>
       </c>
       <c r="O44">
-        <v>84.53270385164889</v>
+        <v>84.27955394335481</v>
       </c>
       <c r="P44">
-        <v>156.9893071530622</v>
+        <v>156.5191716090875</v>
       </c>
       <c r="Q44">
-        <v>323.5893071530622</v>
+        <v>323.1191716090875</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1430108748016337</v>
+        <v>0.1443104586979144</v>
       </c>
       <c r="T44">
-        <v>1.414536676212239</v>
+        <v>1.43344720539794</v>
       </c>
       <c r="U44">
         <v>0.07235748822216712</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.950559566078166</v>
+        <v>8.742407018029835</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1024808794159069</v>
+        <v>0.1022618571622146</v>
       </c>
       <c r="C45">
-        <v>605.1637361341391</v>
+        <v>597.0936978932311</v>
       </c>
       <c r="D45">
-        <v>911.591736134139</v>
+        <v>913.5176978932311</v>
       </c>
       <c r="E45">
-        <v>-95.17199999999997</v>
+        <v>-85.17599999999999</v>
       </c>
       <c r="F45">
-        <v>429.828</v>
+        <v>439.824</v>
       </c>
       <c r="G45">
         <v>123.4</v>
@@ -4977,28 +4977,28 @@
         <v>271.9</v>
       </c>
       <c r="M45">
-        <v>31.10127444755765</v>
+        <v>31.82455989982643</v>
       </c>
       <c r="N45">
-        <v>240.7987255524423</v>
+        <v>240.0754401001736</v>
       </c>
       <c r="O45">
-        <v>84.27955394335481</v>
+        <v>84.02640403506074</v>
       </c>
       <c r="P45">
-        <v>156.5191716090875</v>
+        <v>156.0490360651128</v>
       </c>
       <c r="Q45">
-        <v>323.1191716090875</v>
+        <v>322.6490360651128</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1443104586979144</v>
+        <v>0.1456564563047765</v>
       </c>
       <c r="T45">
-        <v>1.43344720539794</v>
+        <v>1.453033110625987</v>
       </c>
       <c r="U45">
         <v>0.07235748822216712</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.742407018029835</v>
+        <v>8.543715949438248</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1022618571622146</v>
+        <v>0.1020428349085224</v>
       </c>
       <c r="C46">
-        <v>597.0936978932311</v>
+        <v>589.0318150183971</v>
       </c>
       <c r="D46">
-        <v>913.5176978932311</v>
+        <v>915.4518150183969</v>
       </c>
       <c r="E46">
-        <v>-85.17599999999999</v>
+        <v>-75.18000000000001</v>
       </c>
       <c r="F46">
-        <v>439.824</v>
+        <v>449.82</v>
       </c>
       <c r="G46">
         <v>123.4</v>
@@ -5059,28 +5059,28 @@
         <v>271.9</v>
       </c>
       <c r="M46">
-        <v>31.82455989982643</v>
+        <v>32.54784535209521</v>
       </c>
       <c r="N46">
-        <v>240.0754401001736</v>
+        <v>239.3521546479048</v>
       </c>
       <c r="O46">
-        <v>84.02640403506074</v>
+        <v>83.77325412676666</v>
       </c>
       <c r="P46">
-        <v>156.0490360651128</v>
+        <v>155.5789005211381</v>
       </c>
       <c r="Q46">
-        <v>322.6490360651128</v>
+        <v>322.1789005211381</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1456564563047765</v>
+        <v>0.1470513992791609</v>
       </c>
       <c r="T46">
-        <v>1.453033110625987</v>
+        <v>1.473331230589599</v>
       </c>
       <c r="U46">
         <v>0.07235748822216712</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.543715949438248</v>
+        <v>8.353855595006287</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1020428349085224</v>
+        <v>0.1018238126548301</v>
       </c>
       <c r="C47">
-        <v>589.0318150183971</v>
+        <v>580.9781394196323</v>
       </c>
       <c r="D47">
-        <v>915.4518150183969</v>
+        <v>917.3941394196322</v>
       </c>
       <c r="E47">
-        <v>-75.18000000000001</v>
+        <v>-65.18399999999997</v>
       </c>
       <c r="F47">
-        <v>449.82</v>
+        <v>459.816</v>
       </c>
       <c r="G47">
         <v>123.4</v>
@@ -5141,28 +5141,28 @@
         <v>271.9</v>
       </c>
       <c r="M47">
-        <v>32.54784535209521</v>
+        <v>33.271130804364</v>
       </c>
       <c r="N47">
-        <v>239.3521546479048</v>
+        <v>238.628869195636</v>
       </c>
       <c r="O47">
-        <v>83.77325412676666</v>
+        <v>83.5201042184726</v>
       </c>
       <c r="P47">
-        <v>155.5789005211381</v>
+        <v>155.1087649771634</v>
       </c>
       <c r="Q47">
-        <v>322.1789005211381</v>
+        <v>321.7087649771634</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1470513992791609</v>
+        <v>0.1484980068081521</v>
       </c>
       <c r="T47">
-        <v>1.473331230589599</v>
+        <v>1.494381132774087</v>
       </c>
       <c r="U47">
         <v>0.07235748822216712</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.353855595006287</v>
+        <v>8.172250038593106</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1018238126548301</v>
+        <v>0.1016047904011378</v>
       </c>
       <c r="C48">
-        <v>580.9781394196323</v>
+        <v>572.9327234484211</v>
       </c>
       <c r="D48">
-        <v>917.3941394196322</v>
+        <v>919.3447234484212</v>
       </c>
       <c r="E48">
-        <v>-65.18399999999997</v>
+        <v>-55.18799999999999</v>
       </c>
       <c r="F48">
-        <v>459.816</v>
+        <v>469.812</v>
       </c>
       <c r="G48">
         <v>123.4</v>
@@ -5223,28 +5223,28 @@
         <v>271.9</v>
       </c>
       <c r="M48">
-        <v>33.271130804364</v>
+        <v>33.99441625663277</v>
       </c>
       <c r="N48">
-        <v>238.628869195636</v>
+        <v>237.9055837433672</v>
       </c>
       <c r="O48">
-        <v>83.5201042184726</v>
+        <v>83.26695431017852</v>
       </c>
       <c r="P48">
-        <v>155.1087649771634</v>
+        <v>154.6386294331887</v>
       </c>
       <c r="Q48">
-        <v>321.7087649771634</v>
+        <v>321.2386294331886</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1484980068081521</v>
+        <v>0.1499992033005014</v>
       </c>
       <c r="T48">
-        <v>1.494381132774087</v>
+        <v>1.516225370890064</v>
       </c>
       <c r="U48">
         <v>0.07235748822216712</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.172250038593106</v>
+        <v>7.99837237819751</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1016047904011378</v>
+        <v>0.1013857681474455</v>
       </c>
       <c r="C49">
-        <v>572.9327234484211</v>
+        <v>564.8956199024406</v>
       </c>
       <c r="D49">
-        <v>919.3447234484212</v>
+        <v>921.3036199024405</v>
       </c>
       <c r="E49">
-        <v>-55.18799999999999</v>
+        <v>-45.19199999999995</v>
       </c>
       <c r="F49">
-        <v>469.812</v>
+        <v>479.808</v>
       </c>
       <c r="G49">
         <v>123.4</v>
@@ -5305,28 +5305,28 @@
         <v>271.9</v>
       </c>
       <c r="M49">
-        <v>33.99441625663277</v>
+        <v>34.71770170890156</v>
       </c>
       <c r="N49">
-        <v>237.9055837433672</v>
+        <v>237.1822982910984</v>
       </c>
       <c r="O49">
-        <v>83.26695431017852</v>
+        <v>83.01380440188444</v>
       </c>
       <c r="P49">
-        <v>154.6386294331887</v>
+        <v>154.168493889214</v>
       </c>
       <c r="Q49">
-        <v>321.2386294331886</v>
+        <v>320.768493889214</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1499992033005014</v>
+        <v>0.1515581381194796</v>
       </c>
       <c r="T49">
-        <v>1.516225370890064</v>
+        <v>1.538909772010502</v>
       </c>
       <c r="U49">
         <v>0.07235748822216712</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.99837237819751</v>
+        <v>7.831739620318394</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1013857681474455</v>
+        <v>0.1011667458937533</v>
       </c>
       <c r="C50">
-        <v>564.8956199024406</v>
+        <v>556.8668820303228</v>
       </c>
       <c r="D50">
-        <v>921.3036199024405</v>
+        <v>923.2708820303229</v>
       </c>
       <c r="E50">
-        <v>-45.19200000000001</v>
+        <v>-35.19599999999997</v>
       </c>
       <c r="F50">
-        <v>479.808</v>
+        <v>489.804</v>
       </c>
       <c r="G50">
         <v>123.4</v>
@@ -5387,28 +5387,28 @@
         <v>271.9</v>
       </c>
       <c r="M50">
-        <v>34.71770170890156</v>
+        <v>35.44098716117034</v>
       </c>
       <c r="N50">
-        <v>237.1822982910984</v>
+        <v>236.4590128388296</v>
       </c>
       <c r="O50">
-        <v>83.01380440188444</v>
+        <v>82.76065449359037</v>
       </c>
       <c r="P50">
-        <v>154.168493889214</v>
+        <v>153.6983583452393</v>
       </c>
       <c r="Q50">
-        <v>320.768493889214</v>
+        <v>320.2983583452393</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1515581381194796</v>
+        <v>0.1531782076372412</v>
       </c>
       <c r="T50">
-        <v>1.538909772010502</v>
+        <v>1.562483757488603</v>
       </c>
       <c r="U50">
         <v>0.07235748822216712</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.831739620318395</v>
+        <v>7.67190819949557</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1011667458937533</v>
+        <v>0.101207723640061</v>
       </c>
       <c r="C51">
-        <v>556.8668820303228</v>
+        <v>546.5021804901071</v>
       </c>
       <c r="D51">
-        <v>923.2708820303229</v>
+        <v>922.902180490107</v>
       </c>
       <c r="E51">
-        <v>-35.19599999999997</v>
+        <v>-25.19999999999999</v>
       </c>
       <c r="F51">
-        <v>489.804</v>
+        <v>499.8</v>
       </c>
       <c r="G51">
         <v>123.4</v>
@@ -5469,45 +5469,45 @@
         <v>271.9</v>
       </c>
       <c r="M51">
-        <v>35.44098716117034</v>
+        <v>36.56411261343912</v>
       </c>
       <c r="N51">
-        <v>236.4590128388296</v>
+        <v>235.3358873865608</v>
       </c>
       <c r="O51">
-        <v>82.76065449359037</v>
+        <v>82.36756058529629</v>
       </c>
       <c r="P51">
-        <v>153.6983583452393</v>
+        <v>152.9683268012645</v>
       </c>
       <c r="Q51">
-        <v>320.2983583452393</v>
+        <v>319.5683268012646</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1531782076372412</v>
+        <v>0.1548630799357133</v>
       </c>
       <c r="T51">
-        <v>1.562483757488603</v>
+        <v>1.58700070238583</v>
       </c>
       <c r="U51">
-        <v>0.07235748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V51">
         <v>0.35</v>
       </c>
       <c r="W51">
-        <v>0.04703236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y51">
-        <v>7.67190819949557</v>
+        <v>7.436253215675286</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.101207723640061</v>
+        <v>0.1009939013863687</v>
       </c>
       <c r="C52">
-        <v>546.5021804901071</v>
+        <v>538.4333159114221</v>
       </c>
       <c r="D52">
-        <v>922.902180490107</v>
+        <v>924.8293159114222</v>
       </c>
       <c r="E52">
-        <v>-25.19999999999999</v>
+        <v>-15.20400000000001</v>
       </c>
       <c r="F52">
-        <v>499.8</v>
+        <v>509.796</v>
       </c>
       <c r="G52">
         <v>123.4</v>
@@ -5551,28 +5551,28 @@
         <v>271.9</v>
       </c>
       <c r="M52">
-        <v>36.56411261343912</v>
+        <v>37.29539486570791</v>
       </c>
       <c r="N52">
-        <v>235.3358873865608</v>
+        <v>234.6046051342921</v>
       </c>
       <c r="O52">
-        <v>82.36756058529629</v>
+        <v>82.11161179700221</v>
       </c>
       <c r="P52">
-        <v>152.9683268012645</v>
+        <v>152.4929933372898</v>
       </c>
       <c r="Q52">
-        <v>319.5683268012646</v>
+        <v>319.0929933372898</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1548630799357133</v>
+        <v>0.1566167225320823</v>
       </c>
       <c r="T52">
-        <v>1.58700070238583</v>
+        <v>1.612518338911514</v>
       </c>
       <c r="U52">
         <v>0.07315748822216711</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.436253215675286</v>
+        <v>7.290444329093417</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1009939013863687</v>
+        <v>0.1007800791326764</v>
       </c>
       <c r="C53">
-        <v>538.4333159114221</v>
+        <v>530.3725163741343</v>
       </c>
       <c r="D53">
-        <v>924.8293159114222</v>
+        <v>926.7645163741344</v>
       </c>
       <c r="E53">
-        <v>-15.20400000000001</v>
+        <v>-5.20799999999997</v>
       </c>
       <c r="F53">
-        <v>509.796</v>
+        <v>519.792</v>
       </c>
       <c r="G53">
         <v>123.4</v>
@@ -5633,28 +5633,28 @@
         <v>271.9</v>
       </c>
       <c r="M53">
-        <v>37.29539486570791</v>
+        <v>38.02667711797669</v>
       </c>
       <c r="N53">
-        <v>234.6046051342921</v>
+        <v>233.8733228820233</v>
       </c>
       <c r="O53">
-        <v>82.11161179700221</v>
+        <v>81.85566300870813</v>
       </c>
       <c r="P53">
-        <v>152.4929933372898</v>
+        <v>152.0176598733152</v>
       </c>
       <c r="Q53">
-        <v>319.0929933372898</v>
+        <v>318.6176598733151</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1566167225320823</v>
+        <v>0.1584434335699665</v>
       </c>
       <c r="T53">
-        <v>1.612518338911514</v>
+        <v>1.639099210292435</v>
       </c>
       <c r="U53">
         <v>0.07315748822216711</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.290444329093417</v>
+        <v>7.150243476610852</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1007800791326764</v>
+        <v>0.1005662568789842</v>
       </c>
       <c r="C54">
-        <v>530.3725163741343</v>
+        <v>522.3198326125746</v>
       </c>
       <c r="D54">
-        <v>926.7645163741344</v>
+        <v>928.7078326125746</v>
       </c>
       <c r="E54">
-        <v>-5.20799999999997</v>
+        <v>4.788000000000011</v>
       </c>
       <c r="F54">
-        <v>519.792</v>
+        <v>529.788</v>
       </c>
       <c r="G54">
         <v>123.4</v>
@@ -5715,28 +5715,28 @@
         <v>271.9</v>
       </c>
       <c r="M54">
-        <v>38.02667711797669</v>
+        <v>38.75795937024547</v>
       </c>
       <c r="N54">
-        <v>233.8733228820233</v>
+        <v>233.1420406297545</v>
       </c>
       <c r="O54">
-        <v>81.85566300870813</v>
+        <v>81.59971422041407</v>
       </c>
       <c r="P54">
-        <v>152.0176598733152</v>
+        <v>151.5423264093404</v>
       </c>
       <c r="Q54">
-        <v>318.6176598733151</v>
+        <v>318.1423264093404</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1584434335699665</v>
+        <v>0.1603478769924417</v>
       </c>
       <c r="T54">
-        <v>1.639099210292435</v>
+        <v>1.666811182583183</v>
       </c>
       <c r="U54">
         <v>0.07315748822216711</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.150243476610852</v>
+        <v>7.015333222335175</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1005662568789842</v>
+        <v>0.1003524346252919</v>
       </c>
       <c r="C55">
-        <v>522.3198326125746</v>
+        <v>514.2753157875042</v>
       </c>
       <c r="D55">
-        <v>928.7078326125746</v>
+        <v>930.6593157875041</v>
       </c>
       <c r="E55">
-        <v>4.788000000000011</v>
+        <v>14.78399999999999</v>
       </c>
       <c r="F55">
-        <v>529.788</v>
+        <v>539.784</v>
       </c>
       <c r="G55">
         <v>123.4</v>
@@ -5797,28 +5797,28 @@
         <v>271.9</v>
       </c>
       <c r="M55">
-        <v>38.75795937024547</v>
+        <v>39.48924162251425</v>
       </c>
       <c r="N55">
-        <v>233.1420406297545</v>
+        <v>232.4107583774857</v>
       </c>
       <c r="O55">
-        <v>81.59971422041407</v>
+        <v>81.34376543212001</v>
       </c>
       <c r="P55">
-        <v>151.5423264093404</v>
+        <v>151.0669929453657</v>
       </c>
       <c r="Q55">
-        <v>318.1423264093404</v>
+        <v>317.6669929453657</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1603478769924417</v>
+        <v>0.1623351223028505</v>
       </c>
       <c r="T55">
-        <v>1.666811182583183</v>
+        <v>1.695728023234398</v>
       </c>
       <c r="U55">
         <v>0.07315748822216711</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.015333222335175</v>
+        <v>6.885419644143784</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1003524346252919</v>
+        <v>0.1001386123715996</v>
       </c>
       <c r="C56">
-        <v>514.2753157875042</v>
+        <v>506.2390174906028</v>
       </c>
       <c r="D56">
-        <v>930.6593157875041</v>
+        <v>932.6190174906029</v>
       </c>
       <c r="E56">
-        <v>14.78399999999999</v>
+        <v>24.78000000000009</v>
       </c>
       <c r="F56">
-        <v>539.784</v>
+        <v>549.7800000000001</v>
       </c>
       <c r="G56">
         <v>123.4</v>
@@ -5879,28 +5879,28 @@
         <v>271.9</v>
       </c>
       <c r="M56">
-        <v>39.48924162251425</v>
+        <v>40.22052387478304</v>
       </c>
       <c r="N56">
-        <v>232.4107583774857</v>
+        <v>231.6794761252169</v>
       </c>
       <c r="O56">
-        <v>81.34376543212001</v>
+        <v>81.08781664382592</v>
       </c>
       <c r="P56">
-        <v>151.0669929453657</v>
+        <v>150.591659481391</v>
       </c>
       <c r="Q56">
-        <v>317.6669929453657</v>
+        <v>317.191659481391</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1623351223028505</v>
+        <v>0.1644106896270552</v>
       </c>
       <c r="T56">
-        <v>1.695728023234398</v>
+        <v>1.725930056803445</v>
       </c>
       <c r="U56">
         <v>0.07315748822216711</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.885419644143784</v>
+        <v>6.760230196068441</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1001386123715996</v>
+        <v>0.09992479011790732</v>
       </c>
       <c r="C57">
-        <v>506.2390174906028</v>
+        <v>498.2109897490177</v>
       </c>
       <c r="D57">
-        <v>932.6190174906029</v>
+        <v>934.5869897490178</v>
       </c>
       <c r="E57">
-        <v>24.78000000000009</v>
+        <v>34.77600000000007</v>
       </c>
       <c r="F57">
-        <v>549.7800000000001</v>
+        <v>559.7760000000001</v>
       </c>
       <c r="G57">
         <v>123.4</v>
@@ -5961,28 +5961,28 @@
         <v>271.9</v>
       </c>
       <c r="M57">
-        <v>40.22052387478304</v>
+        <v>40.95180612705182</v>
       </c>
       <c r="N57">
-        <v>231.6794761252169</v>
+        <v>230.9481938729481</v>
       </c>
       <c r="O57">
-        <v>81.08781664382592</v>
+        <v>80.83186785553184</v>
       </c>
       <c r="P57">
-        <v>150.591659481391</v>
+        <v>150.1163260174163</v>
       </c>
       <c r="Q57">
-        <v>317.191659481391</v>
+        <v>316.7163260174163</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1644106896270552</v>
+        <v>0.1665806009205421</v>
       </c>
       <c r="T57">
-        <v>1.725930056803445</v>
+        <v>1.757504910080175</v>
       </c>
       <c r="U57">
         <v>0.07315748822216711</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.760230196068441</v>
+        <v>6.639511799710076</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09992479011790732</v>
+        <v>0.09971096786421504</v>
       </c>
       <c r="C58">
-        <v>498.2109897490177</v>
+        <v>490.1912850299656</v>
       </c>
       <c r="D58">
-        <v>934.5869897490178</v>
+        <v>936.5632850299655</v>
       </c>
       <c r="E58">
-        <v>34.77600000000007</v>
+        <v>44.77200000000005</v>
       </c>
       <c r="F58">
-        <v>559.7760000000001</v>
+        <v>569.772</v>
       </c>
       <c r="G58">
         <v>123.4</v>
@@ -6043,28 +6043,28 @@
         <v>271.9</v>
       </c>
       <c r="M58">
-        <v>40.95180612705182</v>
+        <v>41.6830883793206</v>
       </c>
       <c r="N58">
-        <v>230.9481938729481</v>
+        <v>230.2169116206794</v>
       </c>
       <c r="O58">
-        <v>80.83186785553184</v>
+        <v>80.57591906723778</v>
       </c>
       <c r="P58">
-        <v>150.1163260174163</v>
+        <v>149.6409925534416</v>
       </c>
       <c r="Q58">
-        <v>316.7163260174163</v>
+        <v>316.2409925534416</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1665806009205421</v>
+        <v>0.1688514383207027</v>
       </c>
       <c r="T58">
-        <v>1.757504910080175</v>
+        <v>1.790548361183731</v>
       </c>
       <c r="U58">
         <v>0.07315748822216711</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.639511799710076</v>
+        <v>6.523029136557269</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09971096786421504</v>
+        <v>0.09949714561052278</v>
       </c>
       <c r="C59">
-        <v>490.1912850299656</v>
+        <v>482.1799562453964</v>
       </c>
       <c r="D59">
-        <v>936.5632850299655</v>
+        <v>938.5479562453963</v>
       </c>
       <c r="E59">
-        <v>44.77200000000005</v>
+        <v>54.76800000000003</v>
       </c>
       <c r="F59">
-        <v>569.772</v>
+        <v>579.768</v>
       </c>
       <c r="G59">
         <v>123.4</v>
@@ -6125,28 +6125,28 @@
         <v>271.9</v>
       </c>
       <c r="M59">
-        <v>41.6830883793206</v>
+        <v>42.41437063158939</v>
       </c>
       <c r="N59">
-        <v>230.2169116206794</v>
+        <v>229.4856293684106</v>
       </c>
       <c r="O59">
-        <v>80.57591906723778</v>
+        <v>80.3199702789437</v>
       </c>
       <c r="P59">
-        <v>149.6409925534416</v>
+        <v>149.1656590894669</v>
       </c>
       <c r="Q59">
-        <v>316.2409925534416</v>
+        <v>315.7656590894669</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1688514383207027</v>
+        <v>0.1712304108351566</v>
       </c>
       <c r="T59">
-        <v>1.790548361183731</v>
+        <v>1.825165309958884</v>
       </c>
       <c r="U59">
         <v>0.07315748822216711</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.523029136557269</v>
+        <v>6.410563116961454</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09949714561052278</v>
+        <v>0.09928332335683049</v>
       </c>
       <c r="C60">
-        <v>482.1799562453964</v>
+        <v>474.1770567567156</v>
       </c>
       <c r="D60">
-        <v>938.5479562453963</v>
+        <v>940.5410567567155</v>
       </c>
       <c r="E60">
-        <v>54.76800000000003</v>
+        <v>64.76400000000001</v>
       </c>
       <c r="F60">
-        <v>579.768</v>
+        <v>589.764</v>
       </c>
       <c r="G60">
         <v>123.4</v>
@@ -6207,28 +6207,28 @@
         <v>271.9</v>
       </c>
       <c r="M60">
-        <v>42.41437063158939</v>
+        <v>43.14565288385816</v>
       </c>
       <c r="N60">
-        <v>229.4856293684106</v>
+        <v>228.7543471161418</v>
       </c>
       <c r="O60">
-        <v>80.3199702789437</v>
+        <v>80.06402149064964</v>
       </c>
       <c r="P60">
-        <v>149.1656590894669</v>
+        <v>148.6903256254922</v>
       </c>
       <c r="Q60">
-        <v>315.7656590894669</v>
+        <v>315.2903256254922</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1712304108351566</v>
+        <v>0.17372543078934</v>
       </c>
       <c r="T60">
-        <v>1.825165309958883</v>
+        <v>1.861470890381605</v>
       </c>
       <c r="U60">
         <v>0.07315748822216711</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.410563116961454</v>
+        <v>6.301909504809565</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09928332335683049</v>
+        <v>0.09906950110313822</v>
       </c>
       <c r="C61">
-        <v>474.1770567567156</v>
+        <v>466.1826403795658</v>
       </c>
       <c r="D61">
-        <v>940.5410567567155</v>
+        <v>942.5426403795658</v>
       </c>
       <c r="E61">
-        <v>64.76400000000001</v>
+        <v>74.75999999999999</v>
       </c>
       <c r="F61">
-        <v>589.764</v>
+        <v>599.76</v>
       </c>
       <c r="G61">
         <v>123.4</v>
@@ -6289,28 +6289,28 @@
         <v>271.9</v>
       </c>
       <c r="M61">
-        <v>43.14565288385816</v>
+        <v>43.87693513612695</v>
       </c>
       <c r="N61">
-        <v>228.7543471161418</v>
+        <v>228.023064863873</v>
       </c>
       <c r="O61">
-        <v>80.06402149064964</v>
+        <v>79.80807270235556</v>
       </c>
       <c r="P61">
-        <v>148.6903256254922</v>
+        <v>148.2149921615175</v>
       </c>
       <c r="Q61">
-        <v>315.2903256254922</v>
+        <v>314.8149921615175</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.17372543078934</v>
+        <v>0.1763452017412326</v>
       </c>
       <c r="T61">
-        <v>1.861470890381605</v>
+        <v>1.899591749825463</v>
       </c>
       <c r="U61">
         <v>0.07315748822216711</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.301909504809565</v>
+        <v>6.196877679729406</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09906950110313822</v>
+        <v>0.09885567884944596</v>
       </c>
       <c r="C62">
-        <v>466.1826403795658</v>
+        <v>458.1967613886721</v>
       </c>
       <c r="D62">
-        <v>942.5426403795658</v>
+        <v>944.552761388672</v>
       </c>
       <c r="E62">
-        <v>74.75999999999999</v>
+        <v>84.75599999999997</v>
       </c>
       <c r="F62">
-        <v>599.76</v>
+        <v>609.756</v>
       </c>
       <c r="G62">
         <v>123.4</v>
@@ -6371,28 +6371,28 @@
         <v>271.9</v>
       </c>
       <c r="M62">
-        <v>43.87693513612695</v>
+        <v>44.60821738839573</v>
       </c>
       <c r="N62">
-        <v>228.023064863873</v>
+        <v>227.2917826116042</v>
       </c>
       <c r="O62">
-        <v>79.80807270235556</v>
+        <v>79.55212391406148</v>
       </c>
       <c r="P62">
-        <v>148.2149921615175</v>
+        <v>147.7396586975428</v>
       </c>
       <c r="Q62">
-        <v>314.8149921615175</v>
+        <v>314.3396586975427</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1763452017412326</v>
+        <v>0.1790993199214274</v>
       </c>
       <c r="T62">
-        <v>1.899591749825463</v>
+        <v>1.939667525138236</v>
       </c>
       <c r="U62">
         <v>0.07315748822216711</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.196877679729406</v>
+        <v>6.095289521045316</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09885567884944596</v>
+        <v>0.09904485659575368</v>
       </c>
       <c r="C63">
-        <v>458.1967613886721</v>
+        <v>446.4218845340796</v>
       </c>
       <c r="D63">
-        <v>944.552761388672</v>
+        <v>942.7738845340797</v>
       </c>
       <c r="E63">
-        <v>84.75599999999997</v>
+        <v>94.75200000000007</v>
       </c>
       <c r="F63">
-        <v>609.756</v>
+        <v>619.7520000000001</v>
       </c>
       <c r="G63">
         <v>123.4</v>
@@ -6453,45 +6453,45 @@
         <v>271.9</v>
       </c>
       <c r="M63">
-        <v>44.60821738839573</v>
+        <v>45.95925164066452</v>
       </c>
       <c r="N63">
-        <v>227.2917826116042</v>
+        <v>225.9407483593355</v>
       </c>
       <c r="O63">
-        <v>79.55212391406148</v>
+        <v>79.07926192576741</v>
       </c>
       <c r="P63">
-        <v>147.7396586975428</v>
+        <v>146.861486433568</v>
       </c>
       <c r="Q63">
-        <v>314.3396586975427</v>
+        <v>313.461486433568</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1790993199214274</v>
+        <v>0.1819983916900535</v>
       </c>
       <c r="T63">
-        <v>1.939667525138236</v>
+        <v>1.981852551783261</v>
       </c>
       <c r="U63">
-        <v>0.07315748822216711</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V63">
         <v>0.35</v>
       </c>
       <c r="W63">
-        <v>0.04755236734440862</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>6.095289521045316</v>
+        <v>5.916110256230199</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09904485659575368</v>
+        <v>0.0988375343420614</v>
       </c>
       <c r="C64">
-        <v>446.4218845340796</v>
+        <v>438.3757307540886</v>
       </c>
       <c r="D64">
-        <v>942.7738845340797</v>
+        <v>944.7237307540886</v>
       </c>
       <c r="E64">
-        <v>94.75200000000007</v>
+        <v>104.748</v>
       </c>
       <c r="F64">
-        <v>619.7520000000001</v>
+        <v>629.748</v>
       </c>
       <c r="G64">
         <v>123.4</v>
@@ -6535,28 +6535,28 @@
         <v>271.9</v>
       </c>
       <c r="M64">
-        <v>45.95925164066452</v>
+        <v>46.7005298929333</v>
       </c>
       <c r="N64">
-        <v>225.9407483593355</v>
+        <v>225.1994701070667</v>
       </c>
       <c r="O64">
-        <v>79.07926192576741</v>
+        <v>78.81981453747333</v>
       </c>
       <c r="P64">
-        <v>146.861486433568</v>
+        <v>146.3796555695934</v>
       </c>
       <c r="Q64">
-        <v>313.461486433568</v>
+        <v>312.9796555695933</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1819983916900535</v>
+        <v>0.1850541700407675</v>
       </c>
       <c r="T64">
-        <v>1.981852551783261</v>
+        <v>2.026317850138827</v>
       </c>
       <c r="U64">
         <v>0.07415748822216711</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.916110256230199</v>
+        <v>5.822203744226546</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0988375343420614</v>
+        <v>0.09863021208836914</v>
       </c>
       <c r="C65">
-        <v>438.3757307540886</v>
+        <v>430.3376590386</v>
       </c>
       <c r="D65">
-        <v>944.7237307540886</v>
+        <v>946.6816590385999</v>
       </c>
       <c r="E65">
-        <v>104.748</v>
+        <v>114.744</v>
       </c>
       <c r="F65">
-        <v>629.748</v>
+        <v>639.744</v>
       </c>
       <c r="G65">
         <v>123.4</v>
@@ -6617,28 +6617,28 @@
         <v>271.9</v>
       </c>
       <c r="M65">
-        <v>46.7005298929333</v>
+        <v>47.44180814520208</v>
       </c>
       <c r="N65">
-        <v>225.1994701070667</v>
+        <v>224.4581918547979</v>
       </c>
       <c r="O65">
-        <v>78.81981453747333</v>
+        <v>78.56036714917926</v>
       </c>
       <c r="P65">
-        <v>146.3796555695934</v>
+        <v>145.8978247056186</v>
       </c>
       <c r="Q65">
-        <v>312.9796555695933</v>
+        <v>312.4978247056187</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1850541700407675</v>
+        <v>0.18827971385541</v>
       </c>
       <c r="T65">
-        <v>2.026317850138827</v>
+        <v>2.073253442847482</v>
       </c>
       <c r="U65">
         <v>0.07415748822216711</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.822203744226546</v>
+        <v>5.731231810723005</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09863021208836914</v>
+        <v>0.09842288983467685</v>
       </c>
       <c r="C66">
-        <v>430.3376590386</v>
+        <v>422.30771974191</v>
       </c>
       <c r="D66">
-        <v>946.6816590385999</v>
+        <v>948.64771974191</v>
       </c>
       <c r="E66">
-        <v>114.744</v>
+        <v>124.74</v>
       </c>
       <c r="F66">
-        <v>639.744</v>
+        <v>649.74</v>
       </c>
       <c r="G66">
         <v>123.4</v>
@@ -6699,28 +6699,28 @@
         <v>271.9</v>
       </c>
       <c r="M66">
-        <v>47.44180814520208</v>
+        <v>48.18308639747086</v>
       </c>
       <c r="N66">
-        <v>224.4581918547979</v>
+        <v>223.7169136025291</v>
       </c>
       <c r="O66">
-        <v>78.56036714917926</v>
+        <v>78.30091976088519</v>
       </c>
       <c r="P66">
-        <v>145.8978247056186</v>
+        <v>145.4159938416439</v>
       </c>
       <c r="Q66">
-        <v>312.4978247056187</v>
+        <v>312.0159938416439</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.18827971385541</v>
+        <v>0.1916895744594607</v>
       </c>
       <c r="T66">
-        <v>2.073253442847482</v>
+        <v>2.122871069425201</v>
       </c>
       <c r="U66">
         <v>0.07415748822216711</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.731231810723005</v>
+        <v>5.643059013634961</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09842288983467685</v>
+        <v>0.09821556758098457</v>
       </c>
       <c r="C67">
-        <v>422.30771974191</v>
+        <v>414.2859636374866</v>
       </c>
       <c r="D67">
-        <v>948.64771974191</v>
+        <v>950.6219636374865</v>
       </c>
       <c r="E67">
-        <v>124.74</v>
+        <v>134.736</v>
       </c>
       <c r="F67">
-        <v>649.74</v>
+        <v>659.736</v>
       </c>
       <c r="G67">
         <v>123.4</v>
@@ -6781,28 +6781,28 @@
         <v>271.9</v>
       </c>
       <c r="M67">
-        <v>48.18308639747086</v>
+        <v>48.92436464973964</v>
       </c>
       <c r="N67">
-        <v>223.7169136025291</v>
+        <v>222.9756353502603</v>
       </c>
       <c r="O67">
-        <v>78.30091976088519</v>
+        <v>78.04147237259112</v>
       </c>
       <c r="P67">
-        <v>145.4159938416439</v>
+        <v>144.9341629776692</v>
       </c>
       <c r="Q67">
-        <v>312.0159938416439</v>
+        <v>311.5341629776692</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1916895744594607</v>
+        <v>0.1953000150990438</v>
       </c>
       <c r="T67">
-        <v>2.122871069425201</v>
+        <v>2.175407379919257</v>
       </c>
       <c r="U67">
         <v>0.07415748822216711</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.643059013634961</v>
+        <v>5.557558119488976</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09821556758098457</v>
+        <v>0.0980082453272923</v>
       </c>
       <c r="C68">
-        <v>414.2859636374866</v>
+        <v>406.2724419223399</v>
       </c>
       <c r="D68">
-        <v>950.6219636374865</v>
+        <v>952.6044419223399</v>
       </c>
       <c r="E68">
-        <v>134.736</v>
+        <v>144.7320000000001</v>
       </c>
       <c r="F68">
-        <v>659.736</v>
+        <v>669.7320000000001</v>
       </c>
       <c r="G68">
         <v>123.4</v>
@@ -6863,28 +6863,28 @@
         <v>271.9</v>
       </c>
       <c r="M68">
-        <v>48.92436464973964</v>
+        <v>49.66564290200843</v>
       </c>
       <c r="N68">
-        <v>222.9756353502603</v>
+        <v>222.2343570979916</v>
       </c>
       <c r="O68">
-        <v>78.04147237259112</v>
+        <v>77.78202498429704</v>
       </c>
       <c r="P68">
-        <v>144.9341629776692</v>
+        <v>144.4523321136945</v>
       </c>
       <c r="Q68">
-        <v>311.5341629776692</v>
+        <v>311.0523321136945</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1953000150990438</v>
+        <v>0.1991292703228441</v>
       </c>
       <c r="T68">
-        <v>2.175407379919257</v>
+        <v>2.231127709231135</v>
       </c>
       <c r="U68">
         <v>0.07415748822216711</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.557558119488976</v>
+        <v>5.474609490839886</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0980082453272923</v>
+        <v>0.09780092307360003</v>
       </c>
       <c r="C69">
-        <v>406.2724419223399</v>
+        <v>398.2672062214497</v>
       </c>
       <c r="D69">
-        <v>952.6044419223399</v>
+        <v>954.5952062214498</v>
       </c>
       <c r="E69">
-        <v>144.7320000000001</v>
+        <v>154.7280000000001</v>
       </c>
       <c r="F69">
-        <v>669.7320000000001</v>
+        <v>679.7280000000001</v>
       </c>
       <c r="G69">
         <v>123.4</v>
@@ -6945,28 +6945,28 @@
         <v>271.9</v>
       </c>
       <c r="M69">
-        <v>49.66564290200843</v>
+        <v>50.40692115427721</v>
       </c>
       <c r="N69">
-        <v>222.2343570979916</v>
+        <v>221.4930788457228</v>
       </c>
       <c r="O69">
-        <v>77.78202498429704</v>
+        <v>77.52257759600296</v>
       </c>
       <c r="P69">
-        <v>144.4523321136945</v>
+        <v>143.9705012497198</v>
       </c>
       <c r="Q69">
-        <v>311.0523321136945</v>
+        <v>310.5705012497198</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1991292703228441</v>
+        <v>0.2031978539981318</v>
       </c>
       <c r="T69">
-        <v>2.231127709231135</v>
+        <v>2.290330559125005</v>
       </c>
       <c r="U69">
         <v>0.07415748822216711</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.474609490839886</v>
+        <v>5.3941005277393</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09780092307360003</v>
+        <v>0.09759360081990774</v>
       </c>
       <c r="C70">
-        <v>398.2672062214497</v>
+        <v>390.2703085922452</v>
       </c>
       <c r="D70">
-        <v>954.5952062214498</v>
+        <v>956.5943085922452</v>
       </c>
       <c r="E70">
-        <v>154.7280000000001</v>
+        <v>164.724</v>
       </c>
       <c r="F70">
-        <v>679.7280000000001</v>
+        <v>689.724</v>
       </c>
       <c r="G70">
         <v>123.4</v>
@@ -7027,28 +7027,28 @@
         <v>271.9</v>
       </c>
       <c r="M70">
-        <v>50.40692115427721</v>
+        <v>51.14819940654599</v>
       </c>
       <c r="N70">
-        <v>221.4930788457228</v>
+        <v>220.751800593454</v>
       </c>
       <c r="O70">
-        <v>77.52257759600296</v>
+        <v>77.2631302077089</v>
       </c>
       <c r="P70">
-        <v>143.9705012497198</v>
+        <v>143.4886703857451</v>
       </c>
       <c r="Q70">
-        <v>310.5705012497198</v>
+        <v>310.0886703857451</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2031978539981318</v>
+        <v>0.2075289269427929</v>
       </c>
       <c r="T70">
-        <v>2.290330559125005</v>
+        <v>2.353352947721705</v>
       </c>
       <c r="U70">
         <v>0.07415748822216711</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.3941005277393</v>
+        <v>5.315925157772064</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09759360081990774</v>
+        <v>0.09738627856621547</v>
       </c>
       <c r="C71">
-        <v>390.2703085922452</v>
+        <v>382.2818015291427</v>
       </c>
       <c r="D71">
-        <v>956.5943085922452</v>
+        <v>958.6018015291427</v>
       </c>
       <c r="E71">
-        <v>164.724</v>
+        <v>174.72</v>
       </c>
       <c r="F71">
-        <v>689.724</v>
+        <v>699.72</v>
       </c>
       <c r="G71">
         <v>123.4</v>
@@ -7109,28 +7109,28 @@
         <v>271.9</v>
       </c>
       <c r="M71">
-        <v>51.14819940654599</v>
+        <v>51.88947765881478</v>
       </c>
       <c r="N71">
-        <v>220.751800593454</v>
+        <v>220.0105223411852</v>
       </c>
       <c r="O71">
-        <v>77.2631302077089</v>
+        <v>77.00368281941482</v>
       </c>
       <c r="P71">
-        <v>143.4886703857451</v>
+        <v>143.0068395217704</v>
       </c>
       <c r="Q71">
-        <v>310.0886703857451</v>
+        <v>309.6068395217704</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2075289269427929</v>
+        <v>0.2121487380837648</v>
       </c>
       <c r="T71">
-        <v>2.353352947721705</v>
+        <v>2.420576828891519</v>
       </c>
       <c r="U71">
         <v>0.07415748822216711</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.315925157772064</v>
+        <v>5.239983369803891</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09738627856621547</v>
+        <v>0.09717895631252318</v>
       </c>
       <c r="C72">
-        <v>382.2818015291427</v>
+        <v>374.3017379681407</v>
       </c>
       <c r="D72">
-        <v>958.6018015291427</v>
+        <v>960.6177379681408</v>
       </c>
       <c r="E72">
-        <v>174.72</v>
+        <v>184.7160000000001</v>
       </c>
       <c r="F72">
-        <v>699.72</v>
+        <v>709.7160000000001</v>
       </c>
       <c r="G72">
         <v>123.4</v>
@@ -7191,28 +7191,28 @@
         <v>271.9</v>
       </c>
       <c r="M72">
-        <v>51.88947765881478</v>
+        <v>52.63075591108356</v>
       </c>
       <c r="N72">
-        <v>220.0105223411852</v>
+        <v>219.2692440889164</v>
       </c>
       <c r="O72">
-        <v>77.00368281941482</v>
+        <v>76.74423543112074</v>
       </c>
       <c r="P72">
-        <v>143.0068395217704</v>
+        <v>142.5250086577957</v>
       </c>
       <c r="Q72">
-        <v>309.6068395217704</v>
+        <v>309.1250086577957</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2121487380837648</v>
+        <v>0.2170871568896313</v>
       </c>
       <c r="T72">
-        <v>2.420576828891519</v>
+        <v>2.492436839797182</v>
       </c>
       <c r="U72">
         <v>0.07415748822216711</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.239983369803891</v>
+        <v>5.166180787130597</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09717895631252321</v>
+        <v>0.09697163405883093</v>
       </c>
       <c r="C73">
-        <v>374.3017379681406</v>
+        <v>366.3301712914738</v>
       </c>
       <c r="D73">
-        <v>960.6177379681405</v>
+        <v>962.6421712914738</v>
       </c>
       <c r="E73">
-        <v>184.716</v>
+        <v>194.712</v>
       </c>
       <c r="F73">
-        <v>709.716</v>
+        <v>719.712</v>
       </c>
       <c r="G73">
         <v>123.4</v>
@@ -7273,28 +7273,28 @@
         <v>271.9</v>
       </c>
       <c r="M73">
-        <v>52.63075591108355</v>
+        <v>53.37203416335234</v>
       </c>
       <c r="N73">
-        <v>219.2692440889164</v>
+        <v>218.5279658366476</v>
       </c>
       <c r="O73">
-        <v>76.74423543112074</v>
+        <v>76.48478804282666</v>
       </c>
       <c r="P73">
-        <v>142.5250086577957</v>
+        <v>142.043177793821</v>
       </c>
       <c r="Q73">
-        <v>309.1250086577957</v>
+        <v>308.643177793821</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2170871568896313</v>
+        <v>0.2223783198959168</v>
       </c>
       <c r="T73">
-        <v>2.492436839797181</v>
+        <v>2.569429708624677</v>
       </c>
       <c r="U73">
         <v>0.07415748822216711</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.166180787130598</v>
+        <v>5.094428276198228</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09697163405883093</v>
+        <v>0.09676431180513864</v>
       </c>
       <c r="C74">
-        <v>366.3301712914738</v>
+        <v>358.3671553323235</v>
       </c>
       <c r="D74">
-        <v>962.6421712914738</v>
+        <v>964.6751553323235</v>
       </c>
       <c r="E74">
-        <v>194.712</v>
+        <v>204.708</v>
       </c>
       <c r="F74">
-        <v>719.712</v>
+        <v>729.708</v>
       </c>
       <c r="G74">
         <v>123.4</v>
@@ -7355,28 +7355,28 @@
         <v>271.9</v>
       </c>
       <c r="M74">
-        <v>53.37203416335234</v>
+        <v>54.11331241562112</v>
       </c>
       <c r="N74">
-        <v>218.5279658366476</v>
+        <v>217.7866875843789</v>
       </c>
       <c r="O74">
-        <v>76.48478804282666</v>
+        <v>76.22534065453259</v>
       </c>
       <c r="P74">
-        <v>142.043177793821</v>
+        <v>141.5613469298463</v>
       </c>
       <c r="Q74">
-        <v>308.643177793821</v>
+        <v>308.1613469298462</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2223783198959168</v>
+        <v>0.228061420902668</v>
       </c>
       <c r="T74">
-        <v>2.569429708624677</v>
+        <v>2.652125752920876</v>
       </c>
       <c r="U74">
         <v>0.07415748822216711</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.094428276198228</v>
+        <v>5.024641587483184</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09676431180513864</v>
+        <v>0.09655698955144637</v>
       </c>
       <c r="C75">
-        <v>358.3671553323235</v>
+        <v>350.4127443795904</v>
       </c>
       <c r="D75">
-        <v>964.6751553323235</v>
+        <v>966.7167443795904</v>
       </c>
       <c r="E75">
-        <v>204.708</v>
+        <v>214.7040000000001</v>
       </c>
       <c r="F75">
-        <v>729.708</v>
+        <v>739.7040000000001</v>
       </c>
       <c r="G75">
         <v>123.4</v>
@@ -7437,28 +7437,28 @@
         <v>271.9</v>
       </c>
       <c r="M75">
-        <v>54.11331241562112</v>
+        <v>54.85459066788991</v>
       </c>
       <c r="N75">
-        <v>217.7866875843789</v>
+        <v>217.0454093321101</v>
       </c>
       <c r="O75">
-        <v>76.22534065453259</v>
+        <v>75.96589326623852</v>
       </c>
       <c r="P75">
-        <v>141.5613469298463</v>
+        <v>141.0795160658715</v>
       </c>
       <c r="Q75">
-        <v>308.1613469298462</v>
+        <v>307.6795160658716</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.228061420902668</v>
+        <v>0.234181683525323</v>
       </c>
       <c r="T75">
-        <v>2.652125752920876</v>
+        <v>2.741183031393705</v>
       </c>
       <c r="U75">
         <v>0.07415748822216711</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.024641587483184</v>
+        <v>4.956741025490167</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09655698955144637</v>
+        <v>0.0963496672977541</v>
       </c>
       <c r="C76">
-        <v>350.4127443795904</v>
+        <v>342.4669931827268</v>
       </c>
       <c r="D76">
-        <v>966.7167443795904</v>
+        <v>968.7669931827268</v>
       </c>
       <c r="E76">
-        <v>214.7040000000001</v>
+        <v>224.7</v>
       </c>
       <c r="F76">
-        <v>739.7040000000001</v>
+        <v>749.7</v>
       </c>
       <c r="G76">
         <v>123.4</v>
@@ -7519,28 +7519,28 @@
         <v>271.9</v>
       </c>
       <c r="M76">
-        <v>54.85459066788991</v>
+        <v>55.59586892015869</v>
       </c>
       <c r="N76">
-        <v>217.0454093321101</v>
+        <v>216.3041310798413</v>
       </c>
       <c r="O76">
-        <v>75.96589326623852</v>
+        <v>75.70644587794445</v>
       </c>
       <c r="P76">
-        <v>141.0795160658715</v>
+        <v>140.5976852018968</v>
       </c>
       <c r="Q76">
-        <v>307.6795160658716</v>
+        <v>307.1976852018968</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.234181683525323</v>
+        <v>0.2407915671577905</v>
       </c>
       <c r="T76">
-        <v>2.741183031393705</v>
+        <v>2.837364892144362</v>
       </c>
       <c r="U76">
         <v>0.07415748822216711</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.956741025490167</v>
+        <v>4.890651145150299</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0963496672977541</v>
+        <v>0.09614234504406183</v>
       </c>
       <c r="C77">
-        <v>342.4669931827268</v>
+        <v>334.5299569566306</v>
       </c>
       <c r="D77">
-        <v>968.7669931827268</v>
+        <v>970.8259569566306</v>
       </c>
       <c r="E77">
-        <v>224.7</v>
+        <v>234.696</v>
       </c>
       <c r="F77">
-        <v>749.7</v>
+        <v>759.696</v>
       </c>
       <c r="G77">
         <v>123.4</v>
@@ -7601,28 +7601,28 @@
         <v>271.9</v>
       </c>
       <c r="M77">
-        <v>55.59586892015869</v>
+        <v>56.33714717242747</v>
       </c>
       <c r="N77">
-        <v>216.3041310798413</v>
+        <v>215.5628528275725</v>
       </c>
       <c r="O77">
-        <v>75.70644587794445</v>
+        <v>75.44699848965037</v>
       </c>
       <c r="P77">
-        <v>140.5976852018968</v>
+        <v>140.1158543379221</v>
       </c>
       <c r="Q77">
-        <v>307.1976852018968</v>
+        <v>306.7158543379221</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2407915671577905</v>
+        <v>0.247952274426297</v>
       </c>
       <c r="T77">
-        <v>2.837364892144362</v>
+        <v>2.941561907957574</v>
       </c>
       <c r="U77">
         <v>0.07415748822216711</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.890651145150299</v>
+        <v>4.826300472187794</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09614234504406183</v>
+        <v>0.09593502279036953</v>
       </c>
       <c r="C78">
-        <v>334.5299569566306</v>
+        <v>326.6016913866035</v>
       </c>
       <c r="D78">
-        <v>970.8259569566306</v>
+        <v>972.8936913866035</v>
       </c>
       <c r="E78">
-        <v>234.696</v>
+        <v>244.692</v>
       </c>
       <c r="F78">
-        <v>759.696</v>
+        <v>769.692</v>
       </c>
       <c r="G78">
         <v>123.4</v>
@@ -7683,28 +7683,28 @@
         <v>271.9</v>
       </c>
       <c r="M78">
-        <v>56.33714717242747</v>
+        <v>57.07842542469625</v>
       </c>
       <c r="N78">
-        <v>215.5628528275725</v>
+        <v>214.8215745753037</v>
       </c>
       <c r="O78">
-        <v>75.44699848965037</v>
+        <v>75.18755110135629</v>
       </c>
       <c r="P78">
-        <v>140.1158543379221</v>
+        <v>139.6340234739474</v>
       </c>
       <c r="Q78">
-        <v>306.7158543379221</v>
+        <v>306.2340234739474</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.247952274426297</v>
+        <v>0.2557356518920648</v>
       </c>
       <c r="T78">
-        <v>2.941561907957574</v>
+        <v>3.054819533841498</v>
       </c>
       <c r="U78">
         <v>0.07415748822216711</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.826300472187794</v>
+        <v>4.763621245276265</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09593502279036953</v>
+        <v>0.09572770053667726</v>
       </c>
       <c r="C79">
-        <v>326.6016913866035</v>
+        <v>318.6822526333677</v>
       </c>
       <c r="D79">
-        <v>972.8936913866035</v>
+        <v>974.9702526333676</v>
       </c>
       <c r="E79">
-        <v>244.692</v>
+        <v>254.688</v>
       </c>
       <c r="F79">
-        <v>769.692</v>
+        <v>779.688</v>
       </c>
       <c r="G79">
         <v>123.4</v>
@@ -7765,28 +7765,28 @@
         <v>271.9</v>
       </c>
       <c r="M79">
-        <v>57.07842542469625</v>
+        <v>57.81970367696503</v>
       </c>
       <c r="N79">
-        <v>214.8215745753037</v>
+        <v>214.080296323035</v>
       </c>
       <c r="O79">
-        <v>75.18755110135629</v>
+        <v>74.92810371306223</v>
       </c>
       <c r="P79">
-        <v>139.6340234739474</v>
+        <v>139.1521926099727</v>
       </c>
       <c r="Q79">
-        <v>306.2340234739474</v>
+        <v>305.7521926099727</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2557356518920648</v>
+        <v>0.2642266091274479</v>
       </c>
       <c r="T79">
-        <v>3.054819533841498</v>
+        <v>3.178373307533053</v>
       </c>
       <c r="U79">
         <v>0.07415748822216711</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.763621245276265</v>
+        <v>4.702549178029134</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09572770053667726</v>
+        <v>0.09552037828298499</v>
       </c>
       <c r="C80">
-        <v>318.6822526333677</v>
+        <v>310.7716973381545</v>
       </c>
       <c r="D80">
-        <v>974.9702526333676</v>
+        <v>977.0556973381545</v>
       </c>
       <c r="E80">
-        <v>254.688</v>
+        <v>264.6840000000001</v>
       </c>
       <c r="F80">
-        <v>779.688</v>
+        <v>789.6840000000001</v>
       </c>
       <c r="G80">
         <v>123.4</v>
@@ -7847,28 +7847,28 @@
         <v>271.9</v>
       </c>
       <c r="M80">
-        <v>57.81970367696503</v>
+        <v>58.56098192923382</v>
       </c>
       <c r="N80">
-        <v>214.080296323035</v>
+        <v>213.3390180707661</v>
       </c>
       <c r="O80">
-        <v>74.92810371306223</v>
+        <v>74.66865632476815</v>
       </c>
       <c r="P80">
-        <v>139.1521926099727</v>
+        <v>138.670361745998</v>
       </c>
       <c r="Q80">
-        <v>305.7521926099727</v>
+        <v>305.270361745998</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2642266091274479</v>
+        <v>0.2735262289566771</v>
       </c>
       <c r="T80">
-        <v>3.178373307533053</v>
+        <v>3.31369410729047</v>
       </c>
       <c r="U80">
         <v>0.07415748822216711</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.702549178029134</v>
+        <v>4.643023239066739</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09552037828298499</v>
+        <v>0.09531305602929271</v>
       </c>
       <c r="C81">
-        <v>310.7716973381545</v>
+        <v>302.8700826278514</v>
       </c>
       <c r="D81">
-        <v>977.0556973381545</v>
+        <v>979.1500826278515</v>
       </c>
       <c r="E81">
-        <v>264.6840000000001</v>
+        <v>274.6800000000001</v>
       </c>
       <c r="F81">
-        <v>789.6840000000001</v>
+        <v>799.6800000000001</v>
       </c>
       <c r="G81">
         <v>123.4</v>
@@ -7929,28 +7929,28 @@
         <v>271.9</v>
       </c>
       <c r="M81">
-        <v>58.56098192923382</v>
+        <v>59.3022601815026</v>
       </c>
       <c r="N81">
-        <v>213.3390180707661</v>
+        <v>212.5977398184974</v>
       </c>
       <c r="O81">
-        <v>74.66865632476815</v>
+        <v>74.40920893647407</v>
       </c>
       <c r="P81">
-        <v>138.670361745998</v>
+        <v>138.1885308820233</v>
       </c>
       <c r="Q81">
-        <v>305.270361745998</v>
+        <v>304.7885308820233</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2735262289566771</v>
+        <v>0.2837558107688291</v>
       </c>
       <c r="T81">
-        <v>3.31369410729047</v>
+        <v>3.462546987023629</v>
       </c>
       <c r="U81">
         <v>0.07415748822216711</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.643023239066739</v>
+        <v>4.584985448578404</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09531305602929271</v>
+        <v>0.09510573377560044</v>
       </c>
       <c r="C82">
-        <v>302.8700826278514</v>
+        <v>294.977466120221</v>
       </c>
       <c r="D82">
-        <v>979.1500826278515</v>
+        <v>981.2534661202211</v>
       </c>
       <c r="E82">
-        <v>274.6800000000001</v>
+        <v>284.676</v>
       </c>
       <c r="F82">
-        <v>799.6800000000001</v>
+        <v>809.676</v>
       </c>
       <c r="G82">
         <v>123.4</v>
@@ -8011,28 +8011,28 @@
         <v>271.9</v>
       </c>
       <c r="M82">
-        <v>59.3022601815026</v>
+        <v>60.04353843377138</v>
       </c>
       <c r="N82">
-        <v>212.5977398184974</v>
+        <v>211.8564615662286</v>
       </c>
       <c r="O82">
-        <v>74.40920893647407</v>
+        <v>74.14976154818001</v>
       </c>
       <c r="P82">
-        <v>138.1885308820233</v>
+        <v>137.7067000180486</v>
       </c>
       <c r="Q82">
-        <v>304.7885308820233</v>
+        <v>304.3067000180486</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2837558107688291</v>
+        <v>0.2950621906664709</v>
       </c>
       <c r="T82">
-        <v>3.462546987023629</v>
+        <v>3.627068590939226</v>
       </c>
       <c r="U82">
         <v>0.07415748822216711</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.584985448578404</v>
+        <v>4.52838068995398</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09510573377560044</v>
+        <v>0.09623091152190816</v>
       </c>
       <c r="C83">
-        <v>294.977466120221</v>
+        <v>273.6733135788827</v>
       </c>
       <c r="D83">
-        <v>981.2534661202211</v>
+        <v>969.9453135788827</v>
       </c>
       <c r="E83">
-        <v>284.676</v>
+        <v>294.672</v>
       </c>
       <c r="F83">
-        <v>809.676</v>
+        <v>819.672</v>
       </c>
       <c r="G83">
         <v>123.4</v>
@@ -8093,45 +8093,45 @@
         <v>271.9</v>
       </c>
       <c r="M83">
-        <v>60.04353843377138</v>
+        <v>62.83399668604017</v>
       </c>
       <c r="N83">
-        <v>211.8564615662286</v>
+        <v>209.0660033139598</v>
       </c>
       <c r="O83">
-        <v>74.14976154818001</v>
+        <v>73.17310115988593</v>
       </c>
       <c r="P83">
-        <v>137.7067000180486</v>
+        <v>135.8929021540739</v>
       </c>
       <c r="Q83">
-        <v>304.3067000180486</v>
+        <v>302.4929021540739</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2950621906664709</v>
+        <v>0.3076248349971839</v>
       </c>
       <c r="T83">
-        <v>3.627068590939226</v>
+        <v>3.809870373067666</v>
       </c>
       <c r="U83">
-        <v>0.07415748822216711</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V83">
         <v>0.35</v>
       </c>
       <c r="W83">
-        <v>0.04820236734440862</v>
+        <v>0.04982736734440862</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y83">
-        <v>4.52838068995398</v>
+        <v>4.327275270401636</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09623091152190816</v>
+        <v>0.09603983926821588</v>
       </c>
       <c r="C84">
-        <v>273.6733135788827</v>
+        <v>265.5792015641637</v>
       </c>
       <c r="D84">
-        <v>969.9453135788827</v>
+        <v>971.8472015641638</v>
       </c>
       <c r="E84">
-        <v>294.672</v>
+        <v>304.6680000000001</v>
       </c>
       <c r="F84">
-        <v>819.672</v>
+        <v>829.6680000000001</v>
       </c>
       <c r="G84">
         <v>123.4</v>
@@ -8175,28 +8175,28 @@
         <v>271.9</v>
       </c>
       <c r="M84">
-        <v>62.83399668604017</v>
+        <v>63.60026493830895</v>
       </c>
       <c r="N84">
-        <v>209.0660033139598</v>
+        <v>208.299735061691</v>
       </c>
       <c r="O84">
-        <v>73.17310115988593</v>
+        <v>72.90490727159185</v>
       </c>
       <c r="P84">
-        <v>135.8929021540739</v>
+        <v>135.3948277900992</v>
       </c>
       <c r="Q84">
-        <v>302.4929021540739</v>
+        <v>301.9948277900992</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3076248349971839</v>
+        <v>0.3216654374844515</v>
       </c>
       <c r="T84">
-        <v>3.809870373067666</v>
+        <v>4.014178247211218</v>
       </c>
       <c r="U84">
         <v>0.07665748822216711</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.327275270401636</v>
+        <v>4.275139423770291</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09603983926821588</v>
+        <v>0.09584876701452361</v>
       </c>
       <c r="C85">
-        <v>265.5792015641637</v>
+        <v>257.4925627222652</v>
       </c>
       <c r="D85">
-        <v>971.8472015641638</v>
+        <v>973.7565627222652</v>
       </c>
       <c r="E85">
-        <v>304.6680000000001</v>
+        <v>314.6640000000001</v>
       </c>
       <c r="F85">
-        <v>829.6680000000001</v>
+        <v>839.6640000000001</v>
       </c>
       <c r="G85">
         <v>123.4</v>
@@ -8257,28 +8257,28 @@
         <v>271.9</v>
       </c>
       <c r="M85">
-        <v>63.60026493830895</v>
+        <v>64.36653319057774</v>
       </c>
       <c r="N85">
-        <v>208.299735061691</v>
+        <v>207.5334668094222</v>
       </c>
       <c r="O85">
-        <v>72.90490727159185</v>
+        <v>72.63671338329777</v>
       </c>
       <c r="P85">
-        <v>135.3948277900992</v>
+        <v>134.8967534261245</v>
       </c>
       <c r="Q85">
-        <v>301.9948277900992</v>
+        <v>301.4967534261244</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3216654374844515</v>
+        <v>0.3374611152826275</v>
       </c>
       <c r="T85">
-        <v>4.014178247211218</v>
+        <v>4.244024605622713</v>
       </c>
       <c r="U85">
         <v>0.07665748822216711</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.275139423770291</v>
+        <v>4.224244906820644</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09584876701452361</v>
+        <v>0.09565769476083136</v>
       </c>
       <c r="C86">
-        <v>257.4925627222653</v>
+        <v>249.4134411868994</v>
       </c>
       <c r="D86">
-        <v>973.7565627222652</v>
+        <v>975.6734411868993</v>
       </c>
       <c r="E86">
-        <v>314.664</v>
+        <v>324.66</v>
       </c>
       <c r="F86">
-        <v>839.664</v>
+        <v>849.66</v>
       </c>
       <c r="G86">
         <v>123.4</v>
@@ -8339,28 +8339,28 @@
         <v>271.9</v>
       </c>
       <c r="M86">
-        <v>64.36653319057773</v>
+        <v>65.13280144284651</v>
       </c>
       <c r="N86">
-        <v>207.5334668094222</v>
+        <v>206.7671985571534</v>
       </c>
       <c r="O86">
-        <v>72.63671338329777</v>
+        <v>72.3685194950037</v>
       </c>
       <c r="P86">
-        <v>134.8967534261245</v>
+        <v>134.3986790621498</v>
       </c>
       <c r="Q86">
-        <v>301.4967534261244</v>
+        <v>300.9986790621498</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3374611152826273</v>
+        <v>0.3553628834538934</v>
       </c>
       <c r="T86">
-        <v>4.244024605622711</v>
+        <v>4.504517145155739</v>
       </c>
       <c r="U86">
         <v>0.07665748822216711</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.224244906820645</v>
+        <v>4.174547907916873</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09565769476083136</v>
+        <v>0.09546662250713908</v>
       </c>
       <c r="C87">
-        <v>249.4134411868994</v>
+        <v>241.3418814399801</v>
       </c>
       <c r="D87">
-        <v>975.6734411868993</v>
+        <v>977.5978814399801</v>
       </c>
       <c r="E87">
-        <v>324.66</v>
+        <v>334.6560000000001</v>
       </c>
       <c r="F87">
-        <v>849.66</v>
+        <v>859.6560000000001</v>
       </c>
       <c r="G87">
         <v>123.4</v>
@@ -8421,28 +8421,28 @@
         <v>271.9</v>
       </c>
       <c r="M87">
-        <v>65.13280144284651</v>
+        <v>65.8990696951153</v>
       </c>
       <c r="N87">
-        <v>206.7671985571534</v>
+        <v>206.0009303048847</v>
       </c>
       <c r="O87">
-        <v>72.3685194950037</v>
+        <v>72.10032560670963</v>
       </c>
       <c r="P87">
-        <v>134.3986790621498</v>
+        <v>133.900604698175</v>
       </c>
       <c r="Q87">
-        <v>300.9986790621498</v>
+        <v>300.500604698175</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3553628834538934</v>
+        <v>0.3758220470781975</v>
       </c>
       <c r="T87">
-        <v>4.504517145155739</v>
+        <v>4.802222904622056</v>
       </c>
       <c r="U87">
         <v>0.07665748822216711</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.174547907916873</v>
+        <v>4.126006653173652</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09546662250713908</v>
+        <v>0.09527555025344678</v>
       </c>
       <c r="C88">
-        <v>241.3418814399801</v>
+        <v>233.2779283150637</v>
       </c>
       <c r="D88">
-        <v>977.5978814399801</v>
+        <v>979.5299283150638</v>
       </c>
       <c r="E88">
-        <v>334.6560000000001</v>
+        <v>344.652</v>
       </c>
       <c r="F88">
-        <v>859.6560000000001</v>
+        <v>869.652</v>
       </c>
       <c r="G88">
         <v>123.4</v>
@@ -8503,28 +8503,28 @@
         <v>271.9</v>
       </c>
       <c r="M88">
-        <v>65.8990696951153</v>
+        <v>66.66533794738407</v>
       </c>
       <c r="N88">
-        <v>206.0009303048847</v>
+        <v>205.2346620526159</v>
       </c>
       <c r="O88">
-        <v>72.10032560670963</v>
+        <v>71.83213171841557</v>
       </c>
       <c r="P88">
-        <v>133.900604698175</v>
+        <v>133.4025303342003</v>
       </c>
       <c r="Q88">
-        <v>300.500604698175</v>
+        <v>300.0025303342003</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3758220470781975</v>
+        <v>0.3994287743370099</v>
       </c>
       <c r="T88">
-        <v>4.802222904622056</v>
+        <v>5.145729550160114</v>
       </c>
       <c r="U88">
         <v>0.07665748822216711</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.126006653173652</v>
+        <v>4.078581289344071</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09527555025344678</v>
+        <v>0.09508447799975453</v>
       </c>
       <c r="C89">
-        <v>233.2779283150637</v>
+        <v>225.2216270008288</v>
       </c>
       <c r="D89">
-        <v>979.5299283150638</v>
+        <v>981.4696270008288</v>
       </c>
       <c r="E89">
-        <v>344.652</v>
+        <v>354.648</v>
       </c>
       <c r="F89">
-        <v>869.652</v>
+        <v>879.648</v>
       </c>
       <c r="G89">
         <v>123.4</v>
@@ -8585,28 +8585,28 @@
         <v>271.9</v>
       </c>
       <c r="M89">
-        <v>66.66533794738407</v>
+        <v>67.43160619965286</v>
       </c>
       <c r="N89">
-        <v>205.2346620526159</v>
+        <v>204.4683938003471</v>
       </c>
       <c r="O89">
-        <v>71.83213171841557</v>
+        <v>71.56393783012149</v>
       </c>
       <c r="P89">
-        <v>133.4025303342003</v>
+        <v>132.9044559702256</v>
       </c>
       <c r="Q89">
-        <v>300.0025303342003</v>
+        <v>299.5044559702256</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3994287743370099</v>
+        <v>0.4269699561389578</v>
       </c>
       <c r="T89">
-        <v>5.145729550160114</v>
+        <v>5.54648730328785</v>
       </c>
       <c r="U89">
         <v>0.07665748822216711</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.078581289344071</v>
+        <v>4.032233774692434</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09508447799975453</v>
+        <v>0.09691815574606225</v>
       </c>
       <c r="C90">
-        <v>225.2216270008288</v>
+        <v>196.9217544687372</v>
       </c>
       <c r="D90">
-        <v>981.4696270008288</v>
+        <v>963.1657544687372</v>
       </c>
       <c r="E90">
-        <v>354.648</v>
+        <v>364.644</v>
       </c>
       <c r="F90">
-        <v>879.648</v>
+        <v>889.644</v>
       </c>
       <c r="G90">
         <v>123.4</v>
@@ -8667,45 +8667,45 @@
         <v>271.9</v>
       </c>
       <c r="M90">
-        <v>67.43160619965286</v>
+        <v>71.31162845192165</v>
       </c>
       <c r="N90">
-        <v>204.4683938003471</v>
+        <v>200.5883715480783</v>
       </c>
       <c r="O90">
-        <v>71.56393783012149</v>
+        <v>70.20593004182741</v>
       </c>
       <c r="P90">
-        <v>132.9044559702256</v>
+        <v>130.3824415062509</v>
       </c>
       <c r="Q90">
-        <v>299.5044559702256</v>
+        <v>296.9824415062509</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4269699561389578</v>
+        <v>0.4595186255412597</v>
       </c>
       <c r="T90">
-        <v>5.54648730328785</v>
+        <v>6.020110102438809</v>
       </c>
       <c r="U90">
-        <v>0.07665748822216711</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V90">
         <v>0.35</v>
       </c>
       <c r="W90">
-        <v>0.04982736734440862</v>
+        <v>0.05210236734440863</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y90">
-        <v>4.032233774692434</v>
+        <v>3.812842391943344</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09691815574606225</v>
+        <v>0.09674983349236996</v>
       </c>
       <c r="C91">
-        <v>196.9217544687372</v>
+        <v>188.5774492276756</v>
       </c>
       <c r="D91">
-        <v>963.1657544687372</v>
+        <v>964.8174492276755</v>
       </c>
       <c r="E91">
-        <v>364.644</v>
+        <v>374.64</v>
       </c>
       <c r="F91">
-        <v>889.644</v>
+        <v>899.64</v>
       </c>
       <c r="G91">
         <v>123.4</v>
@@ -8749,28 +8749,28 @@
         <v>271.9</v>
       </c>
       <c r="M91">
-        <v>71.31162845192165</v>
+        <v>72.11288270419043</v>
       </c>
       <c r="N91">
-        <v>200.5883715480783</v>
+        <v>199.7871172958095</v>
       </c>
       <c r="O91">
-        <v>70.20593004182741</v>
+        <v>69.92549105353334</v>
       </c>
       <c r="P91">
-        <v>130.3824415062509</v>
+        <v>129.8616262422762</v>
       </c>
       <c r="Q91">
-        <v>296.9824415062509</v>
+        <v>296.4616262422762</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4595186255412597</v>
+        <v>0.4985770288240221</v>
       </c>
       <c r="T91">
-        <v>6.020110102438809</v>
+        <v>6.588457461419961</v>
       </c>
       <c r="U91">
         <v>0.08015748822216712</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.812842391943344</v>
+        <v>3.770477476477307</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09674983349236996</v>
+        <v>0.0965815112386777</v>
       </c>
       <c r="C92">
-        <v>188.5774492276756</v>
+        <v>180.2388185694218</v>
       </c>
       <c r="D92">
-        <v>964.8174492276755</v>
+        <v>966.4748185694218</v>
       </c>
       <c r="E92">
-        <v>374.64</v>
+        <v>384.6360000000001</v>
       </c>
       <c r="F92">
-        <v>899.64</v>
+        <v>909.6360000000001</v>
       </c>
       <c r="G92">
         <v>123.4</v>
@@ -8831,28 +8831,28 @@
         <v>271.9</v>
       </c>
       <c r="M92">
-        <v>72.11288270419043</v>
+        <v>72.91413695645922</v>
       </c>
       <c r="N92">
-        <v>199.7871172958095</v>
+        <v>198.9858630435407</v>
       </c>
       <c r="O92">
-        <v>69.92549105353334</v>
+        <v>69.64505206523926</v>
       </c>
       <c r="P92">
-        <v>129.8616262422762</v>
+        <v>129.3408109783015</v>
       </c>
       <c r="Q92">
-        <v>296.4616262422762</v>
+        <v>295.9408109783014</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4985770288240221</v>
+        <v>0.5463150772807317</v>
       </c>
       <c r="T92">
-        <v>6.588457461419961</v>
+        <v>7.283104233508036</v>
       </c>
       <c r="U92">
         <v>0.08015748822216712</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.770477476477307</v>
+        <v>3.729043658054479</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0965815112386777</v>
+        <v>0.09641318898498541</v>
       </c>
       <c r="C93">
-        <v>180.2388185694218</v>
+        <v>171.9058917877978</v>
       </c>
       <c r="D93">
-        <v>966.4748185694218</v>
+        <v>968.1378917877978</v>
       </c>
       <c r="E93">
-        <v>384.6360000000001</v>
+        <v>394.6320000000001</v>
       </c>
       <c r="F93">
-        <v>909.6360000000001</v>
+        <v>919.6320000000001</v>
       </c>
       <c r="G93">
         <v>123.4</v>
@@ -8913,28 +8913,28 @@
         <v>271.9</v>
       </c>
       <c r="M93">
-        <v>72.91413695645922</v>
+        <v>73.71539120872799</v>
       </c>
       <c r="N93">
-        <v>198.9858630435407</v>
+        <v>198.184608791272</v>
       </c>
       <c r="O93">
-        <v>69.64505206523926</v>
+        <v>69.36461307694519</v>
       </c>
       <c r="P93">
-        <v>129.3408109783015</v>
+        <v>128.8199957143268</v>
       </c>
       <c r="Q93">
-        <v>295.9408109783014</v>
+        <v>295.4199957143268</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5463150772807317</v>
+        <v>0.6059876378516187</v>
       </c>
       <c r="T93">
-        <v>7.283104233508036</v>
+        <v>8.151412698618129</v>
       </c>
       <c r="U93">
         <v>0.08015748822216712</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.729043658054479</v>
+        <v>3.688510574814757</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09641318898498541</v>
+        <v>0.09624486673129314</v>
       </c>
       <c r="C94">
-        <v>171.9058917877978</v>
+        <v>163.5786983786021</v>
       </c>
       <c r="D94">
-        <v>968.1378917877978</v>
+        <v>969.8066983786022</v>
       </c>
       <c r="E94">
-        <v>394.6320000000001</v>
+        <v>404.628</v>
       </c>
       <c r="F94">
-        <v>919.6320000000001</v>
+        <v>929.628</v>
       </c>
       <c r="G94">
         <v>123.4</v>
@@ -8995,28 +8995,28 @@
         <v>271.9</v>
       </c>
       <c r="M94">
-        <v>73.71539120872799</v>
+        <v>74.51664546099677</v>
       </c>
       <c r="N94">
-        <v>198.184608791272</v>
+        <v>197.3833545390032</v>
       </c>
       <c r="O94">
-        <v>69.36461307694519</v>
+        <v>69.08417408865112</v>
       </c>
       <c r="P94">
-        <v>128.8199957143268</v>
+        <v>128.2991804503521</v>
       </c>
       <c r="Q94">
-        <v>295.4199957143268</v>
+        <v>294.8991804503521</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6059876378516187</v>
+        <v>0.6827095014427591</v>
       </c>
       <c r="T94">
-        <v>8.151412698618129</v>
+        <v>9.26780929661682</v>
       </c>
       <c r="U94">
         <v>0.08015748822216712</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.688510574814757</v>
+        <v>3.648849170784491</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09624486673129314</v>
+        <v>0.09607654447760086</v>
       </c>
       <c r="C95">
-        <v>163.5786983786021</v>
+        <v>155.2572680413559</v>
       </c>
       <c r="D95">
-        <v>969.8066983786022</v>
+        <v>971.481268041356</v>
       </c>
       <c r="E95">
-        <v>404.628</v>
+        <v>414.624</v>
       </c>
       <c r="F95">
-        <v>929.628</v>
+        <v>939.624</v>
       </c>
       <c r="G95">
         <v>123.4</v>
@@ -9077,28 +9077,28 @@
         <v>271.9</v>
       </c>
       <c r="M95">
-        <v>74.51664546099677</v>
+        <v>75.31789971326556</v>
       </c>
       <c r="N95">
-        <v>197.3833545390032</v>
+        <v>196.5821002867344</v>
       </c>
       <c r="O95">
-        <v>69.08417408865112</v>
+        <v>68.80373510035704</v>
       </c>
       <c r="P95">
-        <v>128.2991804503521</v>
+        <v>127.7783651863774</v>
       </c>
       <c r="Q95">
-        <v>294.8991804503521</v>
+        <v>294.3783651863774</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6827095014427591</v>
+        <v>0.7850053195642799</v>
       </c>
       <c r="T95">
-        <v>9.26780929661682</v>
+        <v>10.75633809394841</v>
       </c>
       <c r="U95">
         <v>0.08015748822216712</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.648849170784491</v>
+        <v>3.610031626414443</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09607654447760086</v>
+        <v>0.0959082222239086</v>
       </c>
       <c r="C96">
-        <v>155.2572680413559</v>
+        <v>146.9416306810642</v>
       </c>
       <c r="D96">
-        <v>971.481268041356</v>
+        <v>973.1616306810644</v>
       </c>
       <c r="E96">
-        <v>414.624</v>
+        <v>424.6200000000001</v>
       </c>
       <c r="F96">
-        <v>939.624</v>
+        <v>949.6200000000001</v>
       </c>
       <c r="G96">
         <v>123.4</v>
@@ -9159,28 +9159,28 @@
         <v>271.9</v>
       </c>
       <c r="M96">
-        <v>75.31789971326556</v>
+        <v>76.11915396553435</v>
       </c>
       <c r="N96">
-        <v>196.5821002867344</v>
+        <v>195.7808460344656</v>
       </c>
       <c r="O96">
-        <v>68.80373510035704</v>
+        <v>68.52329611206297</v>
       </c>
       <c r="P96">
-        <v>127.7783651863774</v>
+        <v>127.2575499224027</v>
       </c>
       <c r="Q96">
-        <v>294.3783651863774</v>
+        <v>293.8575499224027</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7850053195642799</v>
+        <v>0.9282194649344091</v>
       </c>
       <c r="T96">
-        <v>10.75633809394841</v>
+        <v>12.84027841021264</v>
       </c>
       <c r="U96">
         <v>0.08015748822216712</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.610031626414443</v>
+        <v>3.572031293504817</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.0959082222239086</v>
+        <v>0.09573989997021631</v>
       </c>
       <c r="C97">
-        <v>146.9416306810642</v>
+        <v>138.6318164099972</v>
       </c>
       <c r="D97">
-        <v>973.1616306810644</v>
+        <v>974.8478164099972</v>
       </c>
       <c r="E97">
-        <v>424.6200000000001</v>
+        <v>434.6160000000001</v>
       </c>
       <c r="F97">
-        <v>949.6200000000001</v>
+        <v>959.6160000000001</v>
       </c>
       <c r="G97">
         <v>123.4</v>
@@ -9241,28 +9241,28 @@
         <v>271.9</v>
       </c>
       <c r="M97">
-        <v>76.11915396553435</v>
+        <v>76.92040821780313</v>
       </c>
       <c r="N97">
-        <v>195.7808460344656</v>
+        <v>194.9795917821968</v>
       </c>
       <c r="O97">
-        <v>68.52329611206297</v>
+        <v>68.24285712376889</v>
       </c>
       <c r="P97">
-        <v>127.2575499224027</v>
+        <v>126.736734658428</v>
       </c>
       <c r="Q97">
-        <v>293.8575499224027</v>
+        <v>293.336734658428</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9282194649344091</v>
+        <v>1.143040682989603</v>
       </c>
       <c r="T97">
-        <v>12.84027841021264</v>
+        <v>15.96618888460898</v>
       </c>
       <c r="U97">
         <v>0.08015748822216712</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.572031293504817</v>
+        <v>3.534822634197475</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09573989997021631</v>
+        <v>0.09733697771652405</v>
       </c>
       <c r="C98">
-        <v>138.6318164099973</v>
+        <v>112.8684203157187</v>
       </c>
       <c r="D98">
-        <v>974.8478164099972</v>
+        <v>959.0804203157186</v>
       </c>
       <c r="E98">
-        <v>434.616</v>
+        <v>444.612</v>
       </c>
       <c r="F98">
-        <v>959.616</v>
+        <v>969.612</v>
       </c>
       <c r="G98">
         <v>123.4</v>
@@ -9323,45 +9323,45 @@
         <v>271.9</v>
       </c>
       <c r="M98">
-        <v>76.92040821780311</v>
+        <v>80.43657607007189</v>
       </c>
       <c r="N98">
-        <v>194.9795917821968</v>
+        <v>191.4634239299281</v>
       </c>
       <c r="O98">
-        <v>68.24285712376889</v>
+        <v>67.01219837547482</v>
       </c>
       <c r="P98">
-        <v>126.736734658428</v>
+        <v>124.4512255544532</v>
       </c>
       <c r="Q98">
-        <v>293.336734658428</v>
+        <v>291.0512255544533</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.1430406829896</v>
+        <v>1.501076046414921</v>
       </c>
       <c r="T98">
-        <v>15.96618888460894</v>
+        <v>21.17603967526949</v>
       </c>
       <c r="U98">
-        <v>0.08015748822216712</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V98">
         <v>0.35</v>
       </c>
       <c r="W98">
-        <v>0.05210236734440863</v>
+        <v>0.05392236734440863</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y98">
-        <v>3.534822634197476</v>
+        <v>3.380303007466849</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09733697771652405</v>
+        <v>0.09718685546283176</v>
       </c>
       <c r="C99">
-        <v>112.8684203157187</v>
+        <v>104.3327737510934</v>
       </c>
       <c r="D99">
-        <v>959.0804203157186</v>
+        <v>960.5407737510935</v>
       </c>
       <c r="E99">
-        <v>444.612</v>
+        <v>454.6080000000001</v>
       </c>
       <c r="F99">
-        <v>969.612</v>
+        <v>979.6080000000001</v>
       </c>
       <c r="G99">
         <v>123.4</v>
@@ -9405,28 +9405,28 @@
         <v>271.9</v>
       </c>
       <c r="M99">
-        <v>80.43657607007189</v>
+        <v>81.26581912234069</v>
       </c>
       <c r="N99">
-        <v>191.4634239299281</v>
+        <v>190.6341808776593</v>
       </c>
       <c r="O99">
-        <v>67.01219837547482</v>
+        <v>66.72196330718074</v>
       </c>
       <c r="P99">
-        <v>124.4512255544532</v>
+        <v>123.9122175704785</v>
       </c>
       <c r="Q99">
-        <v>291.0512255544533</v>
+        <v>290.5122175704785</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.501076046414921</v>
+        <v>2.217146773265563</v>
       </c>
       <c r="T99">
-        <v>21.17603967526949</v>
+        <v>31.59574125659058</v>
       </c>
       <c r="U99">
         <v>0.08295748822216711</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.380303007466849</v>
+        <v>3.345810119635554</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09718685546283176</v>
+        <v>0.0970367332091395</v>
       </c>
       <c r="C100">
-        <v>104.3327737510934</v>
+        <v>95.80158121208842</v>
       </c>
       <c r="D100">
-        <v>960.5407737510935</v>
+        <v>962.0055812120884</v>
       </c>
       <c r="E100">
-        <v>454.6080000000001</v>
+        <v>464.604</v>
       </c>
       <c r="F100">
-        <v>979.6080000000001</v>
+        <v>989.604</v>
       </c>
       <c r="G100">
         <v>123.4</v>
@@ -9487,28 +9487,28 @@
         <v>271.9</v>
       </c>
       <c r="M100">
-        <v>81.26581912234069</v>
+        <v>82.09506217460947</v>
       </c>
       <c r="N100">
-        <v>190.6341808776593</v>
+        <v>189.8049378253905</v>
       </c>
       <c r="O100">
-        <v>66.72196330718074</v>
+        <v>66.43172823888668</v>
       </c>
       <c r="P100">
-        <v>123.9122175704785</v>
+        <v>123.3732095865038</v>
       </c>
       <c r="Q100">
-        <v>290.5122175704785</v>
+        <v>289.9732095865038</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.217146773265563</v>
+        <v>4.365358953817491</v>
       </c>
       <c r="T100">
-        <v>31.59574125659058</v>
+        <v>62.85484600055388</v>
       </c>
       <c r="U100">
         <v>0.08295748822216711</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.345810119635554</v>
+        <v>3.312014057821053</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.0970367332091395</v>
-      </c>
-      <c r="C101">
-        <v>95.80158121208842</v>
-      </c>
-      <c r="D101">
-        <v>962.0055812120884</v>
-      </c>
-      <c r="E101">
-        <v>464.604</v>
-      </c>
-      <c r="F101">
-        <v>989.604</v>
-      </c>
-      <c r="G101">
-        <v>123.4</v>
-      </c>
-      <c r="H101">
-        <v>474.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>438.5</v>
-      </c>
-      <c r="K101">
-        <v>166.6</v>
-      </c>
-      <c r="L101">
-        <v>271.9</v>
-      </c>
-      <c r="M101">
-        <v>82.09506217460947</v>
-      </c>
-      <c r="N101">
-        <v>189.8049378253905</v>
-      </c>
-      <c r="O101">
-        <v>66.43172823888668</v>
-      </c>
-      <c r="P101">
-        <v>123.3732095865038</v>
-      </c>
-      <c r="Q101">
-        <v>289.9732095865038</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.365358953817491</v>
-      </c>
-      <c r="T101">
-        <v>62.85484600055388</v>
-      </c>
-      <c r="U101">
-        <v>0.08295748822216711</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.05392236734440863</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.312014057821053</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
